--- a/FOA Singles/Outdoor-Single.xlsx
+++ b/FOA Singles/Outdoor-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,12 +834,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALBA Patio Wooden Bench and its Contemporary character. This outdoor bench is made to fit naturally into the room. Finished in Antique Oak or Black tones, the Cast Iron, Wood build balances durability with visual appeal.
-Product Dimensions: 49 1/4"L X 23 3/4"W X 31"H
-Materials: Cast Iron, Wood.
-Color: Antique Oak or Black
-Weight: 48.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALBA Patio Wooden Bench and its Contemporary character. This outdoor bench is made to fit naturally into the room. Finished in Antique Oak or Black tones, the Cast Iron, Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 49 1/4"L X 23 3/4"W X 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Cast Iron, Wood.&lt;br&gt;
+Color: Antique Oak or Black&lt;br&gt;
+Weight: 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BORDEAUX Bench brings a Contemporary look to your home with a refined, comfortable feel. This outdoor bench is made to fit naturally into the room. The Aluminum, Stainless Steel, Polyspun Fabric construction is complemented by Natural or Beige tones for a polished look.
-Product Dimensions: 57"W X 16.5"D X 18.5"H
-Materials: Aluminum, Stainless Steel, Polyspun Fabric.
-Color: Natural or Beige
-Weight: 26.41 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BORDEAUX Bench brings a Contemporary look to your home with a refined, comfortable feel. This outdoor bench is made to fit naturally into the room. The Aluminum, Stainless Steel, Polyspun Fabric construction is complemented by Natural or Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 57"W X 16.5"D X 18.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Stainless Steel, Polyspun Fabric.&lt;br&gt;
+Color: Natural or Beige&lt;br&gt;
+Weight: 26.41 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BORKUM Garden Bench and its Rustic character. This outdoor bench is made to fit naturally into the room. Finished in Natural tones, the Acacia Wood build balances durability with visual appeal.
-Product Dimensions: 48"W X 22 1/2"D X 33 1/2"H
-Materials: Acacia Wood.
-Color: Natural
-Weight: 27.56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BORKUM Garden Bench and its Rustic character. This outdoor bench is made to fit naturally into the room. Finished in Natural tones, the Acacia Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"W X 22 1/2"D X 33 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 27.56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1207,10 +1207,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOHARI Patio Bench is designed to complement your space with a balanced, versatile look. Built as a outdoor bench, it pairs well with a wide range of interiors.
-Product Dimensions: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")
-Weight: 52.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOHARI Patio Bench is designed to complement your space with a balanced, versatile look. Built as a outdoor bench, it pairs well with a wide range of interiors.&lt;br&gt;
+Product Dimensions: 58"W X 29"D X 25.5"H (SEAT HT: 16.5")&lt;br&gt;
+Weight: 52.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MINOT Patio Steel Bench, styled in Contemporary and designed for everyday comfort. Built as a outdoor bench, it pairs well with a wide range of interiors. With Steel and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 50 2/5"L X 20"W X 33 7/8"H
-Materials: Steel.
-Color: Black
-Weight: 35.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MINOT Patio Steel Bench, styled in Contemporary and designed for everyday comfort. Built as a outdoor bench, it pairs well with a wide range of interiors. With Steel and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 50 2/5"L X 20"W X 33 7/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 35.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-POTTER Patio Steel Bench adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor bench, it is designed to complement your space. Crafted from Steel, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 50 2/5"L X 20 1/4"W X 34"H
-Materials: Steel.
-Color: Black
-Weight: 35.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+POTTER Patio Steel Bench adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor bench, it is designed to complement your space. Crafted from Steel, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 50 2/5"L X 20 1/4"W X 34"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 35.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SINTRA Bench and its Contemporary character. This outdoor bench is made to fit naturally into the room. Finished in Black or Gray tones, the Steel, Polyspun build balances durability with visual appeal.
-Product Dimensions: 59"W X 15 3/4"D X 17 1/4"H
-Materials: Steel, Polyspun.
-Color: Black or Gray
-Weight: 24 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SINTRA Bench and its Contemporary character. This outdoor bench is made to fit naturally into the room. Finished in Black or Gray tones, the Steel, Polyspun build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 59"W X 15 3/4"D X 17 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SKIPPER Shoe Storage Bench and its Contemporary character. This outdoor bench is made to fit naturally into the room. Finished in Natural or Gray tones, the Bamboo, Polyester build balances durability with visual appeal.
-Product Dimensions: 35.5"W X 13"D X 19.5"H
-Materials: Bamboo, Polyester.
-Color: Natural or Gray
-Weight: 17.53 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SKIPPER Shoe Storage Bench and its Contemporary character. This outdoor bench is made to fit naturally into the room. Finished in Natural or Gray tones, the Bamboo, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 35.5"W X 13"D X 19.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Bamboo, Polyester.&lt;br&gt;
+Color: Natural or Gray&lt;br&gt;
+Weight: 17.53 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1817,9 +1817,9 @@
       </c>
       <c r="G10" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA Patio Bench is designed to complement your space with a balanced, versatile look. As a outdoor bench, it is designed to complement your space.
-Product Dimensions: 51.5"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA Patio Bench is designed to complement your space with a balanced, versatile look. As a outdoor bench, it is designed to complement your space.&lt;br&gt;
+Product Dimensions: 51.5"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H10" s="46" t="inlineStr">
@@ -1925,9 +1925,9 @@
       </c>
       <c r="G11" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA Patio Bench is designed to complement your space with a balanced, versatile look. This outdoor bench is made to fit naturally into the room.
-Product Dimensions: 51.5"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA Patio Bench is designed to complement your space with a balanced, versatile look. This outdoor bench is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 51.5"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H11" s="46" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALVERTA Foldable Chair adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 33 1/2"W X 28 1/4"D X 57"H
-Materials: Steel, Mesh, Fabric.
-Color: Black
-Weight: 53.57 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALVERTA Foldable Chair adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 33 1/2"W X 28 1/4"D X 57"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 53.57 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALVERTA Foldable Chair and its Modern character. As a outdoor chair, it is designed to complement your space. Finished in Light Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.
-Product Dimensions: 33 1/2"W X 28 1/4"D X 57"H
-Materials: Steel, Mesh, Fabric.
-Color: Light Gray
-Weight: 53.37 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALVERTA Foldable Chair and its Modern character. As a outdoor chair, it is designed to complement your space. Finished in Light Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 33 1/2"W X 28 1/4"D X 57"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 53.37 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ALYCIA Arm Chair w/ Cushion (6 or CTN) and its Transitional character. This outdoor chair is made to fit naturally into the room. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, build balances durability with visual appeal.
-Product Dimensions: 22 3/8"W X 27"D X 33 1/2-35 1/2"H
-Materials: Aluminum, Polyester Canvas.
-Color: White or Beige or Gray
-Weight: 122.98 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ALYCIA Arm Chair w/ Cushion (6 or CTN) and its Transitional character. This outdoor chair is made to fit naturally into the room. Finished in White or Beige or Gray tones, the Aluminum, Polyester Canvas, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22 3/8"W X 27"D X 33 1/2-35 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas.&lt;br&gt;
+Color: White or Beige or Gray&lt;br&gt;
+Weight: 122.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ANTIGUA Arm Chair and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Gun Metal or Brown or Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build balances durability with visual appeal.
-Product Dimensions: 25 1/2"W X 29 1/2"D X 40 1/4"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gun Metal or Brown or Gray
-Weight: 30 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ANTIGUA Arm Chair and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Gun Metal or Brown or Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 25 1/2"W X 29 1/2"D X 40 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gun Metal or Brown or Gray&lt;br&gt;
+Weight: 30 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ASHURA Stacking Chair (2 or STACK) and its Contemporary character. As a outdoor chair, it is designed to complement your space. Finished in Gray tones, the Steel, Aluminum, PE Rattan Wicker, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 23"W X 23.5"D X 35"H
-Materials: Steel, Aluminum, PE Rattan Wicker, Polyester Fabric.
-Color: Gray
-Weight: 24.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ASHURA Stacking Chair (2 or STACK) and its Contemporary character. As a outdoor chair, it is designed to complement your space. Finished in Gray tones, the Steel, Aluminum, PE Rattan Wicker, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Aluminum, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 24.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ASHURA Stacking Chair (8 or STACK) brings a Contemporary look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Steel, Aluminum, PE Rattan Wicker, Polyester Fabric construction is complemented by Gray tones for a polished look.
-Product Dimensions: 23"W X 23.5"D X 35"H
-Materials: Steel, Aluminum, PE Rattan Wicker, Polyester Fabric.
-Color: Gray
-Weight: 88 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ASHURA Stacking Chair (8 or STACK) brings a Contemporary look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Steel, Aluminum, PE Rattan Wicker, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 23"W X 23.5"D X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Aluminum, PE Rattan Wicker, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BORDEAUX Arm Chair (2 / CTN) and its Contemporary character. As a outdoor chair, it is designed to complement your space. Finished in Natural or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build balances durability with visual appeal.
-Product Dimensions: 24"W X 26.5"D X 33"H
-Materials: Aluminum, Stainless Steel, Polyspun Fabric.
-Color: Natural or Beige
-Weight: 50.76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BORDEAUX Arm Chair (2 / CTN) and its Contemporary character. As a outdoor chair, it is designed to complement your space. Finished in Natural or Beige tones, the Aluminum, Stainless Steel, Polyspun Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 24"W X 26.5"D X 33"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Stainless Steel, Polyspun Fabric.&lt;br&gt;
+Color: Natural or Beige&lt;br&gt;
+Weight: 50.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BORDEAUX Side Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Aluminum, Stainless Steel, Polyspun Fabric, it is finished in Natural or Beige tones that pair easily with surrounding decor.
-Product Dimensions: 20"W X 26.5"D X 33"H
-Materials: Aluminum, Stainless Steel, Polyspun Fabric.
-Color: Natural or Beige
-Weight: 45.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BORDEAUX Side Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Aluminum, Stainless Steel, Polyspun Fabric, it is finished in Natural or Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20"W X 26.5"D X 33"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Stainless Steel, Polyspun Fabric.&lt;br&gt;
+Color: Natural or Beige&lt;br&gt;
+Weight: 45.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="G20" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BREEZE Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 28"W X 34 1/4"D X 46"H
-Materials: Steel, Mesh, Fabric.
-Color: Black
-Weight: 31.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BREEZE Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 28"W X 34 1/4"D X 46"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 31.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H20" s="48" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="G21" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BREEZE Swing Chair and its Modern character. Built as a outdoor chair, it pairs well with a wide range of interiors. Finished in Dark Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.
-Product Dimensions: 28"W X 34 1/4"D X 46"H
-Materials: Steel, Mesh, Fabric.
-Color: Dark Gray
-Weight: 31.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BREEZE Swing Chair and its Modern character. Built as a outdoor chair, it pairs well with a wide range of interiors. Finished in Dark Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 28"W X 34 1/4"D X 46"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 31.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H21" s="48" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="G22" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BREEZE Swing Chair brings a Modern look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Steel, Mesh, Fabric construction is complemented by Light Gray tones for a polished look.
-Product Dimensions: 28"W X 34 1/4"D X 46"H
-Materials: Steel, Mesh, Fabric.
-Color: Light Gray
-Weight: 31.08 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BREEZE Swing Chair brings a Modern look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Steel, Mesh, Fabric construction is complemented by Light Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 28"W X 34 1/4"D X 46"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 31.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H22" s="48" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with CRUSH Swing Chair, styled in Modern and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel, Mesh, Fabric and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H
-Materials: Steel, Mesh, Fabric.
-Color: Black
-Weight: 27.78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with CRUSH Swing Chair, styled in Modern and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel, Mesh, Fabric and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 27.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CRUSH Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, Mesh, Fabric, it is finished in Dark Gray tones that pair easily with surrounding decor.
-Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H
-Materials: Steel, Mesh, Fabric.
-Color: Dark Gray
-Weight: 27.78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CRUSH Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, Mesh, Fabric, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Dark Gray&lt;br&gt;
+Weight: 27.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CRUSH Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Light Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.
-Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H
-Materials: Steel, Mesh, Fabric.
-Color: Light Gray
-Weight: 27.78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CRUSH Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Light Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Light Gray&lt;br&gt;
+Weight: 27.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with CYPRUS Bar Chair and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build balances durability with visual appeal.
-Product Dimensions: 20 1/4"W X 18"D X 41 3/4"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gray
-Weight: 67.25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with CYPRUS Bar Chair and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 20 1/4"W X 18"D X 41 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 67.25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ELK Adirondrack Chair, styled in Rustic and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Eucalyptus Wood and Dark Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H
-Materials: Eucalyptus Wood.
-Color: Dark Brown
-Weight: 26.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ELK Adirondrack Chair, styled in Rustic and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Eucalyptus Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
+Color: Dark Brown&lt;br&gt;
+Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H27" s="31" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELK Adirondrack Chair adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Eucalyptus Wood, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H
-Materials: Eucalyptus Wood.
-Color: Gray
-Weight: 26.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELK Adirondrack Chair adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Eucalyptus Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H28" s="31" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ELK Adirondrack Chair and its Rustic character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Eucalyptus Wood build balances durability with visual appeal.
-Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H
-Materials: Eucalyptus Wood.
-Color: Natural
-Weight: 26.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ELK Adirondrack Chair and its Rustic character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H29" s="31" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ELK Adirondrack Chair brings a Rustic look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Eucalyptus Wood construction is complemented by Weathered Gray tones for a polished look.
-Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H
-Materials: Eucalyptus Wood.
-Color: Weathered Gray
-Weight: 26.46 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ELK Adirondrack Chair brings a Rustic look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Eucalyptus Wood construction is complemented by Weathered Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
+Color: Weathered Gray&lt;br&gt;
+Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H30" s="31" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ENZI Stacking Chair (2 or STACK) and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Steel Frame, PE Rattan Wicker build balances durability with visual appeal.
-Product Dimensions: 21"W X 25"D X 34"H
-Materials: Steel Frame, PE Rattan Wicker.
-Color: Natural
-Weight: 16.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ENZI Stacking Chair (2 or STACK) and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Steel Frame, PE Rattan Wicker build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 21"W X 25"D X 34"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 16.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ENZI Stacking Chair (40 or STACK) brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel Frame, PE Rattan Wicker construction is complemented by Natural tones for a polished look.
-Product Dimensions: 21"W X 25"D X 34"H
-Materials: Steel Frame, PE Rattan Wicker.
-Color: Natural
-Weight: 334 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ENZI Stacking Chair (40 or STACK) brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel Frame, PE Rattan Wicker construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: 21"W X 25"D X 34"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 334 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GATES Footstool (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Polyester, Foam, Solid Wood, it is finished in White or Natural tones that pair easily with surrounding decor.
-Product Dimensions: 15.5"W X 15.5"D X 15.5"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Polyester, Foam, Solid Wood.
-Color: White or Natural
-Weight: 14.33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GATES Footstool (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Polyester, Foam, Solid Wood, it is finished in White or Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 15.5"W X 15.5"D X 15.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Polyester, Foam, Solid Wood.&lt;br&gt;
+Color: White or Natural&lt;br&gt;
+Weight: 14.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALEY Hammock Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 47"L X 122"W X 44"H
-Materials: Steel.
-Color: Black
-Weight: 32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALEY Hammock Stand adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 47"L X 122"W X 44"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4968,10 +4968,10 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOHARI Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.
-Product Dimensions: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")
-Weight: 60.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOHARI Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.&lt;br&gt;
+Product Dimensions: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")&lt;br&gt;
+Weight: 60.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="G36" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with KYUSHU Chair (2 / CTN) and its Rustic character. As a outdoor chair, it is designed to complement your space. Finished in Beige or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.
-Product Dimensions: CHAIR: 24"W X 27 1/4"D X 34 1/4"H
-Materials: Acacia Wood, Polyester.
-Color: Beige or Natural
-Weight: 68.02 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with KYUSHU Chair (2 / CTN) and its Rustic character. As a outdoor chair, it is designed to complement your space. Finished in Beige or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Beige or Natural&lt;br&gt;
+Weight: 68.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H36" s="50" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="G37" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KYUSHU Chair (2 / CTN) brings a Rustic look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Acacia Wood, Polyester construction is complemented by Black or Natural tones for a polished look.
-Product Dimensions: CHAIR: 24"W X 27 1/4"D X 34 1/4"H
-Materials: Acacia Wood, Polyester.
-Color: Black or Natural
-Weight: 68.02 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KYUSHU Chair (2 / CTN) brings a Rustic look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Acacia Wood, Polyester construction is complemented by Black or Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Black or Natural&lt;br&gt;
+Weight: 68.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H37" s="50" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MACKAY Reclining Chair (2 / CTN) brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Aluminum, FSC Certified 100% Teak Wood construction is complemented by Beige or Natural Teak tones for a polished look.
-Product Dimensions: 24 1/2"W X 27 1/2"D X 42 1/2"H
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Beige or Natural Teak
-Weight: 60.62 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MACKAY Reclining Chair (2 / CTN) brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Aluminum, FSC Certified 100% Teak Wood construction is complemented by Beige or Natural Teak tones for a polished look.&lt;br&gt;
+Product Dimensions: 24 1/2"W X 27 1/2"D X 42 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Beige or Natural Teak&lt;br&gt;
+Weight: 60.62 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MACKAY Stacking Chair, styled in Contemporary and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Aluminum, FSC Certified 100% Teak Wood and Gun Metal or Natural Teak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 22.5"W X 25"D X 34"H
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Gun Metal or Natural Teak
-Weight: 5.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MACKAY Stacking Chair, styled in Contemporary and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Aluminum, FSC Certified 100% Teak Wood and Gun Metal or Natural Teak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 22.5"W X 25"D X 34"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Gun Metal or Natural Teak&lt;br&gt;
+Weight: 5.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MALIN Chair (2 / CTN), styled in Contemporary and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Metal, Leatherette, and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 17"W X 20"D X 36"H
-Materials: Metal, Leatherette.
-Color: Black
-Weight: 20.72 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MALIN Chair (2 / CTN), styled in Contemporary and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Metal, Leatherette, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 17"W X 20"D X 36"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Leatherette.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 20.72 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOOSE Rocking Chair brings a Rustic look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Eucalyptus Wood construction is complemented by Natural tones for a polished look.
-Product Dimensions: 33"W X 27 1/2"D X 45"H
-Materials: Eucalyptus Wood.
-Color: Natural
-Weight: 61.61 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOOSE Rocking Chair brings a Rustic look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Eucalyptus Wood construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: 33"W X 27 1/2"D X 45"H&lt;/p&gt;
+&lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 61.61 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUSA Folding Arm Chair adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Teak Wood, it is finished in Natural tones that pair easily with surrounding decor.
-Product Dimensions: 22"W X 24.5"D X 37.5"H
-Materials: Teak Wood.
-Color: Natural
-Weight: 27.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUSA Folding Arm Chair adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Teak Wood, it is finished in Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 22"W X 24.5"D X 37.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Teak Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 27.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NYA Outdoor Chair 4Pc or Carton, styled in Contemporary and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and Natural tones, it blends structure and softness in one clean profile.
-Product Dimensions: 25"W X 23.5"D X 31"H
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Natural
-Weight: 9.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NYA Outdoor Chair 4Pc or Carton, styled in Contemporary and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 25"W X 23.5"D X 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 9.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="G44" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NYA Patio Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black tones that pair easily with surrounding decor.
-Product Dimensions: 25"W X 23.5"D X 31"H
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Black
-Weight: 25.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NYA Patio Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 25"W X 23.5"D X 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 25.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="52" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="G45" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NYA Patio Chair (2 / CTN) and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build balances durability with visual appeal.
-Product Dimensions: 25"W X 23.5"D X 31"H
-Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Natural
-Weight: 9.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NYA Patio Chair (2 / CTN) and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 25"W X 23.5"D X 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 9.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="52" t="inlineStr">
@@ -6353,11 +6353,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVERI Wicker Coffee Table (9 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Fabric, Faux Rattan, it is finished in Brown or Dark Teal tones that pair easily with surrounding decor.
-Product Dimensions: 20"L X 33"W X 16"H
-Materials: Fabric, Faux Rattan.
-Color: Brown or Dark Teal</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVERI Wicker Coffee Table (9 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Fabric, Faux Rattan, it is finished in Brown or Dark Teal tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20"L X 33"W X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Faux Rattan.&lt;br&gt;
+Color: Brown or Dark Teal&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with OLIVERI Wicker Loveseat and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Brown or Dark Teal tones, the Fabric, Faux Rattan build balances durability with visual appeal.
-Product Dimensions: 48"L X 23"W X 35"H
-Materials: Fabric, Faux Rattan.
-Color: Brown or Dark Teal
-Weight: 38 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with OLIVERI Wicker Loveseat and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Brown or Dark Teal tones, the Fabric, Faux Rattan build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 48"L X 23"W X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Faux Rattan.&lt;br&gt;
+Color: Brown or Dark Teal&lt;br&gt;
+Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6606,11 +6606,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVERI Wicker Loveseat (9 or Stack) brings a Transitional look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Fabric, Faux Rattan construction is complemented by Brown or Dark Teal tones for a polished look.
-Product Dimensions: 48"L X 23"W X 35"H
-Materials: Fabric, Faux Rattan.
-Color: Brown or Dark Teal</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVERI Wicker Loveseat (9 or Stack) brings a Transitional look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Fabric, Faux Rattan construction is complemented by Brown or Dark Teal tones for a polished look.&lt;br&gt;
+Product Dimensions: 48"L X 23"W X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Faux Rattan.&lt;br&gt;
+Color: Brown or Dark Teal&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6728,11 +6728,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OLIVERI Wicker Stacking Chair (18 or Stack), styled in Transitional and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Fabric, Faux Rattan and Brown or Dark Teal tones, it blends structure and softness in one clean profile.
-Product Dimensions: 26"L X 23"W X 35"H
-Materials: Fabric, Faux Rattan.
-Color: Brown or Dark Teal</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OLIVERI Wicker Stacking Chair (18 or Stack), styled in Transitional and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Fabric, Faux Rattan and Brown or Dark Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 26"L X 23"W X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Faux Rattan.&lt;br&gt;
+Color: Brown or Dark Teal&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALMA Adjustable Chairs (6 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel, Polyspun Fabric construction is complemented by Black or Gray tones for a polished look.
-Product Dimensions: 24"W X 33"D X 38"H
-Materials: Steel, Polyspun Fabric.
-Color: Black or Gray
-Weight: 127.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALMA Adjustable Chairs (6 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel, Polyspun Fabric construction is complemented by Black or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 24"W X 33"D X 38"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 127.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PALMA Swivel Counter Height Arm Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Ceramic Tile, Polyrattan, Polyspun Fabric, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 25"W X 26"D X 45"H
-Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.
-Color: Black or Gray
-Weight: 70 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PALMA Swivel Counter Height Arm Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Ceramic Tile, Polyrattan, Polyspun Fabric, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 25"W X 26"D X 45"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 70 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PERSE Rocking Chair adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Cast Iron, Wood, it is finished in Dark Gray or Oak tones that pair easily with surrounding decor.
-Product Dimensions: 76"L X 31"W X 37 1/4"H
-Materials: Cast Iron, Wood.
-Color: Dark Gray or Oak
-Weight: 76 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PERSE Rocking Chair adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Cast Iron, Wood, it is finished in Dark Gray or Oak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 76"L X 31"W X 37 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Cast Iron, Wood.&lt;br&gt;
+Color: Dark Gray or Oak&lt;br&gt;
+Weight: 76 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="G53" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PIERRO Stacking Chair (2 or Stack), styled in Transitional and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Glass, Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Blue
-Weight: 28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PIERRO Stacking Chair (2 or Stack), styled in Transitional and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Glass, Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="54" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="G54" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO Stacking Chair (2 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Glass, Metal, Fabric, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Red
-Weight: 28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO Stacking Chair (2 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Glass, Metal, Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H54" s="54" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="G55" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PIERRO Stacking Chair (2 or Stack) and its Transitional character. Built as a outdoor chair, it pairs well with a wide range of interiors. Finished in Beige tones, the Glass, Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Beige
-Weight: 28 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PIERRO Stacking Chair (2 or Stack) and its Transitional character. Built as a outdoor chair, it pairs well with a wide range of interiors. Finished in Beige tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H55" s="54" t="inlineStr">
@@ -7616,11 +7616,11 @@
       </c>
       <c r="G56" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO Stacking Chair (28 or Stack) brings a Transitional look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Glass, Metal, Fabric construction is complemented by Blue tones for a polished look.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Blue</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO Stacking Chair (28 or Stack) brings a Transitional look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Glass, Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="56" t="inlineStr">
@@ -7742,11 +7742,11 @@
       </c>
       <c r="G57" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PIERRO Stacking Chair (28 or Stack), styled in Transitional and designed for everyday comfort. This outdoor chair is made to fit naturally into the room. With Glass, Metal, Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Red</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PIERRO Stacking Chair (28 or Stack), styled in Transitional and designed for everyday comfort. This outdoor chair is made to fit naturally into the room. With Glass, Metal, Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Red&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="56" t="inlineStr">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="G58" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO Stacking Chair (28 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Glass, Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Beige</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO Stacking Chair (28 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Glass, Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="56" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PIERRO Stacking Chair (4 or Stack) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Blue
-Weight: 48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PIERRO Stacking Chair (4 or Stack) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H59" s="29" t="inlineStr">
@@ -8127,12 +8127,12 @@
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO Stacking Chair (4 or Stack) brings a Transitional look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Glass, Metal, Fabric construction is complemented by Red tones for a polished look.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Red
-Weight: 48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO Stacking Chair (4 or Stack) brings a Transitional look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Glass, Metal, Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H60" s="29" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PIERRO Stacking Chair (4 or Stack), styled in Transitional and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Glass, Metal, Fabric and Beige tones, it blends structure and softness in one clean profile.
-Product Dimensions: 23"L X 29"W X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Beige
-Weight: 48 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PIERRO Stacking Chair (4 or Stack), styled in Transitional and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Glass, Metal, Fabric and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 48 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H61" s="29" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="G62" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SANDOR Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Black tones, the Steel, Mesh, Fabric build balances durability with visual appeal.
-Product Dimensions: 65 1/2"W X 57"D X 74 3/4"H
-Materials: Steel, Mesh, Fabric.
-Color: Black
-Weight: 59.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SANDOR Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Black tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 65 1/2"W X 57"D X 74 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 59.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H62" s="50" t="inlineStr">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="G63" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANDOR Swing Chair brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel, Mesh, Fabric construction is complemented by White tones for a polished look.
-Product Dimensions: 65 1/2"W X 57"D X 74 3/4"H
-Materials: Steel, Mesh, Fabric.
-Color: White
-Weight: 59.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANDOR Swing Chair brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel, Mesh, Fabric construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 65 1/2"W X 57"D X 74 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 59.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H63" s="50" t="inlineStr">
@@ -8645,9 +8645,9 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SARABI Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.
-Product Dimensions: CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SARABI Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.&lt;br&gt;
+Product Dimensions: CHAIR: 25.5"W X 28.5"D X 26.5"H (SEAT HT: 14", SEAT DP: 20")&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SEGOVIA Swivel Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Steel, Polyethylene Wicker, Polyspun, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 29 3/4"W X 27 1/4"D X 33 1/4"H
-Materials: Steel, Polyethylene Wicker, Polyspun.
-Color: Black or Gray
-Weight: 150 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SEGOVIA Swivel Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Steel, Polyethylene Wicker, Polyspun, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 29 3/4"W X 27 1/4"D X 33 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 150 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SEGOVIA Swivel Glider Arm Chair (2 / CTN) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Navy or Black or Gray tones, the Steel, Polyethylene Wicker, Ceremic, Polyspun build balances durability with visual appeal.
-Product Dimensions: 30.5"W X 25.5"D X 30.5"H
-Materials: Steel, Polyethylene Wicker, Ceremic, Polyspun.
-Color: Navy or Black or Gray
-Weight: 82.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SEGOVIA Swivel Glider Arm Chair (2 / CTN) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Navy or Black or Gray tones, the Steel, Polyethylene Wicker, Ceremic, Polyspun build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 30.5"W X 25.5"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Ceremic, Polyspun.&lt;br&gt;
+Color: Navy or Black or Gray&lt;br&gt;
+Weight: 82.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINTRA Arm Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, Polyethylene Wicker, Polyspun, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 26 1/2"W X 23 1/2"D X 36 1/2"H
-Materials: Steel, Polyethylene Wicker, Polyspun.
-Color: Black or Gray
-Weight: 46.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINTRA Arm Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, Polyethylene Wicker, Polyspun, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 26 1/2"W X 23 1/2"D X 36 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 46.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINTRA Swivel Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Polyethylene Wicker, Polyspun, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 26 1/2"W X 23 1/2"D X 36 1/2"H
-Materials: Steel, Polyethylene Wicker, Polyspun.
-Color: Black or Gray
-Weight: 58.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINTRA Swivel Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Polyethylene Wicker, Polyspun, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 26 1/2"W X 23 1/2"D X 36 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 58.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9259,12 +9259,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TOMOHON Swivel Wicker Chair brings a Contemporary look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Fabric, Faux Rattan construction is complemented by White tones for a polished look.
-Product Dimensions: 39.5"W X 24.5"D X 30.5"H
-Materials: Fabric, Faux Rattan.
-Color: White
-Weight: 35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TOMOHON Swivel Wicker Chair brings a Contemporary look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Fabric, Faux Rattan construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: 39.5"W X 24.5"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Faux Rattan.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with VALE Footstool (2 / CTN), styled in Contemporary and designed for everyday comfort. This outdoor chair is made to fit naturally into the room. With Leatherette, Solid Wood, and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 16"W X 9"D X 12"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Leatherette, Solid Wood.
-Color: Black
-Weight: 13.01 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with VALE Footstool (2 / CTN), styled in Contemporary and designed for everyday comfort. This outdoor chair is made to fit naturally into the room. With Leatherette, Solid Wood, and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 16"W X 9"D X 12"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Solid Wood.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 13.01 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9510,9 +9510,9 @@
       </c>
       <c r="G71" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. Built as a outdoor chair, it pairs well with a wide range of interiors.
-Product Dimensions: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. Built as a outdoor chair, it pairs well with a wide range of interiors.&lt;br&gt;
+Product Dimensions: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H71" s="59" t="inlineStr">
@@ -9618,9 +9618,9 @@
       </c>
       <c r="G72" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.
-Product Dimensions: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.&lt;br&gt;
+Product Dimensions: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H72" s="59" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ALYCIA Patio Table brings a Transitional look to your home with a refined, comfortable feel. Built as a outdoor dining table, it pairs well with a wide range of interiors. The Aluminum, Glass, construction is complemented by White or Gray tones for a polished look.
-Product Dimensions: 70 7/8"L X 39 3/8"W X 30 3/4"H
-Materials: Aluminum, Glass.
-Color: White or Gray
-Weight: 94.84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ALYCIA Patio Table brings a Transitional look to your home with a refined, comfortable feel. Built as a outdoor dining table, it pairs well with a wide range of interiors. The Aluminum, Glass, construction is complemented by White or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 70 7/8"L X 39 3/8"W X 30 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Glass.&lt;br&gt;
+Color: White or Gray&lt;br&gt;
+Weight: 94.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO Outdoor Dining Table brings a Transitional look to your home with a refined, comfortable feel. Built as a outdoor dining table, it pairs well with a wide range of interiors. The Glass, Metal, Fabric construction is complemented by Black tones for a polished look.
-Product Dimensions: 59"L X 36"W X 28"H
-Materials: Glass, Metal, Fabric.
-Color: Black
-Weight: 49.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO Outdoor Dining Table brings a Transitional look to your home with a refined, comfortable feel. Built as a outdoor dining table, it pairs well with a wide range of interiors. The Glass, Metal, Fabric construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 59"L X 36"W X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 49.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9982,13 +9982,13 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTIGUA Height brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor table, it pairs well with a wide range of interiors. The Aluminum, Polyethylene Wicker, Polyspun construction is complemented by Gun Metal or Brown or Gray tones for a polished look.
-Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H
-Size: Adjustable Table
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gun Metal or Brown or Gray
-Weight: 38.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTIGUA Height brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor table, it pairs well with a wide range of interiors. The Aluminum, Polyethylene Wicker, Polyspun construction is complemented by Gun Metal or Brown or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 63"L X 35 1/2"W X 17 3/4 - 27"H&lt;br&gt;
+Size: Adjustable Table&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gun Metal or Brown or Gray&lt;br&gt;
+Weight: 38.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AROSA Fire Pit Counter Height Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor table is made to fit naturally into the room. Crafted from Steel, Ceramic Tile, Polyrattan, Polyspun Fabric, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 36.5"W X 36.5"D X 36.5"H
-Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.
-Color: Black or Gray
-Weight: 84 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AROSA Fire Pit Counter Height Table adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor table is made to fit naturally into the room. Crafted from Steel, Ceramic Tile, Polyrattan, Polyspun Fabric, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 36.5"W X 36.5"D X 36.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic Tile, Polyrattan, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 84 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BARBUDA Fire Pit Table, styled in Contemporary and designed for everyday comfort. As a outdoor table, it is designed to complement your space. With Steel, Polyrattan, Polyspun Fabric and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 39" DIA X 27.2"H
-Materials: Steel, Polyrattan, Polyspun Fabric.
-Color: Gray
-Weight: 103.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BARBUDA Fire Pit Table, styled in Contemporary and designed for everyday comfort. As a outdoor table, it is designed to complement your space. With Steel, Polyrattan, Polyspun Fabric and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 39" DIA X 27.2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyrattan, Polyspun Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 103.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BORDEAUX Dining Table w/ Fire Pit &amp; Cooler, styled in Contemporary and designed for everyday comfort. Built as a outdoor table, it pairs well with a wide range of interiors. With Aluminum, Stainless Steel and Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 70.5"W X 38.5"D X 29"H
-Materials: Aluminum, Stainless Steel.
-Color: Brown
-Weight: 184.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BORDEAUX Dining Table w/ Fire Pit &amp;amp; Cooler, styled in Contemporary and designed for everyday comfort. Built as a outdoor table, it pairs well with a wide range of interiors. With Aluminum, Stainless Steel and Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 70.5"W X 38.5"D X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Stainless Steel.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 184.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10483,14 +10483,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with COVE Nesting Tables (2 / CTN) and its Contemporary character. As a outdoor table, it is designed to complement your space. Finished in Natural or Black tones, the Metal, Solid Wood build balances durability with visual appeal.
-Product Dimensions: 15.5"W X 15.5"D X 15.5"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Metal, Solid Wood.
-Color: Natural or Black
-Weight: 14.55 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with COVE Nesting Tables (2 / CTN) and its Contemporary character. As a outdoor table, it is designed to complement your space. Finished in Natural or Black tones, the Metal, Solid Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 15.5"W X 15.5"D X 15.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Natural or Black&lt;br&gt;
+Weight: 14.55 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10611,12 +10611,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LOVINA Oval Dining Table and its Transitional character. As a outdoor table, it is designed to complement your space. Finished in Natural tones, the Teak Wood build balances durability with visual appeal.
-Product Dimensions: 78.5"W X 47"D X 29.5"H
-Materials: Teak Wood.
-Color: Natural
-Weight: 141 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LOVINA Oval Dining Table and its Transitional character. As a outdoor table, it is designed to complement your space. Finished in Natural tones, the Teak Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 78.5"W X 47"D X 29.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Teak Wood.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 141 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LYON Game Table, styled in Contemporary and designed for everyday comfort. Built as a outdoor table, it pairs well with a wide range of interiors. With Aluminum, Outdoor Fabric and Black or Natural or Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 50.5"DIA X 29.5"H
-Materials: Aluminum, Outdoor Fabric.
-Color: Black or Natural or Brown
-Weight: 83.33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LYON Game Table, styled in Contemporary and designed for everyday comfort. Built as a outdoor table, it pairs well with a wide range of interiors. With Aluminum, Outdoor Fabric and Black or Natural or Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 50.5"DIA X 29.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Outdoor Fabric.&lt;br&gt;
+Color: Black or Natural or Brown&lt;br&gt;
+Weight: 83.33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -10859,14 +10859,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOLLIE Nesting Tables (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor table, it pairs well with a wide range of interiors. Crafted from Metal, Solid Wood, it is finished in Natural or Black tones that pair easily with surrounding decor.
-Product Dimensions: 15.5"W X 15.5"D X 17.5"H
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Metal, Solid Wood.
-Color: Natural or Black
-Weight: 13.23 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOLLIE Nesting Tables (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor table, it pairs well with a wide range of interiors. Crafted from Metal, Solid Wood, it is finished in Natural or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 15.5"W X 15.5"D X 17.5"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Solid Wood.&lt;br&gt;
+Color: Natural or Black&lt;br&gt;
+Weight: 13.23 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -10987,11 +10987,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MONZA Adjustable Chairs (2 / CTN) and its Contemporary character. Built as a outdoor table, it pairs well with a wide range of interiors. Finished in Gun Metal or Gray tones, the Aluminum, Textilene build balances durability with visual appeal.
-Product Dimensions: 27.5"D X 23"D X 43"H
-Materials: Aluminum, Textilene.
-Color: Gun Metal or Gray</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MONZA Adjustable Chairs (2 / CTN) and its Contemporary character. Built as a outdoor table, it pairs well with a wide range of interiors. Finished in Gun Metal or Gray tones, the Aluminum, Textilene build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 27.5"D X 23"D X 43"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Textilene.&lt;br&gt;
+Color: Gun Metal or Gray&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -11109,11 +11109,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MONZA Extendable Dining Table brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor table, it is designed to complement your space. The Aluminum, Tempered Glass, Textilene construction is complemented by Gun Metal or Gray tones for a polished look.
-Product Dimensions: 63" (EXTENDED 94.5")W X 35.5"D X 29.5"H
-Materials: Aluminum, Tempered Glass, Textilene.
-Color: Gun Metal or Gray</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MONZA Extendable Dining Table brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor table, it is designed to complement your space. The Aluminum, Tempered Glass, Textilene construction is complemented by Gun Metal or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 63" (EXTENDED 94.5")W X 35.5"D X 29.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Tempered Glass, Textilene.&lt;br&gt;
+Color: Gun Metal or Gray&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PALMA Dining Table, styled in Contemporary and designed for everyday comfort. As a outdoor table, it is designed to complement your space. With Steel, Glass, Polyspun Fabric and Black or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 71"W X 35.5"D X 28"H
-Materials: Steel, Glass, Polyspun Fabric.
-Color: Black or Gray
-Weight: 62.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PALMA Dining Table, styled in Contemporary and designed for everyday comfort. As a outdoor table, it is designed to complement your space. With Steel, Glass, Polyspun Fabric and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 71"W X 35.5"D X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 62.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11352,10 +11352,10 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SARABI Patio Side Table is designed to complement your space with a balanced, versatile look. This outdoor table is made to fit naturally into the room.
-Product Dimensions: 21.5"W X 21.5"D X 15.5"H
-Weight: 11.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SARABI Patio Side Table is designed to complement your space with a balanced, versatile look. This outdoor table is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 21.5"W X 21.5"D X 15.5"H&lt;br&gt;
+Weight: 11.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -11458,9 +11458,9 @@
       </c>
       <c r="G87" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA Patio Side Table is designed to complement your space with a balanced, versatile look. This outdoor table is made to fit naturally into the room.
-Product Dimensions: 19.5"W X 19.5"D X 21"H</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA Patio Side Table is designed to complement your space with a balanced, versatile look. This outdoor table is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 19.5"W X 19.5"D X 21"H&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H87" s="52" t="inlineStr">
@@ -11566,9 +11566,9 @@
       </c>
       <c r="G88" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ZALIKA Patio Side Table is designed to complement your space with a balanced, versatile look. Built as a outdoor table, it pairs well with a wide range of interiors.
-Product Dimensions: 19.5"W X 19.5"D X 21"H</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ZALIKA Patio Side Table is designed to complement your space with a balanced, versatile look. Built as a outdoor table, it pairs well with a wide range of interiors.&lt;br&gt;
+Product Dimensions: 19.5"W X 19.5"D X 21"H&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H88" s="52" t="inlineStr">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ANTIGUA Ottoman (2 / CTN), styled in Contemporary and designed for everyday comfort. As a outdoor ottoman, it is designed to complement your space. With Aluminum, Polyethylene Wicker, Polyspun and Gun Metal or Brown or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 17 3/4"L X 17 3/4"W X 16 1/4"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gun Metal or Brown or Gray
-Weight: 17.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ANTIGUA Ottoman (2 / CTN), styled in Contemporary and designed for everyday comfort. As a outdoor ottoman, it is designed to complement your space. With Aluminum, Polyethylene Wicker, Polyspun and Gun Metal or Brown or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 17 3/4"L X 17 3/4"W X 16 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gun Metal or Brown or Gray&lt;br&gt;
+Weight: 17.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -11803,12 +11803,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MACKAY Ottoman (2 / CTN), styled in Contemporary and designed for everyday comfort. Built as a outdoor ottoman, it pairs well with a wide range of interiors. With Aluminum, FSC Certified 100% Teak Wood and Beige or Natural Teak tones, it blends structure and softness in one clean profile.
-Product Dimensions: 21 1/4"L X 21 1/4"W X 16 1/2"H
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Beige or Natural Teak
-Weight: 29.75 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MACKAY Ottoman (2 / CTN), styled in Contemporary and designed for everyday comfort. Built as a outdoor ottoman, it pairs well with a wide range of interiors. With Aluminum, FSC Certified 100% Teak Wood and Beige or Natural Teak tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 21 1/4"L X 21 1/4"W X 16 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Beige or Natural Teak&lt;br&gt;
+Weight: 29.75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ANTIGUA Sofa adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor sofa is made to fit naturally into the room. Crafted from Aluminum, Polyethylene Wicker, Polyspun, it is finished in Gun Metal or Brown or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 76 3/4"L X 34"W X 43"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gun Metal or Brown or Gray
-Weight: 75.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ANTIGUA Sofa adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor sofa is made to fit naturally into the room. Crafted from Aluminum, Polyethylene Wicker, Polyspun, it is finished in Gun Metal or Brown or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 76 3/4"L X 34"W X 43"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gun Metal or Brown or Gray&lt;br&gt;
+Weight: 75.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ARALI HXZ Pop Up Gazebo adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 132"W X 132"D X 98.5"H
-Materials: Metal, Fabric.
-Color: Gray
-Weight: 39.68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ARALI HXZ Pop Up Gazebo adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 98.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 39.68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BARBUDA 5 Pc. Sectional Sofa w/ 2 End Tables brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor patio set, it pairs well with a wide range of interiors. The Steel, Polyrattan, Polyspun Fabric construction is complemented by Gray or Natural tones for a polished look.
-Product Dimensions: Sofa: 64.25"W X 29"D X 33.5"H, End Table: 21.25"L X 28.7"W X 24"H
-Materials: Steel, Polyrattan, Polyspun Fabric.
-Color: Gray or Natural
-Weight: 219.36 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BARBUDA 5 Pc. Sectional Sofa w/ 2 End Tables brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor patio set, it pairs well with a wide range of interiors. The Steel, Polyrattan, Polyspun Fabric construction is complemented by Gray or Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: Sofa: 64.25"W X 29"D X 33.5"H, End Table: 21.25"L X 28.7"W X 24"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyrattan, Polyspun Fabric.&lt;br&gt;
+Color: Gray or Natural&lt;br&gt;
+Weight: 219.36 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="G94" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BASTIA 3 Pc. Conversation Set adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor patio set is made to fit naturally into the room. Crafted from Metal, Glass, Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: Table: 19.5"W X 19.5"D X 17.5"H, Chair: 26.5"D X 29"D X 36.5"H
-Materials: Metal, Glass, Fabric.
-Color: Beige
-Weight: 37.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BASTIA 3 Pc. Conversation Set adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor patio set is made to fit naturally into the room. Crafted from Metal, Glass, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Table: 19.5"W X 19.5"D X 17.5"H, Chair: 26.5"D X 29"D X 36.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 37.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H94" s="35" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="G95" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BASTIA 3 Pc. Conversation Set and its Contemporary character. Built as a outdoor patio set, it pairs well with a wide range of interiors. Finished in Teal tones, the Metal, Glass, Fabric build balances durability with visual appeal.
-Product Dimensions: Table: 19.5"W X 19.5"D X 17.5"H, Chair: 26.5"D X 29"D X 36.5"H
-Materials: Metal, Glass, Fabric.
-Color: Teal
-Weight: 37.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BASTIA 3 Pc. Conversation Set and its Contemporary character. Built as a outdoor patio set, it pairs well with a wide range of interiors. Finished in Teal tones, the Metal, Glass, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: Table: 19.5"W X 19.5"D X 17.5"H, Chair: 26.5"D X 29"D X 36.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 37.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H95" s="35" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CHANDU 5 Pc. Conversation Set brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio set is made to fit naturally into the room. The Metal, Glass, Fabric construction is complemented by Natural or Black tones for a polished look.
-Product Dimensions: Table: 17.5"DIA X 17"H, Chair: 28"W X 24"D X 37.5"H, Ottoman: 22"L X 18"W X 17"H
-Materials: Metal, Glass, Fabric.
-Color: Natural or Black
-Weight: 72.31 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CHANDU 5 Pc. Conversation Set brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio set is made to fit naturally into the room. The Metal, Glass, Fabric construction is complemented by Natural or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: Table: 17.5"DIA X 17"H, Chair: 28"W X 24"D X 37.5"H, Ottoman: 22"L X 18"W X 17"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Natural or Black&lt;br&gt;
+Weight: 72.31 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FARISHA 4 Pc. Outdoor Sectional Set adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor patio set is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in White tones that pair easily with surrounding decor.
-Product Dimensions: Sectional: 77"W X 77"D X 26"H, Table: 15.5"W X 15.5"D X 23.5"H, Chair: 49"W X 27.5"D X 26"H
-Materials: Metal, Fabric.
-Color: White
-Weight: 143.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FARISHA 4 Pc. Outdoor Sectional Set adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor patio set is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Sectional: 77"W X 77"D X 26"H, Table: 15.5"W X 15.5"D X 23.5"H, Chair: 49"W X 27.5"D X 26"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 143.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GENOA Pop Up Gazebo 12' X12' and its Contemporary character. Built as a outdoor patio set, it pairs well with a wide range of interiors. Finished in Brown tones, the Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 143.5"W X 143.5"D X 98.5"H
-Materials: Metal, Fabric.
-Color: Brown
-Weight: 37.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GENOA Pop Up Gazebo 12' X12' and its Contemporary character. Built as a outdoor patio set, it pairs well with a wide range of interiors. Finished in Brown tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 143.5"W X 143.5"D X 98.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 37.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -12949,12 +12949,12 @@
       </c>
       <c r="G99" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HANA 4 Pc. Patio Set and its Rustic character. This outdoor patio set is made to fit naturally into the room. Finished in Denim Blue or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.
-Product Dimensions: TABLE: 29 1/2"L X 19 3/4"W X 13"H, LOVESEAT: 47 1/2"L X 24"W X 32"H, CHAIR: 23 3/4"W X 24"D X 32"H
-Materials: Acacia Wood, Polyester.
-Color: Denim Blue or Natural
-Weight: 85.98 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HANA 4 Pc. Patio Set and its Rustic character. This outdoor patio set is made to fit naturally into the room. Finished in Denim Blue or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: TABLE: 29 1/2"L X 19 3/4"W X 13"H, LOVESEAT: 47 1/2"L X 24"W X 32"H, CHAIR: 23 3/4"W X 24"D X 32"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Denim Blue or Natural&lt;br&gt;
+Weight: 85.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" s="62" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="G100" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HANA 4 Pc. Patio Set brings a Rustic look to your home with a refined, comfortable feel. Built as a outdoor patio set, it pairs well with a wide range of interiors. The Acacia Wood, Polyester construction is complemented by Brown or Natural tones for a polished look.
-Product Dimensions: TABLE: 29 1/2"L X 19 3/4"W X 13"H, LOVESEAT: 47 1/2"L X 24"W X 32"H, CHAIR: 23 3/4"W X 24"D X 32"H
-Materials: Acacia Wood, Polyester.
-Color: Brown or Natural
-Weight: 85.98 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HANA 4 Pc. Patio Set brings a Rustic look to your home with a refined, comfortable feel. Built as a outdoor patio set, it pairs well with a wide range of interiors. The Acacia Wood, Polyester construction is complemented by Brown or Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: TABLE: 29 1/2"L X 19 3/4"W X 13"H, LOVESEAT: 47 1/2"L X 24"W X 32"H, CHAIR: 23 3/4"W X 24"D X 32"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Brown or Natural&lt;br&gt;
+Weight: 85.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" s="62" t="inlineStr">
@@ -13207,12 +13207,12 @@
       </c>
       <c r="G101" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-IBIZA 4 Pc. Sling Set adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Glass, Fabric, it is finished in Green tones that pair easily with surrounding decor.
-Product Dimensions: Table: 33"W X 19"D X 15.5"H, Bench: 42"W X 24.5"D X 30.5"H, Chair: 24.5"W X 23.5"D X 30.5"H
-Materials: Metal, Glass, Fabric.
-Color: Green
-Weight: 66.13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+IBIZA 4 Pc. Sling Set adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Glass, Fabric, it is finished in Green tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Table: 33"W X 19"D X 15.5"H, Bench: 42"W X 24.5"D X 30.5"H, Chair: 24.5"W X 23.5"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Green&lt;br&gt;
+Weight: 66.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="56" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="G102" s="56" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with IBIZA 4 Pc. Sling Set and its Contemporary character. This outdoor patio set is made to fit naturally into the room. Finished in Light Brown tones, the Metal, Glass, Fabric build balances durability with visual appeal.
-Product Dimensions: Table: 33"W X 19"D X 15.5"H, Bench: 42"W X 24.5"D X 30.5"H, Chair: 24.5"W X 23.5"D X 30.5"H
-Materials: Metal, Glass, Fabric.
-Color: Light Brown
-Weight: 66.13 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with IBIZA 4 Pc. Sling Set and its Contemporary character. This outdoor patio set is made to fit naturally into the room. Finished in Light Brown tones, the Metal, Glass, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: Table: 33"W X 19"D X 15.5"H, Bench: 42"W X 24.5"D X 30.5"H, Chair: 24.5"W X 23.5"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Light Brown&lt;br&gt;
+Weight: 66.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" s="56" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="G103" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with KIMARA Dining Table, styled in Contemporary and designed for everyday comfort. This outdoor patio set is made to fit naturally into the room. With Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and Black or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 56.7"L X 29.13"W X 26.77"H
-Materials: Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Black or Gray
-Weight: 30.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with KIMARA Dining Table, styled in Contemporary and designed for everyday comfort. This outdoor patio set is made to fit naturally into the room. With Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 56.7"L X 29.13"W X 26.77"H&lt;/p&gt;
+&lt;p&gt;Materials: Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 30.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="29" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="G104" s="29" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KIMARA Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor patio set, it pairs well with a wide range of interiors. Crafted from Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 56.7"L X 29.13"W X 26.77"H
-Materials: Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.
-Color: Black or Gray
-Weight: 33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KIMARA Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor patio set, it pairs well with a wide range of interiors. Crafted from Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 56.7"L X 29.13"W X 26.77"H&lt;/p&gt;
+&lt;p&gt;Materials: Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="29" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOTUS Sofa &amp; Coffee Table Set brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio set is made to fit naturally into the room. The Aluminum, Fabric construction is complemented by Black or Light Brown tones for a polished look.
-Product Dimensions: Sofa: 74"W X 29.5"D X 34"H, Table: 47"W X 25.5"D X 15.5"H
-Materials: Aluminum, Fabric.
-Color: Black or Light Brown
-Weight: 33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOTUS Sofa &amp;amp; Coffee Table Set brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio set is made to fit naturally into the room. The Aluminum, Fabric construction is complemented by Black or Light Brown tones for a polished look.&lt;br&gt;
+Product Dimensions: Sofa: 74"W X 29.5"D X 34"H, Table: 47"W X 25.5"D X 15.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Fabric.&lt;br&gt;
+Color: Black or Light Brown&lt;br&gt;
+Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -13856,12 +13856,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MYESHA 4 Pc. Conversation Set adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Glass, Fabric, it is finished in Dark Gray or Light Gray tones that pair easily with surrounding decor.
-Product Dimensions: TABLE: 39"W X 23.5"D X 14"H, BENCH: 60"W X 28"D X 28"H, Chair: 26.5"W X 28"D X 28"H
-Materials: Metal, Glass, Fabric.
-Color: Dark Gray or Light Gray
-Weight: 56 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MYESHA 4 Pc. Conversation Set adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Glass, Fabric, it is finished in Dark Gray or Light Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: TABLE: 39"W X 23.5"D X 14"H, BENCH: 60"W X 28"D X 28"H, Chair: 26.5"W X 28"D X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Dark Gray or Light Gray&lt;br&gt;
+Weight: 56 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NOTO 3 Pc. Patio Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Acacia Wood, Polyester, it is finished in Natural or Black tones that pair easily with surrounding decor.
-Product Dimensions: TABLE: 19 1/2"L X 19 1/2"W X 15 1/2"H, CHAIR: 24 1/2"W X 24 1/2"D X 31 1/2"H
-Materials: Acacia Wood, Polyester.
-Color: Natural or Black
-Weight: 57.32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NOTO 3 Pc. Patio Set adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Acacia Wood, Polyester, it is finished in Natural or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: TABLE: 19 1/2"L X 19 1/2"W X 15 1/2"H, CHAIR: 24 1/2"W X 24 1/2"D X 31 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Natural or Black&lt;br&gt;
+Weight: 57.32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -14108,12 +14108,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PALMA 4 Pc. Conversation Set and its Contemporary character. This outdoor patio set is made to fit naturally into the room. Finished in Black or Gray tones, the Steel, Glass, Polyspun Fabric build balances durability with visual appeal.
-Product Dimensions: Table: 38"W X 22"D X 18.5"H, Loveseat: 48"W X 30.5"D X 29"H, Chair: 26"W X 30.5"D X 29"H
-Materials: Steel, Glass, Polyspun Fabric.
-Color: Black or Gray
-Weight: 97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PALMA 4 Pc. Conversation Set and its Contemporary character. This outdoor patio set is made to fit naturally into the room. Finished in Black or Gray tones, the Steel, Glass, Polyspun Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: Table: 38"W X 22"D X 18.5"H, Loveseat: 48"W X 30.5"D X 29"H, Chair: 26"W X 30.5"D X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Glass, Polyspun Fabric.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -14234,12 +14234,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SHANI 3 Pc. Conversation Set and its Contemporary character. As a outdoor patio set, it is designed to complement your space. Finished in Light Gray or Black tones, the Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: Table: 17.5"DIA X 21.5"H, Chair: 23"W X 25.5"D X 30.5"H
-Materials: Metal, Fabric.
-Color: Light Gray or Black
-Weight: 72.16 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SHANI 3 Pc. Conversation Set and its Contemporary character. As a outdoor patio set, it is designed to complement your space. Finished in Light Gray or Black tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: Table: 17.5"DIA X 21.5"H, Chair: 23"W X 25.5"D X 30.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Light Gray or Black&lt;br&gt;
+Weight: 72.16 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -14365,12 +14365,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SHOMARI 4 Pc. Wicker Sofa Set brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio set is made to fit naturally into the room. The Metal, Fabric construction is complemented by White tones for a polished look.
-Product Dimensions: Table: 39.5"W X 19.5"D X 15.5"H, Bench: 55"W X 29.5"D X 27.5"H, Chair: 31.5"W X 29.5"D X 27.5"H
-Materials: Metal, Fabric.
-Color: White
-Weight: 103.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SHOMARI 4 Pc. Wicker Sofa Set brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio set is made to fit naturally into the room. The Metal, Fabric construction is complemented by White tones for a polished look.&lt;br&gt;
+Product Dimensions: Table: 39.5"W X 19.5"D X 15.5"H, Bench: 55"W X 29.5"D X 27.5"H, Chair: 31.5"W X 29.5"D X 27.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: White&lt;br&gt;
+Weight: 103.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -14491,12 +14491,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TUSHARI 7 Pc. Outdoor Dining Set, styled in Contemporary and designed for everyday comfort. As a outdoor patio set, it is designed to complement your space. With Metal, Glass, Fabric and Dark Gray or Light Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: Table: 39.5"W X 19.5"D X 15.5"H, Bench: 55"W X 29.5"D X 27.5"H, Chair: 31.5"W X 29.5"D X 27.5"H
-Materials: Metal, Glass, Fabric.
-Color: Dark Gray or Light Gray
-Weight: 121.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TUSHARI 7 Pc. Outdoor Dining Set, styled in Contemporary and designed for everyday comfort. As a outdoor patio set, it is designed to complement your space. With Metal, Glass, Fabric and Dark Gray or Light Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: Table: 39.5"W X 19.5"D X 15.5"H, Bench: 55"W X 29.5"D X 27.5"H, Chair: 31.5"W X 29.5"D X 27.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
+Color: Dark Gray or Light Gray&lt;br&gt;
+Weight: 121.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -14613,12 +14613,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-AREZZO 4 Pc. Outdoor Conversation Set brings a Transitional look to your home with a refined, comfortable feel. Built as a outdoor dining set, it pairs well with a wide range of interiors. The Metal, Fabric construction is complemented by Beige tones for a polished look.
-Product Dimensions: Table: 36"W X 23.5"D X 19"H, Bench: 44"W X 24"D X 35"H, Chair: 23"W X 24"D X 35"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 110 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+AREZZO 4 Pc. Outdoor Conversation Set brings a Transitional look to your home with a refined, comfortable feel. Built as a outdoor dining set, it pairs well with a wide range of interiors. The Metal, Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: Table: 36"W X 23.5"D X 19"H, Bench: 44"W X 24"D X 35"H, Chair: 23"W X 24"D X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 110 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -14739,12 +14739,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FALLONE 6 Pc. Outdoor Dining Set adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor dining set, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: Table: 30"W X 30"D X 29"H, Chair: 19"W X 26.5"D X 35.5"H, Umbrella: 76"W X 76"D X 86"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 78 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FALLONE 6 Pc. Outdoor Dining Set adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor dining set, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Table: 30"W X 30"D X 29"H, Chair: 19"W X 26.5"D X 35.5"H, Umbrella: 76"W X 76"D X 86"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 78 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -14865,14 +14865,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MARSHA 3 Pc. Outdoor Set and its Contemporary character. As a outdoor dining set, it is designed to complement your space. Finished in Gray or Green or Oak tones, the Fabric, Aluminum, Solid wood build balances durability with visual appeal.
-Product Dimensions: TABLE: 36"L X 19 5/8"W X 17 3/4"H, CHAIR: 28"L X 32 5/8"W X 33"H (SEAT HT: 18 1/4", SEAT DP: 21")
-Features
-- Made with solid wood &amp; wood veneer
-Materials: Fabric, Aluminum, Solid wood.
-Color: Gray or Green or Oak
-Weight: 70.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MARSHA 3 Pc. Outdoor Set and its Contemporary character. As a outdoor dining set, it is designed to complement your space. Finished in Gray or Green or Oak tones, the Fabric, Aluminum, Solid wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: TABLE: 36"L X 19 5/8"W X 17 3/4"H, CHAIR: 28"L X 32 5/8"W X 33"H (SEAT HT: 18 1/4", SEAT DP: 21")&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Aluminum, Solid wood.&lt;br&gt;
+Color: Gray or Green or Oak&lt;br&gt;
+Weight: 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -14994,12 +14994,12 @@
       </c>
       <c r="G115" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Blue
-Weight: 105.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H115" s="62" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="G116" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO 5 Pc. Outdoor Dining Set brings a Transitional look to your home with a refined, comfortable feel. This outdoor dining set is made to fit naturally into the room. The Glass, Metal, Fabric construction is complemented by Red tones for a polished look.
-Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Red
-Weight: 105.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO 5 Pc. Outdoor Dining Set brings a Transitional look to your home with a refined, comfortable feel. This outdoor dining set is made to fit naturally into the room. The Glass, Metal, Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H116" s="62" t="inlineStr">
@@ -15248,12 +15248,12 @@
       </c>
       <c r="G117" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with PIERRO 5 Pc. Outdoor Dining Set, styled in Transitional and designed for everyday comfort. Built as a outdoor dining set, it pairs well with a wide range of interiors. With Glass, Metal, Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Red
-Weight: 105.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with PIERRO 5 Pc. Outdoor Dining Set, styled in Transitional and designed for everyday comfort. Built as a outdoor dining set, it pairs well with a wide range of interiors. With Glass, Metal, Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H117" s="62" t="inlineStr">
@@ -15375,12 +15375,12 @@
       </c>
       <c r="G118" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-PIERRO 5 Pc. Outdoor Dining Set adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor dining set, it is designed to complement your space. Crafted from Glass, Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Beige
-Weight: 105.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+PIERRO 5 Pc. Outdoor Dining Set adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor dining set, it is designed to complement your space. Crafted from Glass, Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H118" s="62" t="inlineStr">
@@ -15502,12 +15502,12 @@
       </c>
       <c r="G119" s="62" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. This outdoor dining set is made to fit naturally into the room. Finished in Beige tones, the Glass, Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H
-Materials: Glass, Metal, Fabric.
-Color: Beige
-Weight: 105.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. This outdoor dining set is made to fit naturally into the room. Finished in Beige tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H119" s="62" t="inlineStr">
@@ -15628,12 +15628,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with AROSA Outdoor Pop-Up Canopy 10' X 10' and its Transitional character. Built as a outdoor canopy, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 136"W X 136"D X 112"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with AROSA Outdoor Pop-Up Canopy 10' X 10' and its Transitional character. Built as a outdoor canopy, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 136"W X 136"D X 112"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GORDOLA Outdoor Canopy 13' X 10' adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor canopy, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Brown tones that pair easily with surrounding decor.
-Product Dimensions: 121"W X 161"D X 120"H
-Materials: Metal, Fabric.
-Color: Brown
-Weight: 106 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GORDOLA Outdoor Canopy 13' X 10' adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor canopy, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Brown tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 121"W X 161"D X 120"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Brown&lt;br&gt;
+Weight: 106 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NESTA Outdoor Pop-Up Canopy 6' X 6', styled in Transitional and designed for everyday comfort. This outdoor canopy is made to fit naturally into the room. With Metal, Fabric and Burgundy tones, it blends structure and softness in one clean profile.
-Product Dimensions: 87"W X 89"D X 83"H
-Materials: Metal, Fabric.
-Color: Burgundy
-Weight: 22 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NESTA Outdoor Pop-Up Canopy 6' X 6', styled in Transitional and designed for everyday comfort. This outdoor canopy is made to fit naturally into the room. With Metal, Fabric and Burgundy tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 87"W X 89"D X 83"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Burgundy&lt;br&gt;
+Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -16007,12 +16007,12 @@
       </c>
       <c r="G123" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BAHIA TOBAGO Reclining Chaise Lounge adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chaise is made to fit naturally into the room. Crafted from Steel, FSC Certified 100% Teak Wood, Polyspun, it is finished in Brown or Dark Gray tones that pair easily with surrounding decor.
-Product Dimensions: LOVESEAT: 46"L X 36 1/2"W X 29"H, BENCH: 39 1/2"W X 11 3/4"D X 22"H
-Materials: Steel, FSC Certified 100% Teak Wood, Polyspun.
-Color: Brown or Dark Gray
-Weight: 97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BAHIA TOBAGO Reclining Chaise Lounge adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chaise is made to fit naturally into the room. Crafted from Steel, FSC Certified 100% Teak Wood, Polyspun, it is finished in Brown or Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: LOVESEAT: 46"L X 36 1/2"W X 29"H, BENCH: 39 1/2"W X 11 3/4"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, FSC Certified 100% Teak Wood, Polyspun.&lt;br&gt;
+Color: Brown or Dark Gray&lt;br&gt;
+Weight: 97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H123" s="50" t="inlineStr">
@@ -16136,12 +16136,12 @@
       </c>
       <c r="G124" s="50" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BAHIA TOBAGO Reclining Chaise Lounge and its Contemporary character. Built as a outdoor chaise, it pairs well with a wide range of interiors. Finished in Gray tones, the Steel, FSC Certified 100% Teak Wood, Polyspun build balances durability with visual appeal.
-Product Dimensions: LOVESEAT: 46"L X 36 1/2"W X 29"H, BENCH: 39 1/2"W X 11 3/4"D X 22"H
-Materials: Steel, FSC Certified 100% Teak Wood, Polyspun.
-Color: Gray
-Weight: 97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BAHIA TOBAGO Reclining Chaise Lounge and its Contemporary character. Built as a outdoor chaise, it pairs well with a wide range of interiors. Finished in Gray tones, the Steel, FSC Certified 100% Teak Wood, Polyspun build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: LOVESEAT: 46"L X 36 1/2"W X 29"H, BENCH: 39 1/2"W X 11 3/4"D X 22"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, FSC Certified 100% Teak Wood, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H124" s="50" t="inlineStr">
@@ -16269,13 +16269,13 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-BOYLE Dust Cover for Chair brings a Transitional look to your home with a refined, comfortable feel. As a outdoor accessory, it is designed to complement your space. The Waterproof Polyester Canvas construction is complemented by Light Brown tones for a polished look.
-Product Dimensions: 32 5/8"L X 36"W X 29 1/8"H
-Size: Small
-Materials: Waterproof Polyester Canvas.
-Color: Light Brown
-Weight: 31.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+BOYLE Dust Cover for Chair brings a Transitional look to your home with a refined, comfortable feel. As a outdoor accessory, it is designed to complement your space. The Waterproof Polyester Canvas construction is complemented by Light Brown tones for a polished look.&lt;br&gt;
+Product Dimensions: 32 5/8"L X 36"W X 29 1/8"H&lt;br&gt;
+Size: Small&lt;/p&gt;
+&lt;p&gt;Materials: Waterproof Polyester Canvas.&lt;br&gt;
+Color: Light Brown&lt;br&gt;
+Weight: 31.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -16401,13 +16401,13 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with BOYLE Dust Cover for Sofa, styled in Transitional and designed for everyday comfort. This outdoor accessory is made to fit naturally into the room. With Waterproof Polyester Canvas and Light Brown tones, it blends structure and softness in one clean profile.
-Product Dimensions: 82"W X 36"D X 29 1/8"H
-Size: Small
-Materials: Waterproof Polyester Canvas.
-Color: Light Brown
-Weight: 57.2 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with BOYLE Dust Cover for Sofa, styled in Transitional and designed for everyday comfort. This outdoor accessory is made to fit naturally into the room. With Waterproof Polyester Canvas and Light Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 82"W X 36"D X 29 1/8"H&lt;br&gt;
+Size: Small&lt;/p&gt;
+&lt;p&gt;Materials: Waterproof Polyester Canvas.&lt;br&gt;
+Color: Light Brown&lt;br&gt;
+Weight: 57.2 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -16528,12 +16528,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with BRINDSMADE 6 Pc. Patio Set w/ Coffee Table and 2 End Tables and its Contemporary character. This outdoor sofa set is made to fit naturally into the room. Finished in Gray or Light Brrown tones, the Aluminum, Polyester Canvas, Faux Rattan, Tempered Glass build balances durability with visual appeal.
-Product Dimensions: SOFAS: 85 7/8"L X 33 7/8"W X 35"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan, Tempered Glass.
-Color: Gray or Light Brrown
-Weight: 238.4 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with BRINDSMADE 6 Pc. Patio Set w/ Coffee Table and 2 End Tables and its Contemporary character. This outdoor sofa set is made to fit naturally into the room. Finished in Gray or Light Brrown tones, the Aluminum, Polyester Canvas, Faux Rattan, Tempered Glass build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: SOFAS: 85 7/8"L X 33 7/8"W X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan, Tempered Glass.&lt;br&gt;
+Color: Gray or Light Brrown&lt;br&gt;
+Weight: 238.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ILONA Armless Chair brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor sofa set, it is designed to complement your space. The Aluminum, Polyester Canvas, Faux Rattan construction is complemented by Brown or Beige tones for a polished look.
-Product Dimensions: 24 1/4"W X 27 1/2"D X 25 1/2 - 31"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ILONA Armless Chair brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor sofa set, it is designed to complement your space. The Aluminum, Polyester Canvas, Faux Rattan construction is complemented by Brown or Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 24 1/4"W X 27 1/2"D X 25 1/2 - 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ILONA Coffee Table, styled in Contemporary and designed for everyday comfort. This outdoor sofa set is made to fit naturally into the room. With Aluminum, Polyester Canvas, Faux Rattan and Brown or Beige tones, it blends structure and softness in one clean profile.
-Product Dimensions: 34 5/8"L X 19 1/4"W X 13 3/4"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 26.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ILONA Coffee Table, styled in Contemporary and designed for everyday comfort. This outdoor sofa set is made to fit naturally into the room. With Aluminum, Polyester Canvas, Faux Rattan and Brown or Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 34 5/8"L X 19 1/4"W X 13 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 26.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ILONA Corner adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor sofa set, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Canvas, Faux Rattan, it is finished in Brown or Beige tones that pair easily with surrounding decor.
-Product Dimensions: 27 1/2"W X 27 1/2"D X 31"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 33 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ILONA Corner adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor sofa set, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Canvas, Faux Rattan, it is finished in Brown or Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 27 1/2"W X 27 1/2"D X 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with ILONA End Table and its Contemporary character. As a outdoor sofa set, it is designed to complement your space. Finished in Brown or Beige tones, the Aluminum, Polyester Canvas, Faux Rattan build balances durability with visual appeal.
-Product Dimensions: 17 3/4"L X 17 3/4"W X 19 5/8"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 17 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with ILONA End Table and its Contemporary character. As a outdoor sofa set, it is designed to complement your space. Finished in Brown or Beige tones, the Aluminum, Polyester Canvas, Faux Rattan build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 17 3/4"L X 17 3/4"W X 19 5/8"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 17 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -17154,12 +17154,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-ILONA Left Arm Chair brings a Contemporary look to your home with a refined, comfortable feel. This outdoor sofa set is made to fit naturally into the room. The Aluminum, Polyester Canvas, Faux Rattan construction is complemented by Brown or Beige tones for a polished look.
-Product Dimensions: 27 1/2"W X 27 1/2"D X 31"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 32 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+ILONA Left Arm Chair brings a Contemporary look to your home with a refined, comfortable feel. This outdoor sofa set is made to fit naturally into the room. The Aluminum, Polyester Canvas, Faux Rattan construction is complemented by Brown or Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 27 1/2"W X 27 1/2"D X 31"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 32 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ILONA Ottoman, styled in Contemporary and designed for everyday comfort. Built as a outdoor sofa set, it pairs well with a wide range of interiors. With Aluminum, Polyester Canvas, Faux Rattan and Brown or Beige tones, it blends structure and softness in one clean profile.
-Product Dimensions: 27 3/4"W X 27 1/4"D X 18"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 20.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ILONA Ottoman, styled in Contemporary and designed for everyday comfort. Built as a outdoor sofa set, it pairs well with a wide range of interiors. With Aluminum, Polyester Canvas, Faux Rattan and Brown or Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 27 3/4"W X 27 1/4"D X 18"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 20.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -17406,12 +17406,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-CYPRUS Round Bar Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor bar table set, it pairs well with a wide range of interiors. The Aluminum, Polyethylene Wicker, Polyspun construction is complemented by Gray tones for a polished look.
-Product Dimensions: 46"DIA X 39 1/2"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gray
-Weight: 77.25 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+CYPRUS Round Bar Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor bar table set, it pairs well with a wide range of interiors. The Aluminum, Polyethylene Wicker, Polyspun construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 46"DIA X 39 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 77.25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -17528,12 +17528,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-DAVINA 3 Pc. Patio Set Storage adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor sectional is made to fit naturally into the room. Crafted from Aluminum, Polyester Canvas, Faux Rattan, it is finished in Brown or Beige tones that pair easily with surrounding decor.
-Product Dimensions: SECTIONAL: 104 1/4"L X 80 5/8"W X 30 3/4"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 172 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+DAVINA 3 Pc. Patio Set Storage adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor sectional is made to fit naturally into the room. Crafted from Aluminum, Polyester Canvas, Faux Rattan, it is finished in Brown or Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: SECTIONAL: 104 1/4"L X 80 5/8"W X 30 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 172 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with DAVINA Patio 3 Pc. Set Storage and its Contemporary character. Built as a outdoor sectional, it pairs well with a wide range of interiors. Finished in Brown or Beige tones, the Aluminum, Polyester Canvas, Faux Rattan build balances durability with visual appeal.
-Product Dimensions: SECTIONAL: 104 1/4"L X 80 5/8"W X 30 3/4"H
-Materials: Aluminum, Polyester Canvas, Faux Rattan.
-Color: Brown or Beige
-Weight: 139 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with DAVINA Patio 3 Pc. Set Storage and its Contemporary character. Built as a outdoor sectional, it pairs well with a wide range of interiors. Finished in Brown or Beige tones, the Aluminum, Polyester Canvas, Faux Rattan build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: SECTIONAL: 104 1/4"L X 80 5/8"W X 30 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas, Faux Rattan.&lt;br&gt;
+Color: Brown or Beige&lt;br&gt;
+Weight: 139 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -17772,12 +17772,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SAMARA Modular Sectional adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor sectional is made to fit naturally into the room. Crafted from Aluminum, FSC Certified 100% Teak Wood, Polyspun, it is finished in Gun Metal or Natural or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 2-SEATER W/ ATTACHED TABLE: 82 3/4"L X 27 1/2"W X 30 3/4"H, TABLE: 27 1/2"L X 12"W X 15"H, SECTIONAL: 110 1/4"L X 82 3/4"W X 30 3/4"H
-Materials: Aluminum, FSC Certified 100% Teak Wood, Polyspun.
-Color: Gun Metal or Natural or Gray
-Weight: 104.72 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SAMARA Modular Sectional adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor sectional is made to fit naturally into the room. Crafted from Aluminum, FSC Certified 100% Teak Wood, Polyspun, it is finished in Gun Metal or Natural or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 2-SEATER W/ ATTACHED TABLE: 82 3/4"L X 27 1/2"W X 30 3/4"H, TABLE: 27 1/2"L X 12"W X 15"H, SECTIONAL: 110 1/4"L X 82 3/4"W X 30 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood, Polyspun.&lt;br&gt;
+Color: Gun Metal or Natural or Gray&lt;br&gt;
+Weight: 104.72 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -17898,12 +17898,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SAN JOSE Modular Sectional, styled in Contemporary and designed for everyday comfort. This outdoor sectional is made to fit naturally into the room. With Aluminum, FSC Certified 100% Teak Wood, Polyspun and Gun Metal or Natural or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 2-SEATER W/ ATTACHED TABLE: 82 3/4"L X 28"W X 30 3/4"H, TABLE: 55"L X 27 1/2"W X 17 3/4 - 22 3/4"H, SECTIONAL: 110 3/4"L X 82 3/4"W X 30 3/4"H
-Materials: Aluminum, FSC Certified 100% Teak Wood, Polyspun.
-Color: Gun Metal or Natural or Gray
-Weight: 165.35 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SAN JOSE Modular Sectional, styled in Contemporary and designed for everyday comfort. This outdoor sectional is made to fit naturally into the room. With Aluminum, FSC Certified 100% Teak Wood, Polyspun and Gun Metal or Natural or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 2-SEATER W/ ATTACHED TABLE: 82 3/4"L X 28"W X 30 3/4"H, TABLE: 55"L X 27 1/2"W X 17 3/4 - 22 3/4"H, SECTIONAL: 110 3/4"L X 82 3/4"W X 30 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood, Polyspun.&lt;br&gt;
+Color: Gun Metal or Natural or Gray&lt;br&gt;
+Weight: 165.35 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WINONA Patio Sectional w/ Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor sectional, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Canvas, it is finished in White or Oak or Blue tones that pair easily with surrounding decor.
-Product Dimensions: 97 3/4"L X 97 3/4"W X 11 3/4"H
-Materials: Aluminum, Polyester Canvas.
-Color: White or Oak or Blue
-Weight: 121 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WINONA Patio Sectional w/ Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor sectional, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Canvas, it is finished in White or Oak or Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 97 3/4"L X 97 3/4"W X 11 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Canvas.&lt;br&gt;
+Color: White or Oak or Blue&lt;br&gt;
+Weight: 121 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -18151,12 +18151,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with DURO Round Umbrella Base, styled in Contemporary and designed for everyday comfort. This outdoor umbrella base is made to fit naturally into the room. With Resin, Metal and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 21"DIA X 14"H
-Materials: Resin, Metal.
-Color: Black
-Weight: 49 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with DURO Round Umbrella Base, styled in Contemporary and designed for everyday comfort. This outdoor umbrella base is made to fit naturally into the room. With Resin, Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 21"DIA X 14"H&lt;/p&gt;
+&lt;p&gt;Materials: Resin, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 49 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -18278,12 +18278,12 @@
       </c>
       <c r="G141" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FAB Round Umbrella Base and its Contemporary character. Built as a outdoor umbrella base, it pairs well with a wide range of interiors. Finished in Black tones, the Plastic or High Density Polyethelene (HDPE) build balances durability with visual appeal.
-Product Dimensions: 17 3/4"DIA X 6 1/4"H
-Materials: Plastic or High Density Polyethelene (HDPE).
-Color: Black
-Weight: 5.95 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FAB Round Umbrella Base and its Contemporary character. Built as a outdoor umbrella base, it pairs well with a wide range of interiors. Finished in Black tones, the Plastic or High Density Polyethelene (HDPE) build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 17 3/4"DIA X 6 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Plastic or High Density Polyethelene (HDPE).&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 5.95 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" s="65" t="inlineStr">
@@ -18407,12 +18407,12 @@
       </c>
       <c r="G142" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FAB Round Umbrella Base brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella base, it is designed to complement your space. The Plastic or High Density Polyethelene (HDPE) construction is complemented by Black tones for a polished look.
-Product Dimensions: 17 3/4"DIA X 6 1/4"H
-Materials: Plastic or High Density Polyethelene (HDPE).
-Color: Black
-Weight: 6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FAB Round Umbrella Base brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella base, it is designed to complement your space. The Plastic or High Density Polyethelene (HDPE) construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 17 3/4"DIA X 6 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Plastic or High Density Polyethelene (HDPE).&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="65" t="inlineStr">
@@ -18535,12 +18535,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SAYA Base For 360 Degree Rotating Umbrella and its Contemporary character. This outdoor umbrella base is made to fit naturally into the room. Finished in Black tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 37.5"W X 37.5"D X 7.5"H
-Materials: Aluminum, Polyester Fabric.
-Color: Black
-Weight: 15.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SAYA Base For 360 Degree Rotating Umbrella and its Contemporary character. This outdoor umbrella base is made to fit naturally into the room. Finished in Black tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 37.5"W X 37.5"D X 7.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 15.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -18661,12 +18661,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TANGRAM Umbrella Base w/ Handle, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella base, it pairs well with a wide range of interiors. With Plastic or High Density Polyethelene (HDPE) and Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 19 3/4"L X 19 3/4"W X 3"H
-Materials: Plastic or High Density Polyethelene (HDPE).
-Color: Black
-Weight: 20.3 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TANGRAM Umbrella Base w/ Handle, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella base, it pairs well with a wide range of interiors. With Plastic or High Density Polyethelene (HDPE) and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 19 3/4"L X 19 3/4"W X 3"H&lt;/p&gt;
+&lt;p&gt;Materials: Plastic or High Density Polyethelene (HDPE).&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 20.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -18792,13 +18792,13 @@
       </c>
       <c r="G145" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 48.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 48.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="38" t="inlineStr">
@@ -18930,13 +18930,13 @@
       </c>
       <c r="G146" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Beige tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 64.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="38" t="inlineStr">
@@ -19066,13 +19066,13 @@
       </c>
       <c r="G147" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FERA 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 48.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FERA 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 48.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="38" t="inlineStr">
@@ -19204,13 +19204,13 @@
       </c>
       <c r="G148" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FERA 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Blue tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 64.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FERA 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Blue tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -19340,13 +19340,13 @@
       </c>
       <c r="G149" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 48.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 48.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -19474,13 +19474,13 @@
       </c>
       <c r="G150" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 64.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -19610,13 +19610,13 @@
       </c>
       <c r="G151" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FERA 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 48.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FERA 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 48.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -19744,13 +19744,13 @@
       </c>
       <c r="G152" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FERA 10' Round Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Red tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 64.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FERA 10' Round Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Red tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -19880,13 +19880,13 @@
       </c>
       <c r="G153" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 48.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 48.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -20014,13 +20014,13 @@
       </c>
       <c r="G154" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Teal tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Bulb
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 64.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Bulb&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -20150,13 +20150,13 @@
       </c>
       <c r="G155" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" s="67" t="inlineStr">
@@ -20288,13 +20288,13 @@
       </c>
       <c r="G156" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" s="67" t="inlineStr">
@@ -20424,13 +20424,13 @@
       </c>
       <c r="G157" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FIDA 8' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Blue tones for a polished look.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FIDA 8' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H157" s="67" t="inlineStr">
@@ -20562,13 +20562,13 @@
       </c>
       <c r="G158" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FIDA 8' Square Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FIDA 8' Square Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" s="67" t="inlineStr">
@@ -20698,13 +20698,13 @@
       </c>
       <c r="G159" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="67" t="inlineStr">
@@ -20832,13 +20832,13 @@
       </c>
       <c r="G160" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" s="67" t="inlineStr">
@@ -20968,13 +20968,13 @@
       </c>
       <c r="G161" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FIDA 8' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Red tones for a polished look.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FIDA 8' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" s="67" t="inlineStr">
@@ -21102,13 +21102,13 @@
       </c>
       <c r="G162" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with FIDA 8' Square Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with FIDA 8' Square Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H162" s="67" t="inlineStr">
@@ -21238,13 +21238,13 @@
       </c>
       <c r="G163" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Teal tones that pair easily with surrounding decor.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Teal tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" s="67" t="inlineStr">
@@ -21372,13 +21372,13 @@
       </c>
       <c r="G164" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" s="67" t="inlineStr">
@@ -21503,12 +21503,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with GLAM Cantilever Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue or White or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"DIA X 98.5"H
-Materials: Metal, Fabric.
-Color: Blue or White or Black
-Weight: 24.47 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with GLAM Cantilever Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue or White or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"DIA X 98.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue or White or Black&lt;br&gt;
+Weight: 24.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -21635,12 +21635,12 @@
       </c>
       <c r="G166" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.
-Product Dimensions: 118"DIA X 98 1/2"H
-Materials: Steel, Polyester.
-Color: Black or White
-Weight: 24.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H166" s="46" t="inlineStr">
@@ -21764,12 +21764,12 @@
       </c>
       <c r="G167" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with GLAM Cantilever Umbrella w/ LED and its Modern character. This outdoor umbrella is made to fit naturally into the room. Finished in Canvas Stone tones, the Steel, Polyester build balances durability with visual appeal.
-Product Dimensions: 118"DIA X 98 1/2"H
-Materials: Steel, Polyester.
-Color: Canvas Stone
-Weight: 24.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with GLAM Cantilever Umbrella w/ LED and its Modern character. This outdoor umbrella is made to fit naturally into the room. Finished in Canvas Stone tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Canvas Stone&lt;br&gt;
+Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H167" s="46" t="inlineStr">
@@ -21893,12 +21893,12 @@
       </c>
       <c r="G168" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GLAM Cantilever Umbrella w/ LED brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Steel, Polyester construction is complemented by Dark Sapphire tones for a polished look.
-Product Dimensions: 118"DIA X 98 1/2"H
-Materials: Steel, Polyester.
-Color: Dark Sapphire
-Weight: 24.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Steel, Polyester construction is complemented by Dark Sapphire tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Dark Sapphire&lt;br&gt;
+Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H168" s="46" t="inlineStr">
@@ -22022,12 +22022,12 @@
       </c>
       <c r="G169" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with GLAM Cantilever Umbrella w/ LED, styled in Modern and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Steel, Polyester and Graphite tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"DIA X 98 1/2"H
-Materials: Steel, Polyester.
-Color: Graphite
-Weight: 24.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with GLAM Cantilever Umbrella w/ LED, styled in Modern and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Steel, Polyester and Graphite tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Graphite&lt;br&gt;
+Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H169" s="46" t="inlineStr">
@@ -22151,12 +22151,12 @@
       </c>
       <c r="G170" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Light Sapphire tones that pair easily with surrounding decor.
-Product Dimensions: 118"DIA X 98 1/2"H
-Materials: Steel, Polyester.
-Color: Light Sapphire
-Weight: 24.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Light Sapphire tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Light Sapphire&lt;br&gt;
+Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H170" s="46" t="inlineStr">
@@ -22279,12 +22279,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HALO Market Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Metal, Fabric and Blue or White or Black tones, it blends structure and softness in one clean profile.
-Product Dimensions: 106"DIA X 94.5"H
-Materials: Metal, Fabric.
-Color: Blue or White or Black
-Weight: 11.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HALO Market Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Metal, Fabric and Blue or White or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 106"DIA X 94.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue or White or Black&lt;br&gt;
+Weight: 11.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -22411,12 +22411,12 @@
       </c>
       <c r="G172" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.
-Product Dimensions: 106 1/4"DIA X 94 1/2"H
-Materials: Steel, Polyester.
-Color: Black or White
-Weight: 12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H172" s="52" t="inlineStr">
@@ -22540,12 +22540,12 @@
       </c>
       <c r="G173" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HALO Round Umbrella and its Modern character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Canvas Stone tones, the Steel, Polyester build balances durability with visual appeal.
-Product Dimensions: 106 1/4"DIA X 94 1/2"H
-Materials: Steel, Polyester.
-Color: Canvas Stone
-Weight: 12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HALO Round Umbrella and its Modern character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Canvas Stone tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Canvas Stone&lt;br&gt;
+Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H173" s="52" t="inlineStr">
@@ -22669,12 +22669,12 @@
       </c>
       <c r="G174" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALO Round Umbrella brings a Modern look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Steel, Polyester construction is complemented by Dark Sapphire tones for a polished look.
-Product Dimensions: 106 1/4"DIA X 94 1/2"H
-Materials: Steel, Polyester.
-Color: Dark Sapphire
-Weight: 12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALO Round Umbrella brings a Modern look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Steel, Polyester construction is complemented by Dark Sapphire tones for a polished look.&lt;br&gt;
+Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Dark Sapphire&lt;br&gt;
+Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H174" s="52" t="inlineStr">
@@ -22798,12 +22798,12 @@
       </c>
       <c r="G175" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HALO Round Umbrella, styled in Modern and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Steel, Polyester and Graphite tones, it blends structure and softness in one clean profile.
-Product Dimensions: 106 1/4"DIA X 94 1/2"H
-Materials: Steel, Polyester.
-Color: Graphite
-Weight: 12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HALO Round Umbrella, styled in Modern and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Steel, Polyester and Graphite tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Graphite&lt;br&gt;
+Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H175" s="52" t="inlineStr">
@@ -22927,12 +22927,12 @@
       </c>
       <c r="G176" s="52" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Steel, Polyester, it is finished in Light Sapphire tones that pair easily with surrounding decor.
-Product Dimensions: 106 1/4"DIA X 94 1/2"H
-Materials: Steel, Polyester.
-Color: Light Sapphire
-Weight: 12 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Steel, Polyester, it is finished in Light Sapphire tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Light Sapphire&lt;br&gt;
+Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H176" s="52" t="inlineStr">
@@ -23060,13 +23060,13 @@
       </c>
       <c r="G177" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H177" s="54" t="inlineStr">
@@ -23198,13 +23198,13 @@
       </c>
       <c r="G178" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H178" s="54" t="inlineStr">
@@ -23334,13 +23334,13 @@
       </c>
       <c r="G179" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HERO 10' Square Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HERO 10' Square Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" s="54" t="inlineStr">
@@ -23472,13 +23472,13 @@
       </c>
       <c r="G180" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HERO 10' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HERO 10' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" s="54" t="inlineStr">
@@ -23608,13 +23608,13 @@
       </c>
       <c r="G181" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" s="54" t="inlineStr">
@@ -23742,13 +23742,13 @@
       </c>
       <c r="G182" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H182" s="54" t="inlineStr">
@@ -23878,13 +23878,13 @@
       </c>
       <c r="G183" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with HERO 10' Square Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with HERO 10' Square Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" s="54" t="inlineStr">
@@ -24012,13 +24012,13 @@
       </c>
       <c r="G184" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HERO 10' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HERO 10' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" s="54" t="inlineStr">
@@ -24148,13 +24148,13 @@
       </c>
       <c r="G185" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H185" s="54" t="inlineStr">
@@ -24282,13 +24282,13 @@
       </c>
       <c r="G186" s="54" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" s="54" t="inlineStr">
@@ -24414,12 +24414,12 @@
       </c>
       <c r="G187" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LALI 11' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Fabric, Steel, construction is complemented by Blue tones for a polished look.
-Product Dimensions: 132"W X 132"D X 101"H
-Materials: Fabric, Steel.
-Color: Blue
-Weight: 67.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LALI 11' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Fabric, Steel, construction is complemented by Blue tones for a polished look.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 67.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H187" s="48" t="inlineStr">
@@ -24545,12 +24545,12 @@
       </c>
       <c r="G188" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LALI 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Fabric, Steel, and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 132"W X 132"D X 101"H
-Materials: Fabric, Steel.
-Color: Red
-Weight: 67.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LALI 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Fabric, Steel, and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 67.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H188" s="48" t="inlineStr">
@@ -24676,12 +24676,12 @@
       </c>
       <c r="G189" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LALI 11' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Fabric, Steel, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: 132"W X 132"D X 101"H
-Materials: Fabric, Steel.
-Color: Beige
-Weight: 67.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LALI 11' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Fabric, Steel, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 67.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H189" s="48" t="inlineStr">
@@ -24807,12 +24807,12 @@
       </c>
       <c r="G190" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LALI 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 104"DIA X 92.5"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 9.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LALI 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 9.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H190" s="24" t="inlineStr">
@@ -24940,12 +24940,12 @@
       </c>
       <c r="G191" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LALI 9' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Metal, Fabric construction is complemented by Beige tones for a polished look.
-Product Dimensions: 104"DIA X 92.5"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 58.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LALI 9' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Metal, Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 58.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H191" s="24" t="inlineStr">
@@ -25071,12 +25071,12 @@
       </c>
       <c r="G192" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with LALI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 104"DIA X 92.5"H
-Materials: Metal, Fabric.
-Color: Blue
-Weight: 9.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with LALI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 9.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" s="24" t="inlineStr">
@@ -25204,12 +25204,12 @@
       </c>
       <c r="G193" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LALI 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 104"DIA X 92.5"H
-Materials: Metal, Fabric.
-Color: Blue
-Weight: 58.92 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LALI 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 58.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H193" s="24" t="inlineStr">
@@ -25335,12 +25335,12 @@
       </c>
       <c r="G194" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with MORA 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 132"W X 132"D X 101"H
-Materials: Metal, Fabric.
-Color: Blue
-Weight: 18.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with MORA 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 18.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H194" s="38" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="G195" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MORA 11' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 132"W X 132"D X 101"H
-Materials: Metal, Fabric.
-Color: Red
-Weight: 18.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MORA 11' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 18.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H195" s="38" t="inlineStr">
@@ -25593,12 +25593,12 @@
       </c>
       <c r="G196" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MORA 11' Outdoor Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 132"W X 132"D X 101"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 18.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MORA 11' Outdoor Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 18.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H196" s="38" t="inlineStr">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="G197" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MUSA Rectangular Market Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Canvas Stone tones, the Metal, Fabric build balances durability with visual appeal.
-Product Dimensions: 176.5"W X 104"D X 94.5"H
-Materials: Metal, Fabric.
-Color: Canvas Stone
-Weight: 43 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MUSA Rectangular Market Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Canvas Stone tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 176.5"W X 104"D X 94.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Canvas Stone&lt;br&gt;
+Weight: 43 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H197" s="67" t="inlineStr">
@@ -25851,12 +25851,12 @@
       </c>
       <c r="G198" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MUSA Rectangular Market Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Gray tones for a polished look.
-Product Dimensions: 176.5"W X 104"D X 94.5"H
-Materials: Metal, Fabric.
-Color: Gray
-Weight: 43 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MUSA Rectangular Market Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 176.5"W X 104"D X 94.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 43 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H198" s="67" t="inlineStr">
@@ -25984,13 +25984,13 @@
       </c>
       <c r="G199" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 46.29 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 46.29 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H199" s="59" t="inlineStr">
@@ -26122,13 +26122,13 @@
       </c>
       <c r="G200" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 61.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H200" s="59" t="inlineStr">
@@ -26258,13 +26258,13 @@
       </c>
       <c r="G201" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NUTI 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 46.29 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NUTI 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 46.29 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H201" s="59" t="inlineStr">
@@ -26396,13 +26396,13 @@
       </c>
       <c r="G202" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUTI 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 61.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUTI 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" s="59" t="inlineStr">
@@ -26532,13 +26532,13 @@
       </c>
       <c r="G203" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 46.29 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 46.29 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" s="59" t="inlineStr">
@@ -26666,13 +26666,13 @@
       </c>
       <c r="G204" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 61.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" s="59" t="inlineStr">
@@ -26802,13 +26802,13 @@
       </c>
       <c r="G205" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with NUTI 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 46.29 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with NUTI 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 46.29 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" s="59" t="inlineStr">
@@ -26936,13 +26936,13 @@
       </c>
       <c r="G206" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUTI 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 61.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUTI 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H206" s="59" t="inlineStr">
@@ -27072,13 +27072,13 @@
       </c>
       <c r="G207" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 46.29 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 46.29 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H207" s="59" t="inlineStr">
@@ -27206,13 +27206,13 @@
       </c>
       <c r="G208" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: LED Light
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 61.89 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: LED Light&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H208" s="59" t="inlineStr">
@@ -27342,13 +27342,13 @@
       </c>
       <c r="G209" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" s="35" t="inlineStr">
@@ -27480,13 +27480,13 @@
       </c>
       <c r="G210" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Beige tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H210" s="35" t="inlineStr">
@@ -27616,13 +27616,13 @@
       </c>
       <c r="G211" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANO 10' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANO 10' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H211" s="35" t="inlineStr">
@@ -27754,13 +27754,13 @@
       </c>
       <c r="G212" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SANO 10' SQ Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Blue tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SANO 10' SQ Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Blue tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H212" s="35" t="inlineStr">
@@ -27890,13 +27890,13 @@
       </c>
       <c r="G213" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H213" s="35" t="inlineStr">
@@ -28024,13 +28024,13 @@
       </c>
       <c r="G214" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H214" s="35" t="inlineStr">
@@ -28160,13 +28160,13 @@
       </c>
       <c r="G215" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANO 10' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANO 10' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H215" s="35" t="inlineStr">
@@ -28294,13 +28294,13 @@
       </c>
       <c r="G216" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SANO 10' SQ Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Red tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SANO 10' SQ Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Red tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H216" s="35" t="inlineStr">
@@ -28430,13 +28430,13 @@
       </c>
       <c r="G217" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 55.11 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 55.11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H217" s="35" t="inlineStr">
@@ -28564,13 +28564,13 @@
       </c>
       <c r="G218" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Teal tones, it blends structure and softness in one clean profile.
-Product Dimensions: 118"W X 118"D X 96.5"H
-Size: Double Top, LED Bulb and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 70.71 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Bulb and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H218" s="35" t="inlineStr">
@@ -28696,12 +28696,12 @@
       </c>
       <c r="G219" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.
-Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H
-Materials: Steel, Polyester.
-Color: Black or White
-Weight: 8.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Black or White&lt;br&gt;
+Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H219" s="24" t="inlineStr">
@@ -28825,12 +28825,12 @@
       </c>
       <c r="G220" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SLEEK Rectangular Umbrella brings a Modern look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Steel, Polyester construction is complemented by Canvas Stone tones for a polished look.
-Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H
-Materials: Steel, Polyester.
-Color: Canvas Stone
-Weight: 8.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SLEEK Rectangular Umbrella brings a Modern look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Steel, Polyester construction is complemented by Canvas Stone tones for a polished look.&lt;br&gt;
+Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Canvas Stone&lt;br&gt;
+Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H220" s="24" t="inlineStr">
@@ -28954,12 +28954,12 @@
       </c>
       <c r="G221" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SLEEK Rectangular Umbrella, styled in Modern and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Steel, Polyester and Dark Sapphire tones, it blends structure and softness in one clean profile.
-Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H
-Materials: Steel, Polyester.
-Color: Dark Sapphire
-Weight: 8.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SLEEK Rectangular Umbrella, styled in Modern and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Steel, Polyester and Dark Sapphire tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Dark Sapphire&lt;br&gt;
+Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H221" s="24" t="inlineStr">
@@ -29083,12 +29083,12 @@
       </c>
       <c r="G222" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SLEEK Rectangular Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Graphite tones that pair easily with surrounding decor.
-Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H
-Materials: Steel, Polyester.
-Color: Graphite
-Weight: 8.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SLEEK Rectangular Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Graphite tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Graphite&lt;br&gt;
+Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H222" s="24" t="inlineStr">
@@ -29212,12 +29212,12 @@
       </c>
       <c r="G223" s="24" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. This outdoor umbrella is made to fit naturally into the room. Finished in Light Sapphire tones, the Steel, Polyester build balances durability with visual appeal.
-Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H
-Materials: Steel, Polyester.
-Color: Light Sapphire
-Weight: 8.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. This outdoor umbrella is made to fit naturally into the room. Finished in Light Sapphire tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
+Color: Light Sapphire&lt;br&gt;
+Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H223" s="24" t="inlineStr">
@@ -29341,12 +29341,12 @@
       </c>
       <c r="G224" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SOLI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 108"W X 108"D X 96"H
-Materials: Fabric, Steel.
-Color: Blue
-Weight: 68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SOLI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H224" s="31" t="inlineStr">
@@ -29472,12 +29472,12 @@
       </c>
       <c r="G225" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOLI 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Fabric, Steel, it is finished in Red tones that pair easily with surrounding decor.
-Product Dimensions: 108"W X 108"D X 96"H
-Materials: Fabric, Steel.
-Color: Red
-Weight: 68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOLI 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Fabric, Steel, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H225" s="31" t="inlineStr">
@@ -29603,12 +29603,12 @@
       </c>
       <c r="G226" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with SOLI 9' Outdoor Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Fabric, Steel, build balances durability with visual appeal.
-Product Dimensions: 108"W X 108"D X 96"H
-Materials: Fabric, Steel.
-Color: Beige
-Weight: 68 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with SOLI 9' Outdoor Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Fabric, Steel, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H226" s="31" t="inlineStr">
@@ -29734,12 +29734,12 @@
       </c>
       <c r="G227" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOLI 9' Outdoor Umbrella w/ Auto Tilt brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Blue tones for a polished look.
-Product Dimensions: 108"W X 108"D X 96"H
-Materials: Metal, Fabric.
-Color: Blue
-Weight: 19 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOLI 9' Outdoor Umbrella w/ Auto Tilt brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 19 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H227" s="65" t="inlineStr">
@@ -29863,12 +29863,12 @@
       </c>
       <c r="G228" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SOLI 9' Outdoor Umbrella w/ Auto Tilt, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 108"W X 108"D X 96"H
-Materials: Metal, Fabric.
-Color: Red
-Weight: 19 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SOLI 9' Outdoor Umbrella w/ Auto Tilt, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 19 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H228" s="65" t="inlineStr">
@@ -29992,12 +29992,12 @@
       </c>
       <c r="G229" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SOLI 9' Outdoor Umbrella w/ Auto Tilt adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: 108"W X 108"D X 96"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 19 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SOLI 9' Outdoor Umbrella w/ Auto Tilt adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 19 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H229" s="65" t="inlineStr">
@@ -30121,12 +30121,12 @@
       </c>
       <c r="G230" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.
-Product Dimensions: 108"W X 108"D X 94"H
-Materials: Metal, Fabric.
-Color: Blue
-Weight: 12.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 12.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H230" s="38" t="inlineStr">
@@ -30250,12 +30250,12 @@
       </c>
       <c r="G231" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TANO 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Blue tones, the Fabric, Steel, build balances durability with visual appeal.
-Product Dimensions: 108"W X 108"D X 94"H
-Materials: Fabric, Steel.
-Color: Blue
-Weight: 61.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TANO 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Blue tones, the Fabric, Steel, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H231" s="38" t="inlineStr">
@@ -30381,12 +30381,12 @@
       </c>
       <c r="G232" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TANO 9' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Metal, Fabric construction is complemented by Red tones for a polished look.
-Product Dimensions: 108"W X 108"D X 94"H
-Materials: Metal, Fabric.
-Color: Red
-Weight: 12.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TANO 9' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Metal, Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 12.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H232" s="38" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="G233" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with TANO 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 108"W X 108"D X 94"H
-Materials: Fabric, Steel.
-Color: Red
-Weight: 61.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with TANO 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H233" s="38" t="inlineStr">
@@ -30641,12 +30641,12 @@
       </c>
       <c r="G234" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: 108"W X 108"D X 94"H
-Materials: Metal, Fabric.
-Color: Beige
-Weight: 12.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
+&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 12.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H234" s="38" t="inlineStr">
@@ -30770,12 +30770,12 @@
       </c>
       <c r="G235" s="38" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TANO 9' Outdoor Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Fabric, Steel, build balances durability with visual appeal.
-Product Dimensions: 108"W X 108"D X 94"H
-Materials: Fabric, Steel.
-Color: Beige
-Weight: 61.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TANO 9' Outdoor Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Fabric, Steel, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H235" s="38" t="inlineStr">
@@ -30905,13 +30905,13 @@
       </c>
       <c r="G236" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H236" s="67" t="inlineStr">
@@ -31043,13 +31043,13 @@
       </c>
       <c r="G237" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Beige
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Beige&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H237" s="67" t="inlineStr">
@@ -31179,13 +31179,13 @@
       </c>
       <c r="G238" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XICO 8' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Blue tones for a polished look.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XICO 8' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H238" s="67" t="inlineStr">
@@ -31317,13 +31317,13 @@
       </c>
       <c r="G239" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with XICO 8' SQ Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Blue
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with XICO 8' SQ Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Blue&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H239" s="67" t="inlineStr">
@@ -31453,13 +31453,13 @@
       </c>
       <c r="G240" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Gray tones that pair easily with surrounding decor.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H240" s="67" t="inlineStr">
@@ -31587,13 +31587,13 @@
       </c>
       <c r="G241" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Gray
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H241" s="67" t="inlineStr">
@@ -31723,13 +31723,13 @@
       </c>
       <c r="G242" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XICO 8' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Red tones for a polished look.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XICO 8' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H242" s="67" t="inlineStr">
@@ -31857,13 +31857,13 @@
       </c>
       <c r="G243" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with XICO 8' SQ Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Red
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with XICO 8' SQ Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Red&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H243" s="67" t="inlineStr">
@@ -31993,13 +31993,13 @@
       </c>
       <c r="G244" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Teal tones that pair easily with surrounding decor.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Teal tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H244" s="67" t="inlineStr">
@@ -32127,13 +32127,13 @@
       </c>
       <c r="G245" s="67" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.
-Product Dimensions: 98.5"W X 98.5"D X 96.5"H
-Size: Double Top, LED Light and Control
-Materials: Aluminum, Polyester Fabric.
-Color: Teal
-Weight: 68.51 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
+Size: Double Top, LED Light and Control&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
+Color: Teal&lt;br&gt;
+Weight: 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H245" s="67" t="inlineStr">
@@ -32259,12 +32259,12 @@
       </c>
       <c r="G246" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with HALEY Hammock w/ Stand and its Contemporary character. This outdoor hammock is made to fit naturally into the room. Finished in Green or Blue tones, the Polyester Cotton, Steel build balances durability with visual appeal.
-Product Dimensions: 130"W X 47"D X 46"H
-Materials: Polyester Cotton, Steel.
-Color: Green or Blue
-Weight: 38 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with HALEY Hammock w/ Stand and its Contemporary character. This outdoor hammock is made to fit naturally into the room. Finished in Green or Blue tones, the Polyester Cotton, Steel build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 130"W X 47"D X 46"H&lt;/p&gt;
+&lt;p&gt;Materials: Polyester Cotton, Steel.&lt;br&gt;
+Color: Green or Blue&lt;br&gt;
+Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H246" s="59" t="inlineStr">
@@ -32386,12 +32386,12 @@
       </c>
       <c r="G247" s="59" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-HALEY Hammock w/ Stand brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor hammock, it pairs well with a wide range of interiors. The Polyester Cotton, Steel construction is complemented by Brown or Black tones for a polished look.
-Product Dimensions: HAMMOCK: 130L X 60"W, STAND: 47"L X 122"W X 44"H"
-Materials: Polyester Cotton, Steel.
-Color: Brown or Black
-Weight: 38 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+HALEY Hammock w/ Stand brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor hammock, it pairs well with a wide range of interiors. The Polyester Cotton, Steel construction is complemented by Brown or Black tones for a polished look.&lt;br&gt;
+Product Dimensions: HAMMOCK: 130L X 60"W, STAND: 47"L X 122"W X 44"H"&lt;/p&gt;
+&lt;p&gt;Materials: Polyester Cotton, Steel.&lt;br&gt;
+Color: Brown or Black&lt;br&gt;
+Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H247" s="59" t="inlineStr">
@@ -32516,12 +32516,12 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-IMBLER Shelf brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor shelf, it pairs well with a wide range of interiors. The Bamboo construction is complemented by Natural tones for a polished look.
-Product Dimensions: 23"W X 8"D X 42.5"H
-Materials: Bamboo.
-Color: Natural
-Weight: 20.94 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+IMBLER Shelf brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor shelf, it pairs well with a wide range of interiors. The Bamboo construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: 23"W X 8"D X 42.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Bamboo.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 20.94 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -32642,12 +32642,12 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with POTTER Trolley and its Contemporary character. This outdoor shelf is made to fit naturally into the room. Finished in Natural tones, the Bamboo build balances durability with visual appeal.
-Product Dimensions: 14.5"W X 15"D X 34.5"H Bonus storage &amp; convenience features (from matching set pieces): Storage Drawer
-Materials: Bamboo.
-Color: Natural
-Weight: 12.26 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with POTTER Trolley and its Contemporary character. This outdoor shelf is made to fit naturally into the room. Finished in Natural tones, the Bamboo build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 14.5"W X 15"D X 34.5"H Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawer&lt;/p&gt;
+&lt;p&gt;Materials: Bamboo.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 12.26 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -32768,12 +32768,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with TIMBER Shelf and its Contemporary character. Built as a outdoor shelf, it pairs well with a wide range of interiors. Finished in Natural tones, the Bamboo build balances durability with visual appeal.
-Product Dimensions: 22"W X 9"D X 52"H
-Materials: Bamboo.
-Color: Natural
-Weight: 31.75 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with TIMBER Shelf and its Contemporary character. Built as a outdoor shelf, it pairs well with a wide range of interiors. Finished in Natural tones, the Bamboo build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 22"W X 9"D X 52"H&lt;/p&gt;
+&lt;p&gt;Materials: Bamboo.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 31.75 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -32894,12 +32894,12 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with WATTER Trolley and its Contemporary character. This outdoor shelf is made to fit naturally into the room. Finished in Natural tones, the Bamboo build balances durability with visual appeal.
-Product Dimensions: 24.5"W X 16.5"D X 29"H Bonus storage &amp; convenience features (from matching set pieces): Storage Drawers
-Materials: Bamboo.
-Color: Natural
-Weight: 18.21 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with WATTER Trolley and its Contemporary character. This outdoor shelf is made to fit naturally into the room. Finished in Natural tones, the Bamboo build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 24.5"W X 16.5"D X 29"H Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Bamboo.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 18.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -33015,10 +33015,10 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-JOHARI Patio Coffee Table is designed to complement your space with a balanced, versatile look. This outdoor coffee table is made to fit naturally into the room.
-Product Dimensions: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")
-Weight: 30.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+JOHARI Patio Coffee Table is designed to complement your space with a balanced, versatile look. This outdoor coffee table is made to fit naturally into the room.&lt;br&gt;
+Product Dimensions: 30"W X 29"D X 25.5"H (SEAT HT: 16.5")&lt;br&gt;
+Weight: 30.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -33124,12 +33124,12 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with KESI Patio Folding Bed, styled in Transitional and designed for everyday comfort. This outdoor bed is made to fit naturally into the room. With Fabric, PE Rattan, Foam, Steel and Natural tones, it blends structure and softness in one clean profile.
-Product Dimensions: 78.5"W X 23.5"D X 16"H
-Materials: Fabric, PE Rattan, Foam, Steel.
-Color: Natural
-Weight: 50.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with KESI Patio Folding Bed, styled in Transitional and designed for everyday comfort. This outdoor bed is made to fit naturally into the room. With Fabric, PE Rattan, Foam, Steel and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 78.5"W X 23.5"D X 16"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, PE Rattan, Foam, Steel.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 50.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -33251,12 +33251,12 @@
       </c>
       <c r="G254" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with KYUSHU Table and Loveseat, styled in Rustic and designed for everyday comfort. Built as a outdoor table set, it pairs well with a wide range of interiors. With Acacia Wood, Polyester and Beige or Natural tones, it blends structure and softness in one clean profile.
-Product Dimensions: TABLE: 39 1/2"L X 23 1/2"W X 18"H, LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H
-Materials: Acacia Wood, Polyester.
-Color: Beige or Natural
-Weight: 57.02 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with KYUSHU Table and Loveseat, styled in Rustic and designed for everyday comfort. Built as a outdoor table set, it pairs well with a wide range of interiors. With Acacia Wood, Polyester and Beige or Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: TABLE: 39 1/2"L X 23 1/2"W X 18"H, LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Beige or Natural&lt;br&gt;
+Weight: 57.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H254" s="35" t="inlineStr">
@@ -33380,12 +33380,12 @@
       </c>
       <c r="G255" s="35" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-KYUSHU Table and Loveseat adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor table set, it is designed to complement your space. Crafted from Acacia Wood, Polyester, it is finished in Black or Natural tones that pair easily with surrounding decor.
-Product Dimensions: TABLE: 39 1/2"L X 23 1/2"W X 18"H, LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H
-Materials: Acacia Wood, Polyester.
-Color: Black or Natural
-Weight: 57.02 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+KYUSHU Table and Loveseat adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor table set, it is designed to complement your space. Crafted from Acacia Wood, Polyester, it is finished in Black or Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: TABLE: 39 1/2"L X 23 1/2"W X 18"H, LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
+Color: Black or Natural&lt;br&gt;
+Weight: 57.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H255" s="35" t="inlineStr">
@@ -33509,12 +33509,12 @@
       </c>
       <c r="G256" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-LOTUS 3 Pc. Patio Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor table set, it pairs well with a wide range of interiors. Crafted from Aluminum, Fabric, Ceramic, it is finished in Black or Light Brown tones that pair easily with surrounding decor.
-Product Dimensions: Chair: 74"W X 29.5"D X 34"H, Table: 28"W X 26.5"D X 37"H
-Materials: Aluminum, Fabric, Ceramic.
-Color: Black or Light Brown
-Weight: 63.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+LOTUS 3 Pc. Patio Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor table set, it pairs well with a wide range of interiors. Crafted from Aluminum, Fabric, Ceramic, it is finished in Black or Light Brown tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Chair: 74"W X 29.5"D X 34"H, Table: 28"W X 26.5"D X 37"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Fabric, Ceramic.&lt;br&gt;
+Color: Black or Light Brown&lt;br&gt;
+Weight: 63.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H256" s="31" t="inlineStr">
@@ -33638,12 +33638,12 @@
       </c>
       <c r="G257" s="31" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with LOTUS 3 Pc. Patio Set and its Contemporary character. As a outdoor table set, it is designed to complement your space. Finished in Natural or Beige tones, the Aluminum, Fabric, Ceramic build balances durability with visual appeal.
-Product Dimensions: SIDE TABLE: 22"DIA X 18 1/4"H, CHAIR: 28 1/4"W X 26 1/2"D X 37"H (SEAT HT: 17", SEAT DP: 28")
-Materials: Aluminum, Fabric, Ceramic.
-Color: Natural or Beige
-Weight: 63.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with LOTUS 3 Pc. Patio Set and its Contemporary character. As a outdoor table set, it is designed to complement your space. Finished in Natural or Beige tones, the Aluminum, Fabric, Ceramic build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: SIDE TABLE: 22"DIA X 18 1/4"H, CHAIR: 28 1/4"W X 26 1/2"D X 37"H (SEAT HT: 17", SEAT DP: 28")&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Fabric, Ceramic.&lt;br&gt;
+Color: Natural or Beige&lt;br&gt;
+Weight: 63.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H257" s="31" t="inlineStr">
@@ -33767,12 +33767,12 @@
       </c>
       <c r="G258" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MACKAY Patio Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio dining table, it is designed to complement your space. Crafted from Aluminum, FSC Certified 100% Teak Wood, it is finished in Gun Metal or Natural Teak tones that pair easily with surrounding decor.
-Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Gun Metal or Natural Teak
-Weight: 52.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MACKAY Patio Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio dining table, it is designed to complement your space. Crafted from Aluminum, FSC Certified 100% Teak Wood, it is finished in Gun Metal or Natural Teak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Gun Metal or Natural Teak&lt;br&gt;
+Weight: 52.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H258" s="65" t="inlineStr">
@@ -33896,12 +33896,12 @@
       </c>
       <c r="G259" s="65" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MACKAY Patio Dining Table and its Contemporary character. This outdoor patio dining table is made to fit naturally into the room. Finished in Gun Metal or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build balances durability with visual appeal.
-Product Dimensions: 59"L X 35 1/2"W X 29"H
-Materials: Aluminum, FSC Certified 100% Teak Wood.
-Color: Gun Metal or Natural Teak
-Weight: 33.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MACKAY Patio Dining Table and its Contemporary character. This outdoor patio dining table is made to fit naturally into the room. Finished in Gun Metal or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 59"L X 35 1/2"W X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
+Color: Gun Metal or Natural Teak&lt;br&gt;
+Weight: 33.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H259" s="65" t="inlineStr">
@@ -34024,12 +34024,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MALIA Patio Dining Table brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio dining table is made to fit naturally into the room. The Aluminum, Polyethylene Wicker, Polyspun construction is complemented by Gray tones for a polished look.
-Product Dimensions: 59"L X 31 1/4"W X 26 3/4"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gray
-Weight: 38.6 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MALIA Patio Dining Table brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio dining table is made to fit naturally into the room. The Aluminum, Polyethylene Wicker, Polyspun construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 59"L X 31 1/4"W X 26 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 38.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -34151,12 +34151,12 @@
       </c>
       <c r="G261" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-SINTRA Patio Dining Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor patio dining table, it pairs well with a wide range of interiors. The Steel, Ceramic Tile construction is complemented by Black or Gray tones for a polished look.
-Product Dimensions: 76"L X 40"W X 28"H
-Materials: Steel, Ceramic Tile.
-Color: Black or Gray
-Weight: 105.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+SINTRA Patio Dining Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor patio dining table, it pairs well with a wide range of interiors. The Steel, Ceramic Tile construction is complemented by Black or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 76"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic Tile.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 105.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="48" t="inlineStr">
@@ -34280,12 +34280,12 @@
       </c>
       <c r="G262" s="48" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SINTRA Patio Dining Table, styled in Contemporary and designed for everyday comfort. As a outdoor patio dining table, it is designed to complement your space. With Steel, Ceramic and Black or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 40"L X 40"W X 28"H
-Materials: Steel, Ceramic.
-Color: Black or Gray
-Weight: 63.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SINTRA Patio Dining Table, styled in Contemporary and designed for everyday comfort. As a outdoor patio dining table, it is designed to complement your space. With Steel, Ceramic and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 40"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 63.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" s="48" t="inlineStr">
@@ -34408,12 +34408,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MALIA 5 Pc. Sectional Set w/ Bench and its Contemporary character. As a outdoor sectional set, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build balances durability with visual appeal.
-Product Dimensions: LEFT SOFA: 86 1/4"L X 31"W X 33"H, RIGHT SOFA: 78"L X 31"W X 33"H, OTTOMAN: 15"L X 15"W X 16"H, BENCH: 55"W X 15"D X 19 3/4"H
-Materials: Aluminum, Polyethylene Wicker, Polyspun.
-Color: Gray
-Weight: 160.9 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MALIA 5 Pc. Sectional Set w/ Bench and its Contemporary character. As a outdoor sectional set, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyethylene Wicker, Polyspun build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: LEFT SOFA: 86 1/4"L X 31"W X 33"H, RIGHT SOFA: 78"L X 31"W X 33"H, OTTOMAN: 15"L X 15"W X 16"H, BENCH: 55"W X 15"D X 19 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: Aluminum, Polyethylene Wicker, Polyspun.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 160.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -34534,12 +34534,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with MAUI Convertible Sofa Daybed and its Contemporary character. As a outdoor daybed, it is designed to complement your space. Finished in Gray or Turquoise tones, the FSC Certified 100% Acacia Wood, Polyester build balances durability with visual appeal.
-Product Dimensions: SOFA: 58 1/2 - 78"L X 15 3/4"W X 30 3/4"H, PULL-OUT TRAY TABLE: 15 3/4"L X 10 1/4"W
-Materials: FSC Certified 100% Acacia Wood, Polyester.
-Color: Gray or Turquoise
-Weight: 52.91 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with MAUI Convertible Sofa Daybed and its Contemporary character. As a outdoor daybed, it is designed to complement your space. Finished in Gray or Turquoise tones, the FSC Certified 100% Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: SOFA: 58 1/2 - 78"L X 15 3/4"W X 30 3/4"H, PULL-OUT TRAY TABLE: 15 3/4"L X 10 1/4"W&lt;/p&gt;
+&lt;p&gt;Materials: FSC Certified 100% Acacia Wood, Polyester.&lt;br&gt;
+Color: Gray or Turquoise&lt;br&gt;
+Weight: 52.91 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -34660,12 +34660,12 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-VELDEN Convertible Sofa Daybed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor daybed, it pairs well with a wide range of interiors. Crafted from FSC Certified 100% Acacia Wood, Polyester, it is finished in Natural or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 62 1/4 - 78"W X 15 3/4"D X 30 3/4"H
-Materials: FSC Certified 100% Acacia Wood, Polyester.
-Color: Natural or Gray
-Weight: 48.5 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+VELDEN Convertible Sofa Daybed adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor daybed, it pairs well with a wide range of interiors. Crafted from FSC Certified 100% Acacia Wood, Polyester, it is finished in Natural or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 62 1/4 - 78"W X 15 3/4"D X 30 3/4"H&lt;/p&gt;
+&lt;p&gt;Materials: FSC Certified 100% Acacia Wood, Polyester.&lt;br&gt;
+Color: Natural or Gray&lt;br&gt;
+Weight: 48.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MOSIER Hall Tree w/ Bench &amp; Shoe Storage adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor storage is made to fit naturally into the room. Crafted from Bamboo, Polyester, it is finished in Natural or Gray tones that pair easily with surrounding decor.
-Product Dimensions: 12"W X 12"D X 65"H
-Materials: Bamboo, Polyester.
-Color: Natural or Gray
-Weight: 13.23 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MOSIER Hall Tree w/ Bench &amp;amp; Shoe Storage adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor storage is made to fit naturally into the room. Crafted from Bamboo, Polyester, it is finished in Natural or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 12"W X 12"D X 65"H&lt;/p&gt;
+&lt;p&gt;Materials: Bamboo, Polyester.&lt;br&gt;
+Color: Natural or Gray&lt;br&gt;
+Weight: 13.23 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -34913,12 +34913,12 @@
       </c>
       <c r="G267" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Make the room feel complete with NIAMBI Square Table and its Contemporary character. As a outdoor patio table, it is designed to complement your space. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build balances durability with visual appeal.
-Product Dimensions: 26.5"W X 23.5"D X 29"H
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
-Color: Gray
-Weight: 33.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Make the room feel complete with NIAMBI Square Table and its Contemporary character. As a outdoor patio table, it is designed to complement your space. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 26.5"W X 23.5"D X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
+Color: Gray&lt;br&gt;
+Weight: 33.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H267" s="46" t="inlineStr">
@@ -35040,12 +35040,12 @@
       </c>
       <c r="G268" s="46" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-NIAMBI Square Table brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio table is made to fit naturally into the room. The Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction is complemented by Natural tones for a polished look.
-Product Dimensions: 26.5"W X 23.5"D X 29"H
-Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.
-Color: Natural
-Weight: 33.8 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+NIAMBI Square Table brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio table is made to fit naturally into the room. The Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Product Dimensions: 26.5"W X 23.5"D X 29"H&lt;/p&gt;
+&lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 33.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H268" s="46" t="inlineStr">
@@ -35166,12 +35166,12 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with ZUBERI Round Table, styled in Contemporary and designed for everyday comfort. As a outdoor patio table, it is designed to complement your space. With Steel Frame, PE Rattan Wicker and Natural tones, it blends structure and softness in one clean profile.
-Product Dimensions: 21.7"L X 21.7"W X 15.7"H
-Materials: Steel Frame, PE Rattan Wicker.
-Color: Natural
-Weight: 11.7 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with ZUBERI Round Table, styled in Contemporary and designed for everyday comfort. As a outdoor patio table, it is designed to complement your space. With Steel Frame, PE Rattan Wicker and Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 21.7"L X 21.7"W X 15.7"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel Frame, PE Rattan Wicker.&lt;br&gt;
+Color: Natural&lt;br&gt;
+Weight: 11.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -35292,12 +35292,12 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-OLIVERI 4 Pc. Wicker Conversation Set brings a Transitional look to your home with a refined, comfortable feel. As a outdoor conversation set, it is designed to complement your space. The Fabric, Faux Rattan construction is complemented by Brown or Dark Teal tones for a polished look.
-Product Dimensions: Table: 20"W X 33"D X 16"H, Bench: 48"W X 23"D X 35"H, Chair: 26"W X 23"D X 35"H
-Materials: Fabric, Faux Rattan.
-Color: Brown or Dark Teal
-Weight: 97 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+OLIVERI 4 Pc. Wicker Conversation Set brings a Transitional look to your home with a refined, comfortable feel. As a outdoor conversation set, it is designed to complement your space. The Fabric, Faux Rattan construction is complemented by Brown or Dark Teal tones for a polished look.&lt;br&gt;
+Product Dimensions: Table: 20"W X 33"D X 16"H, Bench: 48"W X 23"D X 35"H, Chair: 26"W X 23"D X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Fabric, Faux Rattan.&lt;br&gt;
+Color: Brown or Dark Teal&lt;br&gt;
+Weight: 97 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -35414,11 +35414,11 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with OLIVERI 4 Pc. Wicker Conversation Set (9 Pack), styled in Transitional and designed for everyday comfort. This outdoor conversation set is made to fit naturally into the room. With Glass, Fabric, Faux Rattan and Brown or Dark Teal tones, it blends structure and softness in one clean profile.
-Product Dimensions: Table: 20"W X 33"D X 16"H, Bench: 48"D X 23"D X 35"H, Chair: 26"D X 23"D X 35"H
-Materials: Glass, Fabric, Faux Rattan.
-Color: Brown or Dark Teal</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with OLIVERI 4 Pc. Wicker Conversation Set (9 Pack), styled in Transitional and designed for everyday comfort. This outdoor conversation set is made to fit naturally into the room. With Glass, Fabric, Faux Rattan and Brown or Dark Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: Table: 20"W X 33"D X 16"H, Bench: 48"D X 23"D X 35"H, Chair: 26"D X 23"D X 35"H&lt;/p&gt;
+&lt;p&gt;Materials: Glass, Fabric, Faux Rattan.&lt;br&gt;
+Color: Brown or Dark Teal&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -35532,12 +35532,12 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-Elevate your space with SEGOVIA Fire Pit Table, styled in Contemporary and designed for everyday comfort. This outdoor fire pit table is made to fit naturally into the room. With Steel, Polyethylene Wicker, Ceramic, Polyspun and Black or Gray tones, it blends structure and softness in one clean profile.
-Product Dimensions: 40"W X 40"D X 26.5"H
-Materials: Steel, Polyethylene Wicker, Ceramic, Polyspun.
-Color: Black or Gray
-Weight: 98.1 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+Elevate your space with SEGOVIA Fire Pit Table, styled in Contemporary and designed for everyday comfort. This outdoor fire pit table is made to fit naturally into the room. With Steel, Polyethylene Wicker, Ceramic, Polyspun and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 40"W X 40"D X 26.5"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Polyethylene Wicker, Ceramic, Polyspun.&lt;br&gt;
+Color: Black or Gray&lt;br&gt;
+Weight: 98.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -35658,12 +35658,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-WAVE Stand brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor stand, it pairs well with a wide range of interiors. The Steel construction is complemented by Black tones for a polished look.
-Product Dimensions: 45 1/4"L X 42 1/2"W X 75 1/2"H
-Materials: Steel.
-Color: Black
-Weight: 40.34 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+WAVE Stand brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor stand, it pairs well with a wide range of interiors. The Steel construction is complemented by Black tones for a polished look.&lt;br&gt;
+Product Dimensions: 45 1/4"L X 42 1/2"W X 75 1/2"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 40.34 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">

--- a/FOA Singles/Outdoor-Single.xlsx
+++ b/FOA Singles/Outdoor-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD273"/>
+  <dimension ref="A1:AG273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -928,7 +943,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, ALBA</t>
+          <t>Outdoor, Bench, ALBA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1084,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, BORDEAUX</t>
+          <t>Outdoor, Bench, BORDEAUX, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1225,22 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, BORKUM</t>
+          <t>Outdoor, Bench, BORKUM, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1344,22 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, JOHARI</t>
+          <t>Outdoor, Bench, JOHARI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1485,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, MINOT</t>
+          <t>Outdoor, Bench, MINOT, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1626,22 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, POTTER</t>
+          <t>Outdoor, Bench, POTTER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1767,22 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, SINTRA</t>
+          <t>Outdoor, Bench, SINTRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1908,22 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, SKIPPER</t>
+          <t>Outdoor, Bench, SKIPPER, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -1896,7 +2031,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, ZALIKA</t>
+          <t>Outdoor, Bench, ZALIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2154,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Outdoor, Bench, ZALIKA</t>
+          <t>Outdoor, Bench, ZALIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Benches</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2298,22 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ALVERTA</t>
+          <t>Outdoor, Chair, ALVERTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2442,22 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ALVERTA</t>
+          <t>Outdoor, Chair, ALVERTA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2583,22 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ALYCIA</t>
+          <t>Outdoor, Chair, ALYCIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2724,22 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ANTIGUA</t>
+          <t>Outdoor, Chair, ANTIGUA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2870,22 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ASHURA</t>
+          <t>Outdoor, Chair, ASHURA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -2762,7 +3002,22 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ASHURA</t>
+          <t>Outdoor, Chair, ASHURA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -2888,7 +3143,22 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BORDEAUX</t>
+          <t>Outdoor, Chair, BORDEAUX, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3284,22 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BORDEAUX</t>
+          <t>Outdoor, Chair, BORDEAUX, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3428,22 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BREEZE</t>
+          <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3572,22 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BREEZE</t>
+          <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3716,22 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, BREEZE</t>
+          <t>Outdoor, Chair, BREEZE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3860,22 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CRUSH</t>
+          <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3659,7 +4004,22 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CRUSH</t>
+          <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3788,7 +4148,22 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CRUSH</t>
+          <t>Outdoor, Chair, CRUSH, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -3914,7 +4289,22 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, CYPRUS</t>
+          <t>Outdoor, Chair, CYPRUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4433,22 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ELK</t>
+          <t>Outdoor, Chair, ELK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4577,22 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ELK</t>
+          <t>Outdoor, Chair, ELK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4721,22 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ELK</t>
+          <t>Outdoor, Chair, ELK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4865,22 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ELK</t>
+          <t>Outdoor, Chair, ELK, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4561,7 +5011,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ENZI</t>
+          <t>Outdoor, Chair, ENZI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4687,7 +5152,22 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ENZI</t>
+          <t>Outdoor, Chair, ENZI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4815,7 +5295,22 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, GATES</t>
+          <t>Outdoor, Chair, GATES, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -4941,7 +5436,22 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, HALEY</t>
+          <t>Outdoor, Chair, HALEY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5555,22 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, JOHARI</t>
+          <t>Outdoor, Chair, JOHARI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5699,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, KYUSHU</t>
+          <t>Outdoor, Chair, KYUSHU, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5843,22 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, KYUSHU</t>
+          <t>Outdoor, Chair, KYUSHU, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5984,22 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, MACKAY</t>
+          <t>Outdoor, Chair, MACKAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5555,7 +6125,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, MACKAY</t>
+          <t>Outdoor, Chair, MACKAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5681,7 +6266,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, MALIN</t>
+          <t>Outdoor, Chair, MALIN, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5807,7 +6407,22 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, MOOSE</t>
+          <t>Outdoor, Chair, MOOSE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -5933,7 +6548,22 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, NUSA</t>
+          <t>Outdoor, Chair, NUSA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6689,22 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, NYA</t>
+          <t>Outdoor, Chair, NYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6833,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, NYA</t>
+          <t>Outdoor, Chair, NYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6981,22 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, NYA</t>
+          <t>Outdoor, Chair, NYA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6443,7 +7118,22 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, OLIVERI</t>
+          <t>Outdoor, Chair, OLIVERI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6574,7 +7264,22 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, OLIVERI</t>
+          <t>Outdoor, Chair, OLIVERI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6696,7 +7401,22 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, OLIVERI</t>
+          <t>Outdoor, Chair, OLIVERI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7538,22 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, OLIVERI</t>
+          <t>Outdoor, Chair, OLIVERI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -6944,7 +7679,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PALMA</t>
+          <t>Outdoor, Chair, PALMA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7820,22 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PALMA</t>
+          <t>Outdoor, Chair, PALMA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7961,22 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PERSE</t>
+          <t>Outdoor, Chair, PERSE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7325,7 +8105,22 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7454,7 +8249,22 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7583,7 +8393,22 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7709,7 +8534,22 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7835,7 +8675,22 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -7961,7 +8816,22 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8964,22 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8227,7 +9112,22 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8360,7 +9260,22 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, PIERRO</t>
+          <t>Outdoor, Chair, PIERRO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8489,7 +9404,22 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SANDOR</t>
+          <t>Outdoor, Chair, SANDOR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8618,7 +9548,22 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SANDOR</t>
+          <t>Outdoor, Chair, SANDOR, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8718,7 +9663,22 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SARABI</t>
+          <t>Outdoor, Chair, SARABI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8844,7 +9804,22 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SEGOVIA</t>
+          <t>Outdoor, Chair, SEGOVIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9950,22 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SEGOVIA</t>
+          <t>Outdoor, Chair, SEGOVIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9101,7 +10091,22 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SINTRA</t>
+          <t>Outdoor, Chair, SINTRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9227,7 +10232,22 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, SINTRA</t>
+          <t>Outdoor, Chair, SINTRA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9353,7 +10373,22 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, TOMOHON</t>
+          <t>Outdoor, Chair, TOMOHON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9481,7 +10516,22 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, VALE</t>
+          <t>Outdoor, Chair, VALE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9589,7 +10639,22 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ZALIKA</t>
+          <t>Outdoor, Chair, ZALIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9697,7 +10762,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Outdoor, Chair, ZALIKA</t>
+          <t>Outdoor, Chair, ZALIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs</t>
         </is>
       </c>
     </row>
@@ -9819,7 +10899,22 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Table, ALYCIA</t>
+          <t>Outdoor, Dining Table, ALYCIA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -9945,7 +11040,22 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Table, PIERRO</t>
+          <t>Outdoor, Dining Table, PIERRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Kitchen &amp; Dining Room Tables</t>
         </is>
       </c>
     </row>
@@ -10077,7 +11187,22 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Outdoor, Table, ANTIGUA</t>
+          <t>Outdoor, Table, ANTIGUA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10203,7 +11328,22 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Outdoor, Table, AROSA</t>
+          <t>Outdoor, Table, AROSA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10329,7 +11469,22 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Outdoor, Table, BARBUDA</t>
+          <t>Outdoor, Table, BARBUDA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10451,7 +11606,22 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Outdoor, Table, BORDEAUX</t>
+          <t>Outdoor, Table, BORDEAUX, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10579,7 +11749,22 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Outdoor, Table, COVE</t>
+          <t>Outdoor, Table, COVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10701,7 +11886,22 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Outdoor, Table, LOVINA</t>
+          <t>Outdoor, Table, LOVINA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10827,7 +12027,22 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Outdoor, Table, LYON</t>
+          <t>Outdoor, Table, LYON, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -10955,7 +12170,22 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Outdoor, Table, MOLLIE</t>
+          <t>Outdoor, Table, MOLLIE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11077,7 +12307,22 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Outdoor, Table, MONZA</t>
+          <t>Outdoor, Table, MONZA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11199,7 +12444,22 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Outdoor, Table, MONZA</t>
+          <t>Outdoor, Table, MONZA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11325,7 +12585,22 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Outdoor, Table, PALMA</t>
+          <t>Outdoor, Table, PALMA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11429,7 +12704,22 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Outdoor, Table, SARABI</t>
+          <t>Outdoor, Table, SARABI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11537,7 +12827,22 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Outdoor, Table, ZALIKA</t>
+          <t>Outdoor, Table, ZALIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11645,7 +12950,22 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Outdoor, Table, ZALIKA</t>
+          <t>Outdoor, Table, ZALIKA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables</t>
         </is>
       </c>
     </row>
@@ -11771,7 +13091,22 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Outdoor, Ottoman, ANTIGUA</t>
+          <t>Outdoor, Ottoman, ANTIGUA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Ottomans</t>
         </is>
       </c>
     </row>
@@ -11897,7 +13232,22 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Outdoor, Ottoman, MACKAY</t>
+          <t>Outdoor, Ottoman, MACKAY, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Ottomans</t>
         </is>
       </c>
     </row>
@@ -12023,7 +13373,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa, ANTIGUA</t>
+          <t>Outdoor, Sofa, ANTIGUA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -12152,6 +13517,21 @@
           <t>Outdoor, Patio Set, ARALI</t>
         </is>
       </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12278,6 +13658,21 @@
           <t>Outdoor, Patio Set, BARBUDA</t>
         </is>
       </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="35" t="inlineStr">
@@ -12407,6 +13802,21 @@
           <t>Outdoor, Patio Set, BASTIA</t>
         </is>
       </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="35" t="inlineStr">
@@ -12536,6 +13946,21 @@
           <t>Outdoor, Patio Set, BASTIA</t>
         </is>
       </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12667,6 +14092,21 @@
           <t>Outdoor, Patio Set, CHANDU</t>
         </is>
       </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12793,6 +14233,21 @@
           <t>Outdoor, Patio Set, FARISHA</t>
         </is>
       </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12919,6 +14374,21 @@
           <t>Outdoor, Patio Set, GENOA</t>
         </is>
       </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="62" t="inlineStr">
@@ -13048,6 +14518,21 @@
           <t>Outdoor, Patio Set, HANA</t>
         </is>
       </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="62" t="inlineStr">
@@ -13177,6 +14662,21 @@
           <t>Outdoor, Patio Set, HANA</t>
         </is>
       </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="56" t="inlineStr">
@@ -13306,6 +14806,21 @@
           <t>Outdoor, Patio Set, IBIZA</t>
         </is>
       </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="56" t="inlineStr">
@@ -13435,6 +14950,21 @@
           <t>Outdoor, Patio Set, IBIZA</t>
         </is>
       </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="29" t="inlineStr">
@@ -13568,6 +15098,21 @@
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="29" t="inlineStr">
@@ -13701,6 +15246,21 @@
           <t>Outdoor, Patio Set, KIMARA</t>
         </is>
       </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13827,6 +15387,21 @@
           <t>Outdoor, Patio Set, LOTUS</t>
         </is>
       </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13953,6 +15528,21 @@
           <t>Outdoor, Patio Set, MYESHA</t>
         </is>
       </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -14079,6 +15669,21 @@
           <t>Outdoor, Patio Set, NOTO</t>
         </is>
       </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14205,6 +15810,21 @@
           <t>Outdoor, Patio Set, PALMA</t>
         </is>
       </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14336,6 +15956,21 @@
           <t>Outdoor, Patio Set, SHANI</t>
         </is>
       </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14462,6 +16097,21 @@
           <t>Outdoor, Patio Set, SHOMARI</t>
         </is>
       </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14584,6 +16234,21 @@
           <t>Outdoor, Patio Set, TUSHARI</t>
         </is>
       </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14707,7 +16372,22 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, AREZZO</t>
+          <t>Outdoor, Dining Set, AREZZO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14833,7 +16513,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, FALLONE</t>
+          <t>Outdoor, Dining Set, FALLONE, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -14961,7 +16656,22 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, MARSHA</t>
+          <t>Outdoor, Dining Set, MARSHA, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15088,7 +16798,22 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, PIERRO</t>
+          <t>Outdoor, Dining Set, PIERRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15215,7 +16940,22 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, PIERRO</t>
+          <t>Outdoor, Dining Set, PIERRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15342,7 +17082,22 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, PIERRO</t>
+          <t>Outdoor, Dining Set, PIERRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15469,7 +17224,22 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, PIERRO</t>
+          <t>Outdoor, Dining Set, PIERRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15596,7 +17366,22 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Outdoor, Dining Set, PIERRO</t>
+          <t>Outdoor, Dining Set, PIERRO, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -15722,7 +17507,22 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Outdoor, Canopy, AROSA</t>
+          <t>Outdoor, Canopy, AROSA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Structures &gt; Canopies &amp; Gazebos &gt; Canopies</t>
         </is>
       </c>
     </row>
@@ -15848,7 +17648,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Outdoor, Canopy, GORDOLA</t>
+          <t>Outdoor, Canopy, GORDOLA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Structures &gt; Canopies &amp; Gazebos &gt; Canopies</t>
         </is>
       </c>
     </row>
@@ -15974,7 +17789,22 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Outdoor, Canopy, NESTA</t>
+          <t>Outdoor, Canopy, NESTA, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Structures &gt; Canopies &amp; Gazebos &gt; Canopies</t>
         </is>
       </c>
     </row>
@@ -16103,7 +17933,22 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Outdoor, Chaise, BAHIA TOBAGO</t>
+          <t>Outdoor, Chaise, BAHIA TOBAGO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs &gt; Chaises</t>
         </is>
       </c>
     </row>
@@ -16232,7 +18077,22 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Outdoor, Chaise, BAHIA TOBAGO</t>
+          <t>Outdoor, Chaise, BAHIA TOBAGO, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Chairs &gt; Chaises</t>
         </is>
       </c>
     </row>
@@ -16364,7 +18224,22 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Outdoor, Accessory, BOYLE</t>
+          <t>Outdoor, Accessory, BOYLE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -16496,7 +18371,22 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Outdoor, Accessory, BOYLE</t>
+          <t>Outdoor, Accessory, BOYLE, HOME DECOR &amp; ACCESSORIES</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture Accessories &gt; Outdoor Furniture Covers</t>
         </is>
       </c>
     </row>
@@ -16618,7 +18508,22 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, BRINDSMADE</t>
+          <t>Outdoor, Sofa Set, BRINDSMADE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16744,7 +18649,22 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16870,7 +18790,22 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -16996,7 +18931,22 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17122,7 +19072,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17248,7 +19213,22 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17374,7 +19354,22 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Outdoor, Sofa Set, ILONA</t>
+          <t>Outdoor, Sofa Set, ILONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17496,7 +19491,22 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Outdoor, Bar Table Set, CYPRUS</t>
+          <t>Outdoor, Bar Table Set, CYPRUS, DINING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Kitchen &amp; Dining Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -17618,7 +19628,22 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Outdoor, Sectional, DAVINA</t>
+          <t>Outdoor, Sectional, DAVINA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas &gt; Sectional Sofas</t>
         </is>
       </c>
     </row>
@@ -17740,7 +19765,22 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Outdoor, Sectional, DAVINA</t>
+          <t>Outdoor, Sectional, DAVINA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas &gt; Sectional Sofas</t>
         </is>
       </c>
     </row>
@@ -17866,7 +19906,22 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Outdoor, Sectional, SAMARA</t>
+          <t>Outdoor, Sectional, SAMARA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas &gt; Sectional Sofas</t>
         </is>
       </c>
     </row>
@@ -17992,7 +20047,22 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Outdoor, Sectional, SAN JOSE</t>
+          <t>Outdoor, Sectional, SAN JOSE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas &gt; Sectional Sofas</t>
         </is>
       </c>
     </row>
@@ -18119,7 +20189,22 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Outdoor, Sectional, WINONA</t>
+          <t>Outdoor, Sectional, WINONA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas &gt; Sectional Sofas</t>
         </is>
       </c>
     </row>
@@ -18248,6 +20333,21 @@
           <t>Outdoor, Umbrella Base, DURO</t>
         </is>
       </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrella &amp; Sunshade Accessories &gt; Outdoor Umbrella Bases</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="65" t="inlineStr">
@@ -18377,6 +20477,21 @@
           <t>Outdoor, Umbrella Base, FAB</t>
         </is>
       </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrella &amp; Sunshade Accessories &gt; Outdoor Umbrella Bases</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="65" t="inlineStr">
@@ -18506,6 +20621,21 @@
           <t>Outdoor, Umbrella Base, FAB</t>
         </is>
       </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrella &amp; Sunshade Accessories &gt; Outdoor Umbrella Bases</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -18632,6 +20762,21 @@
           <t>Outdoor, Umbrella Base, SAYA</t>
         </is>
       </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrella &amp; Sunshade Accessories &gt; Outdoor Umbrella Bases</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18756,6 +20901,21 @@
       <c r="AD144" t="inlineStr">
         <is>
           <t>Outdoor, Umbrella Base, TANGRAM</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrella &amp; Sunshade Accessories &gt; Outdoor Umbrella Bases</t>
         </is>
       </c>
     </row>
@@ -18896,6 +21056,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="38" t="inlineStr">
@@ -19032,6 +21207,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="38" t="inlineStr">
@@ -19170,6 +21360,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="38" t="inlineStr">
@@ -19306,6 +21511,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="38" t="inlineStr">
@@ -19440,6 +21660,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="38" t="inlineStr">
@@ -19576,6 +21811,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="38" t="inlineStr">
@@ -19710,6 +21960,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="38" t="inlineStr">
@@ -19846,6 +22111,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="38" t="inlineStr">
@@ -19980,6 +22260,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="38" t="inlineStr">
@@ -20116,6 +22411,21 @@
           <t>Outdoor, Umbrella, FERA</t>
         </is>
       </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="67" t="inlineStr">
@@ -20254,6 +22564,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="67" t="inlineStr">
@@ -20390,6 +22715,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="67" t="inlineStr">
@@ -20528,6 +22868,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="67" t="inlineStr">
@@ -20664,6 +23019,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="67" t="inlineStr">
@@ -20798,6 +23168,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="67" t="inlineStr">
@@ -20934,6 +23319,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="67" t="inlineStr">
@@ -21068,6 +23468,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="67" t="inlineStr">
@@ -21204,6 +23619,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="67" t="inlineStr">
@@ -21338,6 +23768,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="67" t="inlineStr">
@@ -21474,6 +23919,21 @@
           <t>Outdoor, Umbrella, FIDA</t>
         </is>
       </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -21605,6 +24065,21 @@
           <t>Outdoor, Umbrella, GLAM</t>
         </is>
       </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="46" t="inlineStr">
@@ -21734,6 +24209,21 @@
           <t>Outdoor, Umbrella, GLAM</t>
         </is>
       </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="46" t="inlineStr">
@@ -21863,6 +24353,21 @@
           <t>Outdoor, Umbrella, GLAM</t>
         </is>
       </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="46" t="inlineStr">
@@ -21992,6 +24497,21 @@
           <t>Outdoor, Umbrella, GLAM</t>
         </is>
       </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="46" t="inlineStr">
@@ -22121,6 +24641,21 @@
           <t>Outdoor, Umbrella, GLAM</t>
         </is>
       </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="46" t="inlineStr">
@@ -22250,6 +24785,21 @@
           <t>Outdoor, Umbrella, GLAM</t>
         </is>
       </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -22381,6 +24931,21 @@
           <t>Outdoor, Umbrella, HALO</t>
         </is>
       </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="52" t="inlineStr">
@@ -22510,6 +25075,21 @@
           <t>Outdoor, Umbrella, HALO</t>
         </is>
       </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="52" t="inlineStr">
@@ -22639,6 +25219,21 @@
           <t>Outdoor, Umbrella, HALO</t>
         </is>
       </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="52" t="inlineStr">
@@ -22768,6 +25363,21 @@
           <t>Outdoor, Umbrella, HALO</t>
         </is>
       </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="52" t="inlineStr">
@@ -22897,6 +25507,21 @@
           <t>Outdoor, Umbrella, HALO</t>
         </is>
       </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="52" t="inlineStr">
@@ -23024,6 +25649,21 @@
       <c r="AD176" t="inlineStr">
         <is>
           <t>Outdoor, Umbrella, HALO</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
         </is>
       </c>
     </row>
@@ -23164,6 +25804,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="54" t="inlineStr">
@@ -23300,6 +25955,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="54" t="inlineStr">
@@ -23438,6 +26108,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="54" t="inlineStr">
@@ -23574,6 +26259,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="54" t="inlineStr">
@@ -23708,6 +26408,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="54" t="inlineStr">
@@ -23844,6 +26559,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="54" t="inlineStr">
@@ -23978,6 +26708,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="54" t="inlineStr">
@@ -24114,6 +26859,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="54" t="inlineStr">
@@ -24248,6 +27008,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="54" t="inlineStr">
@@ -24384,6 +27159,21 @@
           <t>Outdoor, Umbrella, HERO</t>
         </is>
       </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="48" t="inlineStr">
@@ -24515,6 +27305,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="48" t="inlineStr">
@@ -24646,6 +27451,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="48" t="inlineStr">
@@ -24777,6 +27597,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="24" t="inlineStr">
@@ -24910,6 +27745,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="24" t="inlineStr">
@@ -25041,6 +27891,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="24" t="inlineStr">
@@ -25174,6 +28039,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="24" t="inlineStr">
@@ -25305,6 +28185,21 @@
           <t>Outdoor, Umbrella, LALI</t>
         </is>
       </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="38" t="inlineStr">
@@ -25434,6 +28329,21 @@
           <t>Outdoor, Umbrella, MORA</t>
         </is>
       </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="38" t="inlineStr">
@@ -25563,6 +28473,21 @@
           <t>Outdoor, Umbrella, MORA</t>
         </is>
       </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="38" t="inlineStr">
@@ -25692,6 +28617,21 @@
           <t>Outdoor, Umbrella, MORA</t>
         </is>
       </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="67" t="inlineStr">
@@ -25821,6 +28761,21 @@
           <t>Outdoor, Umbrella, MUSA</t>
         </is>
       </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="67" t="inlineStr">
@@ -25948,6 +28903,21 @@
       <c r="AD198" t="inlineStr">
         <is>
           <t>Outdoor, Umbrella, MUSA</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
         </is>
       </c>
     </row>
@@ -26088,6 +29058,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="59" t="inlineStr">
@@ -26224,6 +29209,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="59" t="inlineStr">
@@ -26362,6 +29362,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="59" t="inlineStr">
@@ -26498,6 +29513,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="59" t="inlineStr">
@@ -26632,6 +29662,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="59" t="inlineStr">
@@ -26768,6 +29813,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="59" t="inlineStr">
@@ -26902,6 +29962,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="59" t="inlineStr">
@@ -27038,6 +30113,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="59" t="inlineStr">
@@ -27172,6 +30262,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="59" t="inlineStr">
@@ -27308,6 +30413,21 @@
           <t>Outdoor, Umbrella, NUTI</t>
         </is>
       </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="35" t="inlineStr">
@@ -27446,6 +30566,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="35" t="inlineStr">
@@ -27582,6 +30717,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="35" t="inlineStr">
@@ -27720,6 +30870,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="35" t="inlineStr">
@@ -27856,6 +31021,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="35" t="inlineStr">
@@ -27990,6 +31170,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="35" t="inlineStr">
@@ -28126,6 +31321,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="35" t="inlineStr">
@@ -28260,6 +31470,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="35" t="inlineStr">
@@ -28396,6 +31621,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="35" t="inlineStr">
@@ -28530,6 +31770,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="35" t="inlineStr">
@@ -28666,6 +31921,21 @@
           <t>Outdoor, Umbrella, SANO</t>
         </is>
       </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="24" t="inlineStr">
@@ -28795,6 +32065,21 @@
           <t>Outdoor, Umbrella, SLEEK</t>
         </is>
       </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="24" t="inlineStr">
@@ -28924,6 +32209,21 @@
           <t>Outdoor, Umbrella, SLEEK</t>
         </is>
       </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="24" t="inlineStr">
@@ -29053,6 +32353,21 @@
           <t>Outdoor, Umbrella, SLEEK</t>
         </is>
       </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="24" t="inlineStr">
@@ -29182,6 +32497,21 @@
           <t>Outdoor, Umbrella, SLEEK</t>
         </is>
       </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="24" t="inlineStr">
@@ -29311,6 +32641,21 @@
           <t>Outdoor, Umbrella, SLEEK</t>
         </is>
       </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="31" t="inlineStr">
@@ -29442,6 +32787,21 @@
           <t>Outdoor, Umbrella, SOLI</t>
         </is>
       </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="31" t="inlineStr">
@@ -29573,6 +32933,21 @@
           <t>Outdoor, Umbrella, SOLI</t>
         </is>
       </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="31" t="inlineStr">
@@ -29704,6 +33079,21 @@
           <t>Outdoor, Umbrella, SOLI</t>
         </is>
       </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="65" t="inlineStr">
@@ -29833,6 +33223,21 @@
           <t>Outdoor, Umbrella, SOLI</t>
         </is>
       </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="65" t="inlineStr">
@@ -29962,6 +33367,21 @@
           <t>Outdoor, Umbrella, SOLI</t>
         </is>
       </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="65" t="inlineStr">
@@ -30091,6 +33511,21 @@
           <t>Outdoor, Umbrella, SOLI</t>
         </is>
       </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="38" t="inlineStr">
@@ -30220,6 +33655,21 @@
           <t>Outdoor, Umbrella, TANO</t>
         </is>
       </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="38" t="inlineStr">
@@ -30351,6 +33801,21 @@
           <t>Outdoor, Umbrella, TANO</t>
         </is>
       </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="38" t="inlineStr">
@@ -30480,6 +33945,21 @@
           <t>Outdoor, Umbrella, TANO</t>
         </is>
       </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="38" t="inlineStr">
@@ -30611,6 +34091,21 @@
           <t>Outdoor, Umbrella, TANO</t>
         </is>
       </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="38" t="inlineStr">
@@ -30740,6 +34235,21 @@
           <t>Outdoor, Umbrella, TANO</t>
         </is>
       </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="38" t="inlineStr">
@@ -30869,6 +34379,21 @@
       <c r="AD235" t="inlineStr">
         <is>
           <t>Outdoor, Umbrella, TANO</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
         </is>
       </c>
     </row>
@@ -31009,6 +34534,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="67" t="inlineStr">
@@ -31145,6 +34685,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="67" t="inlineStr">
@@ -31283,6 +34838,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="67" t="inlineStr">
@@ -31419,6 +34989,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="67" t="inlineStr">
@@ -31553,6 +35138,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="67" t="inlineStr">
@@ -31689,6 +35289,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="67" t="inlineStr">
@@ -31823,6 +35438,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="67" t="inlineStr">
@@ -31959,6 +35589,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="67" t="inlineStr">
@@ -32093,6 +35738,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="67" t="inlineStr">
@@ -32229,6 +35889,21 @@
           <t>Outdoor, Umbrella, XICO</t>
         </is>
       </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Outdoor Umbrellas &amp; Sunshades &gt; Outdoor Umbrellas</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="59" t="inlineStr">
@@ -32356,6 +36031,21 @@
           <t>Outdoor, Hammock, HALEY</t>
         </is>
       </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Hammocks</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="59" t="inlineStr">
@@ -32487,6 +36177,21 @@
           <t>Outdoor, Hammock, HALEY</t>
         </is>
       </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Lawn &amp; Garden &gt; Outdoor Living &gt; Hammocks</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -32610,7 +36315,22 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
-          <t>Outdoor, Shelf, IMBLER</t>
+          <t>Outdoor, Shelf, IMBLER, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Shelving &gt; Bookcases &amp; Standing Shelves</t>
         </is>
       </c>
     </row>
@@ -32736,7 +36456,22 @@
       </c>
       <c r="AD249" t="inlineStr">
         <is>
-          <t>Outdoor, Shelf, POTTER</t>
+          <t>Outdoor, Shelf, POTTER, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Shelving &gt; Bookcases &amp; Standing Shelves</t>
         </is>
       </c>
     </row>
@@ -32862,7 +36597,22 @@
       </c>
       <c r="AD250" t="inlineStr">
         <is>
-          <t>Outdoor, Shelf, TIMBER</t>
+          <t>Outdoor, Shelf, TIMBER, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Shelving &gt; Bookcases &amp; Standing Shelves</t>
         </is>
       </c>
     </row>
@@ -32988,7 +36738,22 @@
       </c>
       <c r="AD251" t="inlineStr">
         <is>
-          <t>Outdoor, Shelf, WATTER</t>
+          <t>Outdoor, Shelf, WATTER, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Shelving &gt; Bookcases &amp; Standing Shelves</t>
         </is>
       </c>
     </row>
@@ -33092,7 +36857,22 @@
       </c>
       <c r="AD252" t="inlineStr">
         <is>
-          <t>Outdoor, Coffee Table, JOHARI</t>
+          <t>Outdoor, Coffee Table, JOHARI, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Tables &gt; Accent Tables &gt; Coffee Tables</t>
         </is>
       </c>
     </row>
@@ -33218,7 +36998,22 @@
       </c>
       <c r="AD253" t="inlineStr">
         <is>
-          <t>Outdoor, Bed, KESI</t>
+          <t>Outdoor, Bed, KESI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Beds &amp; Accessories &gt; Beds &amp; Bed Frames</t>
         </is>
       </c>
     </row>
@@ -33347,7 +37142,22 @@
       </c>
       <c r="AD254" t="inlineStr">
         <is>
-          <t>Outdoor, Table Set, KYUSHU</t>
+          <t>Outdoor, Table Set, KYUSHU, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33476,7 +37286,22 @@
       </c>
       <c r="AD255" t="inlineStr">
         <is>
-          <t>Outdoor, Table Set, KYUSHU</t>
+          <t>Outdoor, Table Set, KYUSHU, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33605,7 +37430,22 @@
       </c>
       <c r="AD256" t="inlineStr">
         <is>
-          <t>Outdoor, Table Set, LOTUS</t>
+          <t>Outdoor, Table Set, LOTUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33734,7 +37574,22 @@
       </c>
       <c r="AD257" t="inlineStr">
         <is>
-          <t>Outdoor, Table Set, LOTUS</t>
+          <t>Outdoor, Table Set, LOTUS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -33866,6 +37721,21 @@
           <t>Outdoor, Patio Dining Table, MACKAY</t>
         </is>
       </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="65" t="inlineStr">
@@ -33995,6 +37865,21 @@
           <t>Outdoor, Patio Dining Table, MACKAY</t>
         </is>
       </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -34121,6 +38006,21 @@
           <t>Outdoor, Patio Dining Table, MALIA</t>
         </is>
       </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="48" t="inlineStr">
@@ -34250,6 +38150,21 @@
           <t>Outdoor, Patio Dining Table, SINTRA</t>
         </is>
       </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="48" t="inlineStr">
@@ -34379,6 +38294,21 @@
           <t>Outdoor, Patio Dining Table, SINTRA</t>
         </is>
       </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Dining Tables</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -34502,7 +38432,22 @@
       </c>
       <c r="AD263" t="inlineStr">
         <is>
-          <t>Outdoor, Sectional Set, MALIA</t>
+          <t>Outdoor, Sectional Set, MALIA, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Furniture Sets &gt; Living Room Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -34524,7 +38469,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Daybed</t>
+          <t>Day Bed</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -34628,7 +38573,22 @@
       </c>
       <c r="AD264" t="inlineStr">
         <is>
-          <t>Outdoor, Daybed, MAUI</t>
+          <t>Outdoor, Day Bed, MAUI, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Daybeds</t>
         </is>
       </c>
     </row>
@@ -34650,7 +38610,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Daybed</t>
+          <t>Day Bed</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -34754,7 +38714,22 @@
       </c>
       <c r="AD265" t="inlineStr">
         <is>
-          <t>Outdoor, Daybed, VELDEN</t>
+          <t>Outdoor, Day Bed, VELDEN, BEDROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Daybeds</t>
         </is>
       </c>
     </row>
@@ -34880,7 +38855,22 @@
       </c>
       <c r="AD266" t="inlineStr">
         <is>
-          <t>Outdoor, Storage, MOSIER</t>
+          <t>Outdoor, Storage, MOSIER, OFFICE FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Cabinets &amp; Storage</t>
         </is>
       </c>
     </row>
@@ -35010,6 +39000,21 @@
           <t>Outdoor, Patio Table, NIAMBI</t>
         </is>
       </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="46" t="inlineStr">
@@ -35137,6 +39142,21 @@
           <t>Outdoor, Patio Table, NIAMBI</t>
         </is>
       </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -35263,6 +39283,21 @@
           <t>Outdoor, Patio Table, ZUBERI</t>
         </is>
       </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -35385,6 +39420,21 @@
           <t>Outdoor, Conversation Set, OLIVERI</t>
         </is>
       </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -35501,6 +39551,21 @@
       <c r="AD271" t="inlineStr">
         <is>
           <t>Outdoor, Conversation Set, OLIVERI</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Furniture Sets</t>
         </is>
       </c>
     </row>
@@ -35629,6 +39694,21 @@
           <t>Outdoor, Fire Pit Table, SEGOVIA</t>
         </is>
       </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture &gt; Outdoor Tables &gt; Fire Pits</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -35752,7 +39832,22 @@
       </c>
       <c r="AD273" t="inlineStr">
         <is>
-          <t>Outdoor, Stand, WAVE</t>
+          <t>Outdoor, Stand, WAVE, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Outdoor Furniture</t>
         </is>
       </c>
     </row>

--- a/FOA Singles/Outdoor-Single.xlsx
+++ b/FOA Singles/Outdoor-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2076,7 +2076,7 @@
       <c r="G11" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZALIKA Patio Bench is designed to complement your space with a balanced, versatile look. This outdoor bench is made to fit naturally into the room.&lt;br&gt;
+ZALIKA Patio Bench is designed to complement your space with a balanced, versatile look. As a outdoor bench, it is designed to complement your space.&lt;br&gt;
 Product Dimensions: 51.5"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;</t>
         </is>
       </c>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2206,8 +2206,8 @@
 ALVERTA Foldable Chair adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 33 1/2"W X 28 1/4"D X 57"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 53.57 lbs&lt;/p&gt;</t>
+Color: Black or Light Gray&lt;br&gt;
+Weight: 53.57 or 53.37 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2347,11 +2347,11 @@
       <c r="G13" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ALVERTA Foldable Chair and its Modern character. As a outdoor chair, it is designed to complement your space. Finished in Light Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+ALVERTA Foldable Chair adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 33 1/2"W X 28 1/4"D X 57"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
-Weight: 53.37 lbs&lt;/p&gt;</t>
+Color: Black or Light Gray&lt;br&gt;
+Weight: 53.57 or 53.37 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H13" s="29" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3336,7 +3336,7 @@
 BREEZE Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 28"W X 34 1/4"D X 46"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 31.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3477,10 +3477,10 @@
       <c r="G21" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BREEZE Swing Chair and its Modern character. Built as a outdoor chair, it pairs well with a wide range of interiors. Finished in Dark Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+BREEZE Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 28"W X 34 1/4"D X 46"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 31.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3621,10 +3621,10 @@
       <c r="G22" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BREEZE Swing Chair brings a Modern look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Steel, Mesh, Fabric construction is complemented by Light Gray tones for a polished look.&lt;br&gt;
+BREEZE Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Steel, Mesh, Fabric, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 28"W X 34 1/4"D X 46"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 31.08 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3768,7 +3768,7 @@
 Elevate your space with CRUSH Swing Chair, styled in Modern and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel, Mesh, Fabric and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 27.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3909,10 +3909,10 @@
       <c r="G24" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CRUSH Swing Chair adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel, Mesh, Fabric, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with CRUSH Swing Chair, styled in Modern and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel, Mesh, Fabric and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 27.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4053,10 +4053,10 @@
       <c r="G25" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CRUSH Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Light Gray tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with CRUSH Swing Chair, styled in Modern and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Steel, Mesh, Fabric and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 28 1/4"W X 29 1/2"D X 43 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Light Gray&lt;br&gt;
+Color: Black or Dark Gray or Light Gray&lt;br&gt;
 Weight: 27.78 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4341,7 +4341,7 @@
 Elevate your space with ELK Adirondrack Chair, styled in Rustic and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Eucalyptus Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
-Color: Dark Brown&lt;br&gt;
+Color: Dark Brown or Gray or Natural or Weathered Gray&lt;br&gt;
 Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4482,10 +4482,10 @@
       <c r="G28" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELK Adirondrack Chair adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Eucalyptus Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with ELK Adirondrack Chair, styled in Rustic and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Eucalyptus Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Dark Brown or Gray or Natural or Weathered Gray&lt;br&gt;
 Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4626,10 +4626,10 @@
       <c r="G29" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ELK Adirondrack Chair and its Rustic character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with ELK Adirondrack Chair, styled in Rustic and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Eucalyptus Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
-Color: Natural&lt;br&gt;
+Color: Dark Brown or Gray or Natural or Weathered Gray&lt;br&gt;
 Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4770,10 +4770,10 @@
       <c r="G30" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ELK Adirondrack Chair brings a Rustic look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Eucalyptus Wood construction is complemented by Weathered Gray tones for a polished look.&lt;br&gt;
+Elevate your space with ELK Adirondrack Chair, styled in Rustic and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Eucalyptus Wood and Dark Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 34"W X 27 1/2"D X 35 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Eucalyptus Wood.&lt;br&gt;
-Color: Weathered Gray&lt;br&gt;
+Color: Dark Brown or Gray or Natural or Weathered Gray&lt;br&gt;
 Weight: 26.46 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5607,7 +5607,7 @@
 Make the room feel complete with KYUSHU Chair (2 / CTN) and its Rustic character. As a outdoor chair, it is designed to complement your space. Finished in Beige or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Beige or Natural&lt;br&gt;
+Color: Beige or Natural or Black or Natural&lt;br&gt;
 Weight: 68.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -5748,10 +5748,10 @@
       <c r="G37" s="50" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KYUSHU Chair (2 / CTN) brings a Rustic look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Acacia Wood, Polyester construction is complemented by Black or Natural tones for a polished look.&lt;br&gt;
+Make the room feel complete with KYUSHU Chair (2 / CTN) and its Rustic character. As a outdoor chair, it is designed to complement your space. Finished in Beige or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: CHAIR: 24"W X 27 1/4"D X 34 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Black or Natural&lt;br&gt;
+Color: Beige or Natural or Black or Natural&lt;br&gt;
 Weight: 68.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6741,8 +6741,8 @@
 NYA Patio Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 25"W X 23.5"D X 31"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 25.9 lbs&lt;/p&gt;</t>
+Color: Black or Natural&lt;br&gt;
+Weight: 25.9 or 9.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H44" s="52" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -6882,11 +6882,11 @@
       <c r="G45" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with NYA Patio Chair (2 / CTN) and its Contemporary character. This outdoor chair is made to fit naturally into the room. Finished in Natural tones, the Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam build balances durability with visual appeal.&lt;br&gt;
+NYA Patio Chair (2 / CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor chair, it is designed to complement your space. Crafted from Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 25"W X 23.5"D X 31"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
-Color: Natural&lt;br&gt;
-Weight: 9.6 lbs&lt;/p&gt;</t>
+Color: Black or Natural&lt;br&gt;
+Weight: 25.9 or 9.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H45" s="52" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8013,7 +8013,7 @@
 Elevate your space with PIERRO Stacking Chair (2 or Stack), styled in Transitional and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Glass, Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8154,10 +8154,10 @@
       <c r="G54" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PIERRO Stacking Chair (2 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. This outdoor chair is made to fit naturally into the room. Crafted from Glass, Metal, Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with PIERRO Stacking Chair (2 or Stack), styled in Transitional and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Glass, Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8298,10 +8298,10 @@
       <c r="G55" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with PIERRO Stacking Chair (2 or Stack) and its Transitional character. Built as a outdoor chair, it pairs well with a wide range of interiors. Finished in Beige tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with PIERRO Stacking Chair (2 or Stack), styled in Transitional and designed for everyday comfort. As a outdoor chair, it is designed to complement your space. With Glass, Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8445,7 +8445,7 @@
 PIERRO Stacking Chair (28 or Stack) brings a Transitional look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Glass, Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;/p&gt;</t>
+Color: Blue or Red or Beige&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H56" s="56" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8583,10 +8583,10 @@
       <c r="G57" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PIERRO Stacking Chair (28 or Stack), styled in Transitional and designed for everyday comfort. This outdoor chair is made to fit naturally into the room. With Glass, Metal, Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+PIERRO Stacking Chair (28 or Stack) brings a Transitional look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Glass, Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Red&lt;/p&gt;</t>
+Color: Blue or Red or Beige&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H57" s="56" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -8724,10 +8724,10 @@
       <c r="G58" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PIERRO Stacking Chair (28 or Stack) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a outdoor chair, it pairs well with a wide range of interiors. Crafted from Glass, Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+PIERRO Stacking Chair (28 or Stack) brings a Transitional look to your home with a refined, comfortable feel. As a outdoor chair, it is designed to complement your space. The Glass, Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;/p&gt;</t>
+Color: Blue or Red or Beige&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H58" s="56" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -8868,7 +8868,7 @@
 Make the room feel complete with PIERRO Stacking Chair (4 or Stack) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 48 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9013,10 +9013,10 @@
       <c r="G60" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PIERRO Stacking Chair (4 or Stack) brings a Transitional look to your home with a refined, comfortable feel. This outdoor chair is made to fit naturally into the room. The Glass, Metal, Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Make the room feel complete with PIERRO Stacking Chair (4 or Stack) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 48 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9161,10 +9161,10 @@
       <c r="G61" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PIERRO Stacking Chair (4 or Stack), styled in Transitional and designed for everyday comfort. Built as a outdoor chair, it pairs well with a wide range of interiors. With Glass, Metal, Fabric and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with PIERRO Stacking Chair (4 or Stack) and its Transitional character. As a outdoor chair, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 23"L X 29"W X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 48 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9312,7 +9312,7 @@
 Make the room feel complete with SANDOR Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Black tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 65 1/2"W X 57"D X 74 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 59.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9453,10 +9453,10 @@
       <c r="G63" s="50" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANDOR Swing Chair brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor chair, it pairs well with a wide range of interiors. The Steel, Mesh, Fabric construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with SANDOR Swing Chair and its Modern character. This outdoor chair is made to fit naturally into the room. Finished in Black tones, the Steel, Mesh, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 65 1/2"W X 57"D X 74 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Mesh, Fabric.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 59.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -10684,7 +10684,7 @@
       <c r="G72" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZALIKA Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. As a outdoor chair, it is designed to complement your space.&lt;br&gt;
+ZALIKA Patio Chair (2 / CTN) is designed to complement your space with a balanced, versatile look. Built as a outdoor chair, it pairs well with a wide range of interiors.&lt;br&gt;
 Product Dimensions: 22"W X 26.5"D X 35"H (SEAT HT: 19.5"; SEAT DP: 18")&lt;/p&gt;</t>
         </is>
       </c>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -12872,7 +12872,7 @@
       <c r="G88" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZALIKA Patio Side Table is designed to complement your space with a balanced, versatile look. Built as a outdoor table, it pairs well with a wide range of interiors.&lt;br&gt;
+ZALIKA Patio Side Table is designed to complement your space with a balanced, versatile look. This outdoor table is made to fit naturally into the room.&lt;br&gt;
 Product Dimensions: 19.5"W X 19.5"D X 21"H&lt;/p&gt;</t>
         </is>
       </c>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -13707,7 +13707,7 @@
 BASTIA 3 Pc. Conversation Set adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor patio set is made to fit naturally into the room. Crafted from Metal, Glass, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: Table: 19.5"W X 19.5"D X 17.5"H, Chair: 26.5"D X 29"D X 36.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Teal&lt;br&gt;
 Weight: 37.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -13848,10 +13848,10 @@
       <c r="G95" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BASTIA 3 Pc. Conversation Set and its Contemporary character. Built as a outdoor patio set, it pairs well with a wide range of interiors. Finished in Teal tones, the Metal, Glass, Fabric build balances durability with visual appeal.&lt;br&gt;
+BASTIA 3 Pc. Conversation Set adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor patio set is made to fit naturally into the room. Crafted from Metal, Glass, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: Table: 19.5"W X 19.5"D X 17.5"H, Chair: 26.5"D X 29"D X 36.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
+Color: Beige or Teal&lt;br&gt;
 Weight: 37.47 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14423,7 +14423,7 @@
 Make the room feel complete with HANA 4 Pc. Patio Set and its Rustic character. This outdoor patio set is made to fit naturally into the room. Finished in Denim Blue or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: TABLE: 29 1/2"L X 19 3/4"W X 13"H, LOVESEAT: 47 1/2"L X 24"W X 32"H, CHAIR: 23 3/4"W X 24"D X 32"H&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Denim Blue or Natural&lt;br&gt;
+Color: Denim Blue or Natural or Brown or Natural&lt;br&gt;
 Weight: 85.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -14564,10 +14564,10 @@
       <c r="G100" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HANA 4 Pc. Patio Set brings a Rustic look to your home with a refined, comfortable feel. Built as a outdoor patio set, it pairs well with a wide range of interiors. The Acacia Wood, Polyester construction is complemented by Brown or Natural tones for a polished look.&lt;br&gt;
+Make the room feel complete with HANA 4 Pc. Patio Set and its Rustic character. This outdoor patio set is made to fit naturally into the room. Finished in Denim Blue or Natural tones, the Acacia Wood, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: TABLE: 29 1/2"L X 19 3/4"W X 13"H, LOVESEAT: 47 1/2"L X 24"W X 32"H, CHAIR: 23 3/4"W X 24"D X 32"H&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Brown or Natural&lt;br&gt;
+Color: Denim Blue or Natural or Brown or Natural&lt;br&gt;
 Weight: 85.98 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -14711,7 +14711,7 @@
 IBIZA 4 Pc. Sling Set adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Glass, Fabric, it is finished in Green tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: Table: 33"W X 19"D X 15.5"H, Bench: 42"W X 24.5"D X 30.5"H, Chair: 24.5"W X 23.5"D X 30.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
-Color: Green&lt;br&gt;
+Color: Green or Light Brown&lt;br&gt;
 Weight: 66.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -14852,10 +14852,10 @@
       <c r="G102" s="56" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with IBIZA 4 Pc. Sling Set and its Contemporary character. This outdoor patio set is made to fit naturally into the room. Finished in Light Brown tones, the Metal, Glass, Fabric build balances durability with visual appeal.&lt;br&gt;
+IBIZA 4 Pc. Sling Set adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio set, it is designed to complement your space. Crafted from Metal, Glass, Fabric, it is finished in Green tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: Table: 33"W X 19"D X 15.5"H, Bench: 42"W X 24.5"D X 30.5"H, Chair: 24.5"W X 23.5"D X 30.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Fabric.&lt;br&gt;
-Color: Light Brown&lt;br&gt;
+Color: Green or Light Brown&lt;br&gt;
 Weight: 66.13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15000,7 +15000,7 @@
 Product Dimensions: 56.7"L X 29.13"W X 26.77"H&lt;/p&gt;
 &lt;p&gt;Materials: Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
 Color: Black or Gray&lt;br&gt;
-Weight: 30.8 lbs&lt;/p&gt;</t>
+Weight: 30.8 or 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="29" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15144,11 +15144,11 @@
       <c r="G104" s="29" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KIMARA Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor patio set, it pairs well with a wide range of interiors. Crafted from Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam, it is finished in Black or Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with KIMARA Dining Table, styled in Contemporary and designed for everyday comfort. This outdoor patio set is made to fit naturally into the room. With Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 56.7"L X 29.13"W X 26.77"H&lt;/p&gt;
 &lt;p&gt;Materials: Powder-Coated Steel Frame, PE Rattan Wicker, Polyester Fabric, Foam.&lt;br&gt;
 Color: Black or Gray&lt;br&gt;
-Weight: 33 lbs&lt;/p&gt;</t>
+Weight: 30.8 or 33 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="29" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -16708,7 +16708,7 @@
 Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -16847,10 +16847,10 @@
       <c r="G116" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PIERRO 5 Pc. Outdoor Dining Set brings a Transitional look to your home with a refined, comfortable feel. This outdoor dining set is made to fit naturally into the room. The Glass, Metal, Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -16989,10 +16989,10 @@
       <c r="G117" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PIERRO 5 Pc. Outdoor Dining Set, styled in Transitional and designed for everyday comfort. Built as a outdoor dining set, it pairs well with a wide range of interiors. With Glass, Metal, Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -17131,10 +17131,10 @@
       <c r="G118" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PIERRO 5 Pc. Outdoor Dining Set adds a Transitional touch while keeping the room feeling warm and welcoming. As a outdoor dining set, it is designed to complement your space. Crafted from Glass, Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -17273,10 +17273,10 @@
       <c r="G119" s="62" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. This outdoor dining set is made to fit naturally into the room. Finished in Beige tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with PIERRO 5 Pc. Outdoor Dining Set and its Transitional character. As a outdoor dining set, it is designed to complement your space. Finished in Blue tones, the Glass, Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: Table: 59"W X 36"D X 28"H, Chair: 23"D X 29"D X 37"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 105.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -17841,7 +17841,7 @@
 BAHIA TOBAGO Reclining Chaise Lounge adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chaise is made to fit naturally into the room. Crafted from Steel, FSC Certified 100% Teak Wood, Polyspun, it is finished in Brown or Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: LOVESEAT: 46"L X 36 1/2"W X 29"H, BENCH: 39 1/2"W X 11 3/4"D X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, FSC Certified 100% Teak Wood, Polyspun.&lt;br&gt;
-Color: Brown or Dark Gray&lt;br&gt;
+Color: Brown or Dark Gray or Gray&lt;br&gt;
 Weight: 97 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -17982,10 +17982,10 @@
       <c r="G124" s="50" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BAHIA TOBAGO Reclining Chaise Lounge and its Contemporary character. Built as a outdoor chaise, it pairs well with a wide range of interiors. Finished in Gray tones, the Steel, FSC Certified 100% Teak Wood, Polyspun build balances durability with visual appeal.&lt;br&gt;
+BAHIA TOBAGO Reclining Chaise Lounge adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor chaise is made to fit naturally into the room. Crafted from Steel, FSC Certified 100% Teak Wood, Polyspun, it is finished in Brown or Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: LOVESEAT: 46"L X 36 1/2"W X 29"H, BENCH: 39 1/2"W X 11 3/4"D X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, FSC Certified 100% Teak Wood, Polyspun.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Brown or Dark Gray or Gray&lt;br&gt;
 Weight: 97 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -18785,7 +18785,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -20381,9 +20381,9 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with FAB Round Umbrella Base and its Contemporary character. Built as a outdoor umbrella base, it pairs well with a wide range of interiors. Finished in Black tones, the Plastic or High Density Polyethelene (HDPE) build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17 3/4"DIA X 6 1/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Plastic or High Density Polyethelene (HDPE).&lt;br&gt;
+&lt;p&gt;Materials: Plastic/High Density Polyethelene (HDPE).&lt;br&gt;
 Color: Black&lt;br&gt;
-Weight: 5.95 lbs&lt;/p&gt;</t>
+Weight: 5.95 or 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" s="65" t="inlineStr">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -20523,11 +20523,11 @@
       <c r="G142" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FAB Round Umbrella Base brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella base, it is designed to complement your space. The Plastic or High Density Polyethelene (HDPE) construction is complemented by Black tones for a polished look.&lt;br&gt;
+Make the room feel complete with FAB Round Umbrella Base and its Contemporary character. Built as a outdoor umbrella base, it pairs well with a wide range of interiors. Finished in Black tones, the Plastic or High Density Polyethelene (HDPE) build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17 3/4"DIA X 6 1/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Plastic or High Density Polyethelene (HDPE).&lt;br&gt;
+&lt;p&gt;Materials: Plastic/High Density Polyethelene (HDPE).&lt;br&gt;
 Color: Black&lt;br&gt;
-Weight: 6 lbs&lt;/p&gt;</t>
+Weight: 5.95 or 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="65" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -20895,7 +20895,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -20957,8 +20957,8 @@
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 48.5 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H145" s="38" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -21106,12 +21106,12 @@
       <c r="G146" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 64.1 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H146" s="38" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -21257,12 +21257,12 @@
       <c r="G147" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FERA 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 48.5 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H147" s="38" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -21410,12 +21410,12 @@
       <c r="G148" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FERA 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Blue tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 64.1 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H148" s="38" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -21561,12 +21561,12 @@
       <c r="G149" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 48.5 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H149" s="38" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -21710,12 +21710,12 @@
       <c r="G150" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 64.1 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H150" s="38" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -21861,12 +21861,12 @@
       <c r="G151" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FERA 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 48.5 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H151" s="38" t="inlineStr">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -22010,12 +22010,12 @@
       <c r="G152" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FERA 10' Round Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Red tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 64.1 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H152" s="38" t="inlineStr">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -22161,12 +22161,12 @@
       <c r="G153" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 48.5 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H153" s="38" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -22310,12 +22310,12 @@
       <c r="G154" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FERA 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FERA 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Bulb&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 64.1 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 48.5 or 64.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H154" s="38" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -22465,8 +22465,8 @@
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H155" s="67" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -22614,12 +22614,12 @@
       <c r="G156" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H156" s="67" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -22765,12 +22765,12 @@
       <c r="G157" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FIDA 8' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H157" s="67" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -22918,12 +22918,12 @@
       <c r="G158" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FIDA 8' Square Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H158" s="67" t="inlineStr">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -23069,12 +23069,12 @@
       <c r="G159" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H159" s="67" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23218,12 +23218,12 @@
       <c r="G160" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H160" s="67" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -23369,12 +23369,12 @@
       <c r="G161" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FIDA 8' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H161" s="67" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -23518,12 +23518,12 @@
       <c r="G162" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FIDA 8' Square Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H162" s="67" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -23669,12 +23669,12 @@
       <c r="G163" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Teal tones that pair easily with surrounding decor.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H163" s="67" t="inlineStr">
@@ -23760,7 +23760,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -23818,12 +23818,12 @@
       <c r="G164" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FIDA 8' Square Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+FIDA 8' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H164" s="67" t="inlineStr">
@@ -23911,7 +23911,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -24114,7 +24114,7 @@
 GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Black or White&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -24255,10 +24255,10 @@
       <c r="G167" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with GLAM Cantilever Umbrella w/ LED and its Modern character. This outdoor umbrella is made to fit naturally into the room. Finished in Canvas Stone tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Canvas Stone&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -24399,10 +24399,10 @@
       <c r="G168" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GLAM Cantilever Umbrella w/ LED brings a Modern look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Steel, Polyester construction is complemented by Dark Sapphire tones for a polished look.&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Dark Sapphire&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -24543,10 +24543,10 @@
       <c r="G169" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with GLAM Cantilever Umbrella w/ LED, styled in Modern and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Steel, Polyester and Graphite tones, it blends structure and softness in one clean profile.&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Graphite&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -24633,7 +24633,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -24687,10 +24687,10 @@
       <c r="G170" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Light Sapphire tones that pair easily with surrounding decor.&lt;br&gt;
+GLAM Cantilever Umbrella w/ LED adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 118"DIA X 98 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Light Sapphire&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 24.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -24980,7 +24980,7 @@
 HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Black or White&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -25121,10 +25121,10 @@
       <c r="G173" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HALO Round Umbrella and its Modern character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Canvas Stone tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Canvas Stone&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25211,7 +25211,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -25265,10 +25265,10 @@
       <c r="G174" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HALO Round Umbrella brings a Modern look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Steel, Polyester construction is complemented by Dark Sapphire tones for a polished look.&lt;br&gt;
+HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Dark Sapphire&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25355,7 +25355,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -25409,10 +25409,10 @@
       <c r="G175" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HALO Round Umbrella, styled in Modern and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Steel, Polyester and Graphite tones, it blends structure and softness in one clean profile.&lt;br&gt;
+HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Graphite&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25499,7 +25499,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -25553,10 +25553,10 @@
       <c r="G176" s="52" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Steel, Polyester, it is finished in Light Sapphire tones that pair easily with surrounding decor.&lt;br&gt;
+HALO Round Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Steel, Polyester, it is finished in Black or White tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 106 1/4"DIA X 94 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Light Sapphire&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25643,7 +25643,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -25705,8 +25705,8 @@
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H177" s="54" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -25854,12 +25854,12 @@
       <c r="G178" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H178" s="54" t="inlineStr">
@@ -25947,7 +25947,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -26005,12 +26005,12 @@
       <c r="G179" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HERO 10' Square Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H179" s="54" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -26158,12 +26158,12 @@
       <c r="G180" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HERO 10' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" s="54" t="inlineStr">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -26309,12 +26309,12 @@
       <c r="G181" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" s="54" t="inlineStr">
@@ -26400,7 +26400,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -26458,12 +26458,12 @@
       <c r="G182" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H182" s="54" t="inlineStr">
@@ -26551,7 +26551,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -26609,12 +26609,12 @@
       <c r="G183" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HERO 10' Square Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H183" s="54" t="inlineStr">
@@ -26700,7 +26700,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -26758,12 +26758,12 @@
       <c r="G184" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HERO 10' Square Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H184" s="54" t="inlineStr">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -26909,12 +26909,12 @@
       <c r="G185" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H185" s="54" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -27058,12 +27058,12 @@
       <c r="G186" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HERO 10' Square Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+Make the room feel complete with HERO 10' Square Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: Double Top&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H186" s="54" t="inlineStr">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -27207,8 +27207,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LALI 11' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Fabric, Steel, construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Blue&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 67.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27297,7 +27297,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -27351,10 +27351,10 @@
       <c r="G188" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with LALI 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Fabric, Steel, and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+LALI 11' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Fabric, Steel, construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Red&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 67.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27443,7 +27443,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -27497,10 +27497,10 @@
       <c r="G189" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LALI 11' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Fabric, Steel, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+LALI 11' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Fabric, Steel, construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Beige&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 67.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27589,7 +27589,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -27646,8 +27646,8 @@
 Make the room feel complete with LALI 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 9.92 lbs&lt;/p&gt;</t>
+Color: Beige or Blue&lt;br&gt;
+Weight: 9.92 or 58.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H190" s="24" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -27791,11 +27791,11 @@
       <c r="G191" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LALI 9' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Metal, Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Make the room feel complete with LALI 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 58.92 lbs&lt;/p&gt;</t>
+Color: Beige or Blue&lt;br&gt;
+Weight: 9.92 or 58.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H191" s="24" t="inlineStr">
@@ -27883,7 +27883,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -27937,11 +27937,11 @@
       <c r="G192" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with LALI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with LALI 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 9.92 lbs&lt;/p&gt;</t>
+Color: Beige or Blue&lt;br&gt;
+Weight: 9.92 or 58.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H192" s="24" t="inlineStr">
@@ -28031,7 +28031,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -28085,11 +28085,11 @@
       <c r="G193" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LALI 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with LALI 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 104"DIA X 92.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 58.92 lbs&lt;/p&gt;</t>
+Color: Beige or Blue&lt;br&gt;
+Weight: 9.92 or 58.92 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H193" s="24" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -28234,7 +28234,7 @@
 Elevate your space with MORA 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 18.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28321,7 +28321,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -28375,10 +28375,10 @@
       <c r="G195" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MORA 11' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with MORA 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 18.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28465,7 +28465,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -28519,10 +28519,10 @@
       <c r="G196" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with MORA 11' Outdoor Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with MORA 11' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 132"W X 132"D X 101"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 18.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28609,7 +28609,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -28666,7 +28666,7 @@
 Make the room feel complete with MUSA Rectangular Market Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Canvas Stone tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 176.5"W X 104"D X 94.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Canvas Stone&lt;br&gt;
+Color: Canvas Stone or Gray&lt;br&gt;
 Weight: 43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -28807,10 +28807,10 @@
       <c r="G198" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MUSA Rectangular Market Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with MUSA Rectangular Market Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Canvas Stone tones, the Metal, Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 176.5"W X 104"D X 94.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Canvas Stone or Gray&lt;br&gt;
 Weight: 43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -28959,8 +28959,8 @@
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 46.29 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H199" s="59" t="inlineStr">
@@ -29050,7 +29050,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29108,12 +29108,12 @@
       <c r="G200" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 61.89 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H200" s="59" t="inlineStr">
@@ -29201,7 +29201,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -29259,12 +29259,12 @@
       <c r="G201" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NUTI 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 46.29 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H201" s="59" t="inlineStr">
@@ -29354,7 +29354,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -29412,12 +29412,12 @@
       <c r="G202" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NUTI 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 61.89 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H202" s="59" t="inlineStr">
@@ -29505,7 +29505,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -29563,12 +29563,12 @@
       <c r="G203" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 46.29 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H203" s="59" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -29712,12 +29712,12 @@
       <c r="G204" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 61.89 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H204" s="59" t="inlineStr">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -29863,12 +29863,12 @@
       <c r="G205" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NUTI 10' Round Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 46.29 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H205" s="59" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -30012,12 +30012,12 @@
       <c r="G206" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NUTI 10' Round Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 61.89 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H206" s="59" t="inlineStr">
@@ -30105,7 +30105,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -30163,12 +30163,12 @@
       <c r="G207" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 46.29 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H207" s="59" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -30312,12 +30312,12 @@
       <c r="G208" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NUTI 10' Round Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+Make the room feel complete with NUTI 10' Round Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
 Size: LED Light&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 61.89 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 46.29 or 61.89 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H208" s="59" t="inlineStr">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -30465,10 +30465,10 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H209" s="35" t="inlineStr">
@@ -30558,7 +30558,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -30616,12 +30616,12 @@
       <c r="G210" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H210" s="35" t="inlineStr">
@@ -30709,7 +30709,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -30767,12 +30767,12 @@
       <c r="G211" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANO 10' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H211" s="35" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -30920,12 +30920,12 @@
       <c r="G212" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SANO 10' SQ Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Blue tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H212" s="35" t="inlineStr">
@@ -31013,7 +31013,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -31071,12 +31071,12 @@
       <c r="G213" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Aluminum, Polyester Fabric construction is complemented by Gray tones for a polished look.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H213" s="35" t="inlineStr">
@@ -31162,7 +31162,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -31220,12 +31220,12 @@
       <c r="G214" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Aluminum, Polyester Fabric and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H214" s="35" t="inlineStr">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -31371,12 +31371,12 @@
       <c r="G215" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANO 10' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H215" s="35" t="inlineStr">
@@ -31462,7 +31462,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -31520,12 +31520,12 @@
       <c r="G216" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SANO 10' SQ Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Red tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H216" s="35" t="inlineStr">
@@ -31613,7 +31613,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -31671,12 +31671,12 @@
       <c r="G217" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Teal tones for a polished look.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 55.11 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H217" s="35" t="inlineStr">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -31820,12 +31820,12 @@
       <c r="G218" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SANO 10' SQ Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+SANO 10' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Beige tones for a polished look.&lt;br&gt;
 Product Dimensions: 118"W X 118"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Bulb and Control&lt;/p&gt;
+Size: Double Top, LED Bulb + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 70.71 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 55.11 or 70.71 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H218" s="35" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -31970,7 +31970,7 @@
 Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Black or White&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32057,7 +32057,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -32111,10 +32111,10 @@
       <c r="G220" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SLEEK Rectangular Umbrella brings a Modern look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Steel, Polyester construction is complemented by Canvas Stone tones for a polished look.&lt;br&gt;
+Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Canvas Stone&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32201,7 +32201,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -32255,10 +32255,10 @@
       <c r="G221" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SLEEK Rectangular Umbrella, styled in Modern and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Steel, Polyester and Dark Sapphire tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Dark Sapphire&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -32399,10 +32399,10 @@
       <c r="G222" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SLEEK Rectangular Umbrella adds a Modern touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Steel, Polyester, it is finished in Graphite tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Graphite&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -32543,10 +32543,10 @@
       <c r="G223" s="24" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. This outdoor umbrella is made to fit naturally into the room. Finished in Light Sapphire tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with SLEEK Rectangular Umbrella and its Modern character. As a outdoor umbrella, it is designed to complement your space. Finished in Black or White tones, the Steel, Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 90 1/2"L X 59"W X 93 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Steel, Polyester.&lt;br&gt;
-Color: Light Sapphire&lt;br&gt;
+Color: Black or White or Canvas Stone or Dark Sapphire or Graphite or Light Sapphire&lt;br&gt;
 Weight: 8.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -32689,8 +32689,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with SOLI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Blue&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -32833,10 +32833,10 @@
       <c r="G225" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SOLI 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Fabric, Steel, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with SOLI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Red&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -32979,10 +32979,10 @@
       <c r="G226" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SOLI 9' Outdoor Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Fabric, Steel, build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with SOLI 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Beige&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 68 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -33128,7 +33128,7 @@
 SOLI 9' Outdoor Umbrella w/ Auto Tilt brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 19 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33215,7 +33215,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -33269,10 +33269,10 @@
       <c r="G228" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SOLI 9' Outdoor Umbrella w/ Auto Tilt, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Metal, Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+SOLI 9' Outdoor Umbrella w/ Auto Tilt brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 19 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -33413,10 +33413,10 @@
       <c r="G229" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SOLI 9' Outdoor Umbrella w/ Auto Tilt adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+SOLI 9' Outdoor Umbrella w/ Auto Tilt brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Metal, Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 96"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
 Weight: 19 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33503,7 +33503,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -33559,9 +33559,9 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
-&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 12.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Fabric or Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
+Weight: 12.8 or 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H230" s="38" t="inlineStr">
@@ -33647,7 +33647,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -33701,11 +33701,11 @@
       <c r="G231" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with TANO 9' Outdoor Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Blue tones, the Fabric, Steel, build balances durability with visual appeal.&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 61.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Fabric or Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
+Weight: 12.8 or 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H231" s="38" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -33847,11 +33847,11 @@
       <c r="G232" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TANO 9' Outdoor Umbrella brings a Contemporary look to your home with a refined, comfortable feel. As a outdoor umbrella, it is designed to complement your space. The Metal, Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
-&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 12.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Fabric or Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
+Weight: 12.8 or 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H232" s="38" t="inlineStr">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -33991,11 +33991,11 @@
       <c r="G233" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with TANO 9' Outdoor Umbrella, styled in Contemporary and designed for everyday comfort. This outdoor umbrella is made to fit naturally into the room. With Fabric, Steel, and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 61.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Fabric or Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
+Weight: 12.8 or 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H233" s="38" t="inlineStr">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -34137,11 +34137,11 @@
       <c r="G234" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Metal, Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
-&lt;p&gt;Materials: Metal, Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 12.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Fabric or Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
+Weight: 12.8 or 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H234" s="38" t="inlineStr">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -34281,11 +34281,11 @@
       <c r="G235" s="38" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with TANO 9' Outdoor Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Fabric, Steel, build balances durability with visual appeal.&lt;br&gt;
+TANO 9' Outdoor Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Metal, Fabric, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 108"W X 108"D X 94"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Steel.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 61.8 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Metal, Fabric or Fabric, Steel, Others.&lt;br&gt;
+Color: Blue or Red or Beige&lt;br&gt;
+Weight: 12.8 or 61.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H235" s="38" t="inlineStr">
@@ -34373,7 +34373,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -34433,10 +34433,10 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H236" s="67" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -34584,12 +34584,12 @@
       <c r="G237" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. As a outdoor umbrella, it is designed to complement your space. Finished in Beige tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H237" s="67" t="inlineStr">
@@ -34677,7 +34677,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -34735,12 +34735,12 @@
       <c r="G238" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-XICO 8' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. This outdoor umbrella is made to fit naturally into the room. The Aluminum, Polyester Fabric construction is complemented by Blue tones for a polished look.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H238" s="67" t="inlineStr">
@@ -34830,7 +34830,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -34888,12 +34888,12 @@
       <c r="G239" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with XICO 8' SQ Umbrella, styled in Contemporary and designed for everyday comfort. Built as a outdoor umbrella, it pairs well with a wide range of interiors. With Aluminum, Polyester Fabric and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Blue&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H239" s="67" t="inlineStr">
@@ -34981,7 +34981,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -35039,12 +35039,12 @@
       <c r="G240" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor umbrella, it is designed to complement your space. Crafted from Aluminum, Polyester Fabric, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H240" s="67" t="inlineStr">
@@ -35130,7 +35130,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -35188,12 +35188,12 @@
       <c r="G241" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. This outdoor umbrella is made to fit naturally into the room. Finished in Gray tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H241" s="67" t="inlineStr">
@@ -35281,7 +35281,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -35339,12 +35339,12 @@
       <c r="G242" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-XICO 8' SQ Umbrella brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor umbrella, it pairs well with a wide range of interiors. The Aluminum, Polyester Fabric construction is complemented by Red tones for a polished look.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H242" s="67" t="inlineStr">
@@ -35430,7 +35430,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -35488,12 +35488,12 @@
       <c r="G243" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with XICO 8' SQ Umbrella, styled in Contemporary and designed for everyday comfort. As a outdoor umbrella, it is designed to complement your space. With Aluminum, Polyester Fabric and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Red&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H243" s="67" t="inlineStr">
@@ -35581,7 +35581,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -35639,12 +35639,12 @@
       <c r="G244" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. This outdoor umbrella is made to fit naturally into the room. Crafted from Aluminum, Polyester Fabric, it is finished in Teal tones that pair easily with surrounding decor.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 52.91 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H244" s="67" t="inlineStr">
@@ -35730,7 +35730,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD244" t="inlineStr">
@@ -35788,12 +35788,12 @@
       <c r="G245" s="67" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with XICO 8' SQ Umbrella and its Contemporary character. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Finished in Teal tones, the Aluminum, Polyester Fabric build balances durability with visual appeal.&lt;br&gt;
+XICO 8' SQ Umbrella adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor umbrella, it pairs well with a wide range of interiors. Crafted from Aluminum, Polyester Fabric, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 98.5"W X 98.5"D X 96.5"H&lt;br&gt;
-Size: Double Top, LED Light and Control&lt;/p&gt;
+Size: Double Top, LED Light + Control&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Polyester Fabric.&lt;br&gt;
-Color: Teal&lt;br&gt;
-Weight: 68.51 lbs&lt;/p&gt;</t>
+Color: Beige or Blue or Gray or Red or Teal&lt;br&gt;
+Weight: 52.91 or 68.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H245" s="67" t="inlineStr">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -35936,9 +35936,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with HALEY Hammock w/ Stand and its Contemporary character. This outdoor hammock is made to fit naturally into the room. Finished in Green or Blue tones, the Polyester Cotton, Steel build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 130"W X 47"D X 46"H&lt;/p&gt;
+Product Dimensions: 130"W X 47"D X 46"H / HAMMOCK: 130L X 60"W, STAND: 47"L X 122"W X 44"H"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester Cotton, Steel.&lt;br&gt;
-Color: Green or Blue&lt;br&gt;
+Color: Green or Blue or Brown or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36023,7 +36023,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -36077,10 +36077,10 @@
       <c r="G247" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HALEY Hammock w/ Stand brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor hammock, it pairs well with a wide range of interiors. The Polyester Cotton, Steel construction is complemented by Brown or Black tones for a polished look.&lt;br&gt;
-Product Dimensions: HAMMOCK: 130L X 60"W, STAND: 47"L X 122"W X 44"H"&lt;/p&gt;
+Make the room feel complete with HALEY Hammock w/ Stand and its Contemporary character. This outdoor hammock is made to fit naturally into the room. Finished in Green or Blue tones, the Polyester Cotton, Steel build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 130"W X 47"D X 46"H / HAMMOCK: 130L X 60"W, STAND: 47"L X 122"W X 44"H"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester Cotton, Steel.&lt;br&gt;
-Color: Brown or Black&lt;br&gt;
+Color: Green or Blue or Brown or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36169,7 +36169,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -36310,7 +36310,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -36451,7 +36451,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -36592,7 +36592,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr">
@@ -36733,7 +36733,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -36993,7 +36993,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -37050,7 +37050,7 @@
 Elevate your space with KYUSHU Table and Loveseat, styled in Rustic and designed for everyday comfort. Built as a outdoor table set, it pairs well with a wide range of interiors. With Acacia Wood, Polyester and Beige or Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: TABLE: 39 1/2"L X 23 1/2"W X 18"H, LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Beige or Natural&lt;br&gt;
+Color: Beige or Natural or Black or Natural&lt;br&gt;
 Weight: 57.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD254" t="inlineStr">
@@ -37191,10 +37191,10 @@
       <c r="G255" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KYUSHU Table and Loveseat adds a Rustic touch while keeping the room feeling warm and welcoming. As a outdoor table set, it is designed to complement your space. Crafted from Acacia Wood, Polyester, it is finished in Black or Natural tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with KYUSHU Table and Loveseat, styled in Rustic and designed for everyday comfort. Built as a outdoor table set, it pairs well with a wide range of interiors. With Acacia Wood, Polyester and Beige or Natural tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: TABLE: 39 1/2"L X 23 1/2"W X 18"H, LOVESEAT: 52 3/4"L X 27 1/4"W X 34 1/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Acacia Wood, Polyester.&lt;br&gt;
-Color: Black or Natural&lt;br&gt;
+Color: Beige or Natural or Black or Natural&lt;br&gt;
 Weight: 57.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37281,7 +37281,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -37336,9 +37336,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 LOTUS 3 Pc. Patio Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor table set, it pairs well with a wide range of interiors. Crafted from Aluminum, Fabric, Ceramic, it is finished in Black or Light Brown tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: Chair: 74"W X 29.5"D X 34"H, Table: 28"W X 26.5"D X 37"H&lt;/p&gt;
+Product Dimensions: Chair: 74"W X 29.5"D X 34"H, Table: 28"W X 26.5"D X 37"H / SIDE TABLE: 22"DIA X 18 1/4"H, CHAIR: 28 1/4"W X 26 1/2"D X 37"H (SEAT HT: 17", SEAT DP: 28")&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Fabric, Ceramic.&lt;br&gt;
-Color: Black or Light Brown&lt;br&gt;
+Color: Black or Light Brown or Natural or Beige&lt;br&gt;
 Weight: 63.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37425,7 +37425,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD256" t="inlineStr">
@@ -37479,10 +37479,10 @@
       <c r="G257" s="31" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with LOTUS 3 Pc. Patio Set and its Contemporary character. As a outdoor table set, it is designed to complement your space. Finished in Natural or Beige tones, the Aluminum, Fabric, Ceramic build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: SIDE TABLE: 22"DIA X 18 1/4"H, CHAIR: 28 1/4"W X 26 1/2"D X 37"H (SEAT HT: 17", SEAT DP: 28")&lt;/p&gt;
+LOTUS 3 Pc. Patio Set adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a outdoor table set, it pairs well with a wide range of interiors. Crafted from Aluminum, Fabric, Ceramic, it is finished in Black or Light Brown tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: Chair: 74"W X 29.5"D X 34"H, Table: 28"W X 26.5"D X 37"H / SIDE TABLE: 22"DIA X 18 1/4"H, CHAIR: 28 1/4"W X 26 1/2"D X 37"H (SEAT HT: 17", SEAT DP: 28")&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, Fabric, Ceramic.&lt;br&gt;
-Color: Natural or Beige&lt;br&gt;
+Color: Black or Light Brown or Natural or Beige&lt;br&gt;
 Weight: 63.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -37624,10 +37624,10 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MACKAY Patio Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio dining table, it is designed to complement your space. Crafted from Aluminum, FSC Certified 100% Teak Wood, it is finished in Gun Metal or Natural Teak tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H&lt;/p&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H / 59"L X 35 1/2"W X 29"H&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
 Color: Gun Metal or Natural Teak&lt;br&gt;
-Weight: 52.9 lbs&lt;/p&gt;</t>
+Weight: 52.9 or 33.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H258" s="65" t="inlineStr">
@@ -37713,7 +37713,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -37767,11 +37767,11 @@
       <c r="G259" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with MACKAY Patio Dining Table and its Contemporary character. This outdoor patio dining table is made to fit naturally into the room. Finished in Gun Metal or Natural Teak tones, the Aluminum, FSC Certified 100% Teak Wood build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 59"L X 35 1/2"W X 29"H&lt;/p&gt;
+MACKAY Patio Dining Table adds a Contemporary touch while keeping the room feeling warm and welcoming. As a outdoor patio dining table, it is designed to complement your space. Crafted from Aluminum, FSC Certified 100% Teak Wood, it is finished in Gun Metal or Natural Teak tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 61 1/2 - 84"L X 35 1/2"W X 30"H / 59"L X 35 1/2"W X 29"H&lt;/p&gt;
 &lt;p&gt;Materials: Aluminum, FSC Certified 100% Teak Wood.&lt;br&gt;
 Color: Gun Metal or Natural Teak&lt;br&gt;
-Weight: 33.1 lbs&lt;/p&gt;</t>
+Weight: 52.9 or 33.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H259" s="65" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -37998,7 +37998,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr">
@@ -38053,10 +38053,10 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SINTRA Patio Dining Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor patio dining table, it pairs well with a wide range of interiors. The Steel, Ceramic Tile construction is complemented by Black or Gray tones for a polished look.&lt;br&gt;
-Product Dimensions: 76"L X 40"W X 28"H&lt;/p&gt;
-&lt;p&gt;Materials: Steel, Ceramic Tile.&lt;br&gt;
+Product Dimensions: 76"L X 40"W X 28"H / 40"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic Tile or Steel, Ceramic.&lt;br&gt;
 Color: Black or Gray&lt;br&gt;
-Weight: 105.8 lbs&lt;/p&gt;</t>
+Weight: 105.8 or 63.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="48" t="inlineStr">
@@ -38142,7 +38142,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -38196,11 +38196,11 @@
       <c r="G262" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SINTRA Patio Dining Table, styled in Contemporary and designed for everyday comfort. As a outdoor patio dining table, it is designed to complement your space. With Steel, Ceramic and Black or Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 40"L X 40"W X 28"H&lt;/p&gt;
-&lt;p&gt;Materials: Steel, Ceramic.&lt;br&gt;
+SINTRA Patio Dining Table brings a Contemporary look to your home with a refined, comfortable feel. Built as a outdoor patio dining table, it pairs well with a wide range of interiors. The Steel, Ceramic Tile construction is complemented by Black or Gray tones for a polished look.&lt;br&gt;
+Product Dimensions: 76"L X 40"W X 28"H / 40"L X 40"W X 28"H&lt;/p&gt;
+&lt;p&gt;Materials: Steel, Ceramic Tile or Steel, Ceramic.&lt;br&gt;
 Color: Black or Gray&lt;br&gt;
-Weight: 63.9 lbs&lt;/p&gt;</t>
+Weight: 105.8 or 63.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" s="48" t="inlineStr">
@@ -38286,7 +38286,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
@@ -38427,7 +38427,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD264" t="inlineStr">
@@ -38709,7 +38709,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -38850,7 +38850,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -38907,7 +38907,7 @@
 Make the room feel complete with NIAMBI Square Table and its Contemporary character. As a outdoor patio table, it is designed to complement your space. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 26.5"W X 23.5"D X 29"H&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Gray or Natural&lt;br&gt;
 Weight: 33.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38992,7 +38992,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -39046,10 +39046,10 @@
       <c r="G268" s="46" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NIAMBI Square Table brings a Contemporary look to your home with a refined, comfortable feel. This outdoor patio table is made to fit naturally into the room. The Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber construction is complemented by Natural tones for a polished look.&lt;br&gt;
+Make the room feel complete with NIAMBI Square Table and its Contemporary character. As a outdoor patio table, it is designed to complement your space. Finished in Gray tones, the Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 26.5"W X 23.5"D X 29"H&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Steel, Aluminum, PE Rattan Wicker, Polyester Fiber.&lt;br&gt;
-Color: Natural&lt;br&gt;
+Color: Gray or Natural&lt;br&gt;
 Weight: 33.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39134,7 +39134,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr">
@@ -39275,7 +39275,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -39412,7 +39412,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -39545,7 +39545,7 @@
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD271" t="inlineStr">
@@ -39686,7 +39686,7 @@
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD272" t="inlineStr">
@@ -39827,7 +39827,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Outdoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">

--- a/FOA Singles/Outdoor-Single.xlsx
+++ b/FOA Singles/Outdoor-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,12 +859,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ALBA Patio Wooden Bench in Antique Oak Black | GOODDEGG</t>
+          <t>ALBA Patio Wooden Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The ALBA Patio Wooden Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALBA Patio Wooden Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BORDEAUX Bench in Natural Beige | GOODDEGG</t>
+          <t>BORDEAUX Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The BORDEAUX Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORDEAUX Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BORKUM Garden Bench in Natural | GOODDEGG</t>
+          <t>BORKUM Garden Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The BORKUM Garden Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORKUM Garden Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The JOHARI Patio Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI Patio Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MINOT Patio Steel Bench in Black | GOODDEGG</t>
+          <t>MINOT Patio Steel Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The MINOT Patio Steel Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MINOT Patio Steel Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>POTTER Patio Steel Bench in Black | GOODDEGG</t>
+          <t>POTTER Patio Steel Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The POTTER Patio Steel Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>POTTER Patio Steel Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SINTRA Bench in Black Gray | GOODDEGG</t>
+          <t>SINTRA Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The SINTRA Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SKIPPER Shoe Storage Bench in Natural Gray | GOODDEGG</t>
+          <t>SKIPPER Shoe Storage Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The SKIPPER Shoe Storage Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SKIPPER Shoe Storage Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="I10" s="46" t="inlineStr">
         <is>
-          <t>The ZALIKA Patio Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA Patio Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" s="46" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I11" s="46" t="inlineStr">
         <is>
-          <t>The ZALIKA Patio Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA Patio Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" s="46" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>ALVERTA Foldable Chair in Black | GOODDEGG</t>
+          <t>ALVERTA Foldable Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>The ALVERTA Foldable Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALVERTA Foldable Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="29" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
-          <t>ALVERTA Foldable Chair in Light Gray | GOODDEGG</t>
+          <t>ALVERTA Foldable Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="29" t="inlineStr">
         <is>
-          <t>The ALVERTA Foldable Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALVERTA Foldable Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="29" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ALYCIA Arm Chair w/ Cushion (6 CTN) in White Beige Gra</t>
+          <t>ALYCIA Arm Chair w/ Cushion (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ALYCIA Arm Chair w/ Cushion adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALYCIA Arm Chair w/ Cushion (6/CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ANTIGUA Arm Chair in Gun Metal Brown Gray | GOODDEGG</t>
+          <t>ANTIGUA Arm Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The ANTIGUA Arm Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA Arm Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ASHURA Stacking Chair (2 STACK) in Gray | GOODDEGG</t>
+          <t>ASHURA Stacking Chair (2/STACK) | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The ASHURA Stacking Chair ( or STACK) adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ASHURA Stacking Chair (2/STACK) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ASHURA Stacking Chair (8 STACK) in Gray | GOODDEGG</t>
+          <t>ASHURA Stacking Chair (8/STACK) | GOODDEGG</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>The ASHURA Stacking Chair ( or STACK) adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ASHURA Stacking Chair (8/STACK) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BORDEAUX Arm Chair (2 / CTN) in Natural Beige | GOODDEGG</t>
+          <t>BORDEAUX Arm Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The BORDEAUX Arm Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORDEAUX Arm Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BORDEAUX Side Chair (2 / CTN) in Natural Beige | GOODDEGG</t>
+          <t>BORDEAUX Side Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>The BORDEAUX Side Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORDEAUX Side Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="H20" s="48" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair in Black | GOODDEGG</t>
+          <t>BREEZE Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" s="48" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" s="48" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H21" s="48" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair in Dark Gray | GOODDEGG</t>
+          <t>BREEZE Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" s="48" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" s="48" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="H22" s="48" t="inlineStr">
         <is>
-          <t>BREEZE Swing Chair in Light Gray | GOODDEGG</t>
+          <t>BREEZE Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" s="48" t="inlineStr">
         <is>
-          <t>The BREEZE Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BREEZE Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" s="48" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair in Black | GOODDEGG</t>
+          <t>CRUSH Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" s="24" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair in Dark Gray | GOODDEGG</t>
+          <t>CRUSH Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" s="24" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>CRUSH Swing Chair in Light Gray | GOODDEGG</t>
+          <t>CRUSH Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>The CRUSH Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CRUSH Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" s="24" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CYPRUS Bar Chair in Gray | GOODDEGG</t>
+          <t>CYPRUS Bar Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The CYPRUS Bar Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYPRUS Bar Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="H27" s="31" t="inlineStr">
         <is>
-          <t>ELK Adirondrack Chair in Dark Brown | GOODDEGG</t>
+          <t>ELK Adirondrack Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" s="31" t="inlineStr">
         <is>
-          <t>The ELK Adirondrack Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELK Adirondrack Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" s="31" t="inlineStr">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="H28" s="31" t="inlineStr">
         <is>
-          <t>ELK Adirondrack Chair in Gray | GOODDEGG</t>
+          <t>ELK Adirondrack Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I28" s="31" t="inlineStr">
         <is>
-          <t>The ELK Adirondrack Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELK Adirondrack Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" s="31" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="H29" s="31" t="inlineStr">
         <is>
-          <t>ELK Adirondrack Chair in Natural | GOODDEGG</t>
+          <t>ELK Adirondrack Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I29" s="31" t="inlineStr">
         <is>
-          <t>The ELK Adirondrack Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELK Adirondrack Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" s="31" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>ELK Adirondrack Chair in Weathered Gray | GOODDEGG</t>
+          <t>ELK Adirondrack Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I30" s="31" t="inlineStr">
         <is>
-          <t>The ELK Adirondrack Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELK Adirondrack Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" s="31" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ENZI Stacking Chair (2 STACK) in Natural | GOODDEGG</t>
+          <t>ENZI Stacking Chair (2/STACK) | GOODDEGG</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>The ENZI Stacking Chair ( or STACK) adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ENZI Stacking Chair (2/STACK) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ENZI Stacking Chair (40 STACK) in Natural | GOODDEGG</t>
+          <t>ENZI Stacking Chair (40/STACK) | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>The ENZI Stacking Chair ( or STACK) adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ENZI Stacking Chair (40/STACK) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>GATES Footstool (2 / CTN) in White Natural | GOODDEGG</t>
+          <t>GATES Footstool (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>The GATES Footstool adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GATES Footstool (2 / CTN) Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HALEY Hammock Stand in Black | GOODDEGG</t>
+          <t>HALEY Hammock Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The HALEY Hammock Stand adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEY Hammock Stand Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>The JOHARI Patio Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI Patio Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="H36" s="50" t="inlineStr">
         <is>
-          <t>Kyushu Chair (2 / CTN) in Beige Natural | GOODDEGG</t>
+          <t>KYUSHU Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" s="50" t="inlineStr">
         <is>
-          <t>The KYUSHU Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" s="50" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H37" s="50" t="inlineStr">
         <is>
-          <t>Kyushu Chair (2 / CTN) in Black Natural | GOODDEGG</t>
+          <t>KYUSHU Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I37" s="50" t="inlineStr">
         <is>
-          <t>The KYUSHU Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" s="50" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MACKAY Reclining Chair (2 / CTN) in Beige Natural Teak | GOODDEG</t>
+          <t>MACKAY Reclining Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>The MACKAY Reclining Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY Reclining Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MACKAY Stacking Chair in Gun Metal Natural Teak | GOODDEGG</t>
+          <t>MACKAY Stacking Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>The MACKAY Stacking Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY Stacking Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MALIN Chair (2 / CTN) in Black | GOODDEGG</t>
+          <t>MALIN Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>The MALIN Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIN Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MOOSE Rocking Chair in Natural | GOODDEGG</t>
+          <t>MOOSE Rocking Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>The MOOSE Rocking Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOOSE Rocking Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NUSA Folding Arm Chair in Natural | GOODDEGG</t>
+          <t>NUSA Folding Arm Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The NUSA Folding Arm Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUSA Folding Arm Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>NYA Outdoor Chair 4Pc Carton in Natural | GOODDEGG</t>
+          <t>NYA Outdoor Chair 4Pc/Carton | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>The NYA Outdoor Chair or Carton adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NYA Outdoor Chair 4Pc/Carton supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="H44" s="52" t="inlineStr">
         <is>
-          <t>NYA Patio Chair (2 / CTN) in Black | GOODDEGG</t>
+          <t>NYA Patio Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" s="52" t="inlineStr">
         <is>
-          <t>The NYA Patio Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NYA Patio Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" s="52" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H45" s="52" t="inlineStr">
         <is>
-          <t>NYA Patio Chair (2 / CTN) in Natural | GOODDEGG</t>
+          <t>NYA Patio Chair (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I45" s="52" t="inlineStr">
         <is>
-          <t>The NYA Patio Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NYA Patio Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" s="52" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Coffee Table (9 Stack) in Brown Dark Teal | GOO</t>
+          <t>OLIVERI Wicker Coffee Table (9/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Coffee Table - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVERI Wicker Coffee Table (9/Stack) Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Loveseat in Brown Dark Teal | GOODDEGG</t>
+          <t>OLIVERI Wicker Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The OLIVERI Wicker Loveseat adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVERI Wicker Loveseat Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Loveseat (9 Stack) in Brown Dark Teal | GOODDEG</t>
+          <t>OLIVERI Wicker Loveseat (9/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>The OLIVERI Wicker Loveseat - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVERI Wicker Loveseat (9/Stack) Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Stacking Chair (18 Stack) | GOODDEGG</t>
+          <t>OLIVERI Wicker Stacking Chair (18/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVERI Wicker Stacking Chair (18/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>PALMA Adjustable Chairs (6 CTN) in Black Gray | GOODDEGG</t>
+          <t>PALMA Adjustable Chairs (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>The PALMA Adjustable Chairs adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALMA Adjustable Chairs (6/CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PALMA Swivel Counter Height Arm Chair adds comfortable seating and style to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALMA Swivel Counter Height Arm Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PERSE Rocking Chair in Dark Gray Oak | GOODDEGG</t>
+          <t>PERSE Rocking Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>The PERSE Rocking Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PERSE Rocking Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="H53" s="54" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (2 Stack) in Blue | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (2/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I53" s="54" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (2/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" s="54" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="H54" s="54" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (2 Stack) in Red | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (2/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I54" s="54" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (2/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" s="54" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="H55" s="54" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (2 Stack) in Beige | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (2/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" s="54" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (2/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" s="54" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="H56" s="56" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (28 Stack) in Blue | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (28/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I56" s="56" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (28/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J56" s="56" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H57" s="56" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (28 Stack) in Red | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (28/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I57" s="56" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (28/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J57" s="56" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="H58" s="56" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (28 Stack) in Beige | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (28/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I58" s="56" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (28/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J58" s="56" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (4 Stack) in Blue | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (4/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I59" s="29" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (4/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J59" s="29" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (4 Stack) in Red | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (4/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (4/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J60" s="29" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="H61" s="29" t="inlineStr">
         <is>
-          <t>PIERRO Stacking Chair (4 Stack) in Beige | GOODDEGG</t>
+          <t>PIERRO Stacking Chair (4/Stack) | GOODDEGG</t>
         </is>
       </c>
       <c r="I61" s="29" t="inlineStr">
         <is>
-          <t>The PIERRO Stacking Chair - or Stack adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Stacking Chair (4/Stack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J61" s="29" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="H62" s="50" t="inlineStr">
         <is>
-          <t>SANDOR Swing Chair in Black | GOODDEGG</t>
+          <t>SANDOR Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I62" s="50" t="inlineStr">
         <is>
-          <t>The SANDOR Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANDOR Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J62" s="50" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="H63" s="50" t="inlineStr">
         <is>
-          <t>SANDOR Swing Chair in White | GOODDEGG</t>
+          <t>SANDOR Swing Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I63" s="50" t="inlineStr">
         <is>
-          <t>The SANDOR Swing Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANDOR Swing Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J63" s="50" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>The SARABI Patio Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SARABI Patio Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SEGOVIA Swivel Chair in Black Gray | GOODDEGG</t>
+          <t>SEGOVIA Swivel Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The SEGOVIA Swivel Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SEGOVIA Swivel Glider Arm Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA Swivel Glider Arm Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SINTRA Arm Chair in Black Gray | GOODDEGG</t>
+          <t>SINTRA Arm Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>The SINTRA Arm Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA Arm Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SINTRA Swivel Chair in Black Gray | GOODDEGG</t>
+          <t>SINTRA Swivel Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>The SINTRA Swivel Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>TOMOHON Swivel Wicker Chair in White | GOODDEGG</t>
+          <t>TOMOHON Swivel Wicker Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>The TOMOHON Swivel Wicker Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TOMOHON Swivel Wicker Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>VALE Footstool (2 / CTN) in Black | GOODDEGG</t>
+          <t>VALE Footstool (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>The VALE Footstool adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALE Footstool (2 / CTN) Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="I71" s="59" t="inlineStr">
         <is>
-          <t>The ZALIKA Patio Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA Patio Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J71" s="59" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="I72" s="59" t="inlineStr">
         <is>
-          <t>The ZALIKA Patio Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA Patio Chair (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J72" s="59" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ALYCIA Patio Table in White Gray | GOODDEGG</t>
+          <t>ALYCIA Patio Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>The ALYCIA Patio Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALYCIA Patio Table Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>PIERRO Outdoor Dining Table in Black | GOODDEGG</t>
+          <t>PIERRO Outdoor Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>The PIERRO Outdoor Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO Outdoor Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ANTIGUA Height Adjustable Table in Gun Metal Brown Gray | GO</t>
+          <t>ANTIGUA Height-Adjustable Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>The ANTIGUA Height creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA Height-Adjustable Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>AROSA Fire Pit Counter Height Table in Black Gray | GOODDEGG</t>
+          <t>AROSA Fire Pit Counter Height Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>The AROSA Fire Pit Counter Height Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AROSA Fire Pit Counter Height Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>BARBUDA Fire Pit Table in Gray | GOODDEGG</t>
+          <t>BARBUDA Fire Pit Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>The BARBUDA Fire Pit Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BARBUDA Fire Pit Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BORDEAUX Dining Table w/ Fire Pit &amp; Cooler in Brown | GOODDEGG</t>
+          <t>BORDEAUX Dining Table w/ Fire Pit &amp; Cooler | GOODDEGG</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>BORDEAUX Dining Table w/ Fire Pit &amp; Cooler creates a welcoming place for meals and. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BORDEAUX Dining Table w/ Fire Pit &amp; Cooler supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>COVE Nesting Tables (2 / CTN) in Natural Black | GOODDEGG</t>
+          <t>COVE Nesting Tables (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>The COVE Nesting Tables creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>COVE Nesting Tables (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -11806,12 +11806,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>LOVINA Oval Dining Table in Natural | GOODDEGG</t>
+          <t>LOVINA Oval Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>The LOVINA Oval Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOVINA Oval Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>LYON Game Table in Black Natural Brown | GOODDEGG</t>
+          <t>LYON Game Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The LYON Game Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LYON Game Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MOLLIE Nesting Tables (2 / CTN) in Natural Black | GOODDEGG</t>
+          <t>MOLLIE Nesting Tables (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>The MOLLIE Nesting Tables creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOLLIE Nesting Tables (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -12226,12 +12226,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MONZA Adjustable Chairs (2 / CTN) in Gun Metal Gray | GOODDEGG</t>
+          <t>MONZA Adjustable Chairs (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>The MONZA Adjustable Chairs creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONZA Adjustable Chairs (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>MONZA Extendable Dining Table in Gun Metal Gray | GOODDEGG</t>
+          <t>MONZA Extendable Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>The MONZA Extendable Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONZA Extendable Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>PALMA Dining Table in Black Gray | GOODDEGG</t>
+          <t>PALMA Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The PALMA Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALMA Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>The SARABI Patio Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SARABI Patio Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="I87" s="52" t="inlineStr">
         <is>
-          <t>The ZALIKA Patio Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA Patio Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J87" s="52" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="I88" s="52" t="inlineStr">
         <is>
-          <t>The ZALIKA Patio Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZALIKA Patio Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J88" s="52" t="inlineStr">
@@ -13007,12 +13007,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ANTIGUA Ottoman (2 / CTN) in Gun Metal Brown Gray | GOODDEG</t>
+          <t>ANTIGUA Ottoman (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>The ANTIGUA Ottoman brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA Ottoman (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MACKAY Ottoman (2 / CTN) in Beige Natural Teak | GOODDEGG</t>
+          <t>MACKAY Ottoman (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>The MACKAY Ottoman brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY Ottoman (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -13289,12 +13289,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Antigua Sofa in Gun Metal Brown Gray | GOODDEGG</t>
+          <t>ANTIGUA Sofa | GOODDEGG</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>The ANTIGUA Sofa offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANTIGUA Sofa supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -13430,12 +13430,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ARALI HXZ Pop Up Gazebo in Gray | GOODDEGG</t>
+          <t>ARALI HXZ Pop Up Gazebo | GOODDEGG</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>The ARALI HXZ Pop Up Gazebo brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARALI HXZ Pop Up Gazebo Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>BARBUDA Sectional Sofa w/ End Tables brings everyday comfort and function to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Patio Set BARBUDA 5 Pc. Sectional Sofa w/ 2 supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -13713,12 +13713,12 @@
       </c>
       <c r="H94" s="35" t="inlineStr">
         <is>
-          <t>BASTIA 3 Pc. Conversation Set in Beige | GOODDEGG</t>
+          <t>BASTIA 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I94" s="35" t="inlineStr">
         <is>
-          <t>The BASTIA Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASTIA 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J94" s="35" t="inlineStr">
@@ -13857,12 +13857,12 @@
       </c>
       <c r="H95" s="35" t="inlineStr">
         <is>
-          <t>BASTIA 3 Pc. Conversation Set in Teal | GOODDEGG</t>
+          <t>BASTIA 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I95" s="35" t="inlineStr">
         <is>
-          <t>The BASTIA Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BASTIA 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J95" s="35" t="inlineStr">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CHANDU 5 Pc. Conversation Set in Natural Black | GOODDEGG</t>
+          <t>CHANDU 5 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>The CHANDU Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHANDU 5 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>FARISHA 4 Pc. Outdoor Sectional Set in White | GOODDEGG</t>
+          <t>FARISHA 4 Pc. Outdoor Sectional Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>The FARISHA Outdoor Sectional brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FARISHA 4 Pc. Outdoor Sectional Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>GENOA Pop Up Gazebo 12' X12' in Brown | GOODDEGG</t>
+          <t>GENOA Pop Up Gazebo 12' X12' | GOODDEGG</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>The GENOA Pop Up Gazebo X12 brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GENOA Pop Up Gazebo 12' X12' Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="H99" s="62" t="inlineStr">
         <is>
-          <t>HANA 4 Pc. Patio Set in Denim Blue Natural | GOODDEGG</t>
+          <t>HANA 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I99" s="62" t="inlineStr">
         <is>
-          <t>The HANA Patio brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HANA 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J99" s="62" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="H100" s="62" t="inlineStr">
         <is>
-          <t>HANA 4 Pc. Patio Set in Brown Natural | GOODDEGG</t>
+          <t>HANA 4 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I100" s="62" t="inlineStr">
         <is>
-          <t>The HANA Patio brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HANA 4 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J100" s="62" t="inlineStr">
@@ -14717,12 +14717,12 @@
       </c>
       <c r="H101" s="56" t="inlineStr">
         <is>
-          <t>IBIZA 4 Pc. Sling Set in Green | GOODDEGG</t>
+          <t>IBIZA 4 Pc. Sling Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I101" s="56" t="inlineStr">
         <is>
-          <t>The IBIZA Sling brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IBIZA 4 Pc. Sling Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J101" s="56" t="inlineStr">
@@ -14861,12 +14861,12 @@
       </c>
       <c r="H102" s="56" t="inlineStr">
         <is>
-          <t>IBIZA 4 Pc. Sling Set in Light Brown | GOODDEGG</t>
+          <t>IBIZA 4 Pc. Sling Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I102" s="56" t="inlineStr">
         <is>
-          <t>The IBIZA Sling brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IBIZA 4 Pc. Sling Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J102" s="56" t="inlineStr">
@@ -15005,12 +15005,12 @@
       </c>
       <c r="H103" s="29" t="inlineStr">
         <is>
-          <t>KIMARA Dining Table in Black Gray | GOODDEGG</t>
+          <t>KIMARA Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I103" s="29" t="inlineStr">
         <is>
-          <t>The KIMARA Dining Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA Dining Table Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J103" s="29" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="H104" s="29" t="inlineStr">
         <is>
-          <t>KIMARA Dining Table in Black Gray | GOODDEGG</t>
+          <t>KIMARA Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I104" s="29" t="inlineStr">
         <is>
-          <t>The KIMARA Dining Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMARA Dining Table Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J104" s="29" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>LOTUS Sofa &amp; Coffee Table Set in Black Light Brown | GOODDEGG</t>
+          <t>LOTUS Sofa &amp; Coffee Table Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>The LOTUS Sofa &amp; Coffee Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOTUS Sofa &amp; Coffee Table Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -15441,12 +15441,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>MYESHA 4 Pc. Conversation Set in Dark Gray Light Gray | GOODDEGG</t>
+          <t>MYESHA 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>The MYESHA Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MYESHA 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -15582,12 +15582,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>NOTO 3 Pc. Patio Set in Natural Black | GOODDEGG</t>
+          <t>NOTO 3 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>The NOTO Patio brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NOTO 3 Pc. Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -15723,12 +15723,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>PALMA 4 Pc. Conversation Set in Black Gray | GOODDEGG</t>
+          <t>PALMA 4 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>The PALMA Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PALMA 4 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -15864,12 +15864,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>SHANI 3 Pc. Conversation Set in Light Gray Black | GOODDEGG</t>
+          <t>SHANI 3 Pc. Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>The SHANI Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHANI 3 Pc. Conversation Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -16010,12 +16010,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>SHOMARI 4 Pc. Wicker Sofa Set in White | GOODDEGG</t>
+          <t>SHOMARI 4 Pc. Wicker Sofa Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>The SHOMARI Wicker Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHOMARI 4 Pc. Wicker Sofa Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -16151,12 +16151,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>TUSHARI 7 Pc. Outdoor Dining Set in Dark Gray Light Gray | GOODDE</t>
+          <t>TUSHARI 7 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>The TUSHARI Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TUSHARI 7 Pc. Outdoor Dining Set Patio Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -16288,12 +16288,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>AREZZO 4 Pc. Outdoor Conversation Set in Beige | GOODDEGG</t>
+          <t>AREZZO 4 Pc. Outdoor Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>The AREZZO Outdoor Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AREZZO 4 Pc. Outdoor Conversation Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -16429,12 +16429,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>FALLONE 6 Pc. Outdoor Dining Set in Beige | GOODDEGG</t>
+          <t>FALLONE 6 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>The FALLONE Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FALLONE 6 Pc. Outdoor Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -16572,12 +16572,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>MARSHA 3 Pc. Outdoor Set in Gray Green Oak | GOODDEGG</t>
+          <t>MARSHA 3 Pc. Outdoor Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>The MARSHA Outdoor brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARSHA 3 Pc. Outdoor Set Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -16714,12 +16714,12 @@
       </c>
       <c r="H115" s="62" t="inlineStr">
         <is>
-          <t>PIERRO 5 Pc. Outdoor Dining Set in Blue | GOODDEGG</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I115" s="62" t="inlineStr">
         <is>
-          <t>The PIERRO Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J115" s="62" t="inlineStr">
@@ -16856,12 +16856,12 @@
       </c>
       <c r="H116" s="62" t="inlineStr">
         <is>
-          <t>PIERRO 5 Pc. Outdoor Dining Set in Red | GOODDEGG</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I116" s="62" t="inlineStr">
         <is>
-          <t>The PIERRO Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J116" s="62" t="inlineStr">
@@ -16998,12 +16998,12 @@
       </c>
       <c r="H117" s="62" t="inlineStr">
         <is>
-          <t>PIERRO 5 Pc. Outdoor Dining Set in Red | GOODDEGG</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I117" s="62" t="inlineStr">
         <is>
-          <t>The PIERRO Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J117" s="62" t="inlineStr">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="H118" s="62" t="inlineStr">
         <is>
-          <t>PIERRO 5 Pc. Outdoor Dining Set in Beige | GOODDEGG</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I118" s="62" t="inlineStr">
         <is>
-          <t>The PIERRO Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J118" s="62" t="inlineStr">
@@ -17282,12 +17282,12 @@
       </c>
       <c r="H119" s="62" t="inlineStr">
         <is>
-          <t>PIERRO 5 Pc. Outdoor Dining Set in Beige | GOODDEGG</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I119" s="62" t="inlineStr">
         <is>
-          <t>The PIERRO Outdoor Dining brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PIERRO 5 Pc. Outdoor Dining Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J119" s="62" t="inlineStr">
@@ -17423,12 +17423,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>AROSA Outdoor Pop-Up Canopy 10' X 10' in Beige | GOODDEGG</t>
+          <t>AROSA Outdoor Pop-Up Canopy 10' X 10' | GOODDEGG</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>The AROSA Outdoor Pop-Up Canopy brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AROSA Outdoor Pop-Up Canopy 10' X 10' supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>GORDOLA Outdoor Canopy 13' X 10' in Brown | GOODDEGG</t>
+          <t>GORDOLA Outdoor Canopy 13' X 10' | GOODDEGG</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>The GORDOLA Outdoor Canopy brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GORDOLA Outdoor Canopy 13' X 10' supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>NESTA Outdoor Pop-Up Canopy 6' X 6' in Burgundy | GOODDEGG</t>
+          <t>NESTA Outdoor Pop-Up Canopy 6' X 6' | GOODDEGG</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>The NESTA Outdoor Pop-Up Canopy brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NESTA Outdoor Pop-Up Canopy 6' X 6' supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -17847,12 +17847,12 @@
       </c>
       <c r="H123" s="50" t="inlineStr">
         <is>
-          <t>BAHIA TOBAGO Reclining Chaise Lounge in Brown Dark Gray | GOODDEG</t>
+          <t>BAHIA TOBAGO Reclining Chaise Lounge | GOODDEGG</t>
         </is>
       </c>
       <c r="I123" s="50" t="inlineStr">
         <is>
-          <t>BAHIA TOBAGO Reclining Chaise Lounge brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BAHIA TOBAGO Reclining Chaise Lounge supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J123" s="50" t="inlineStr">
@@ -17991,12 +17991,12 @@
       </c>
       <c r="H124" s="50" t="inlineStr">
         <is>
-          <t>BAHIA TOBAGO Reclining Chaise Lounge in Gray | GOODDEGG</t>
+          <t>BAHIA TOBAGO Reclining Chaise Lounge | GOODDEGG</t>
         </is>
       </c>
       <c r="I124" s="50" t="inlineStr">
         <is>
-          <t>BAHIA TOBAGO Reclining Chaise Lounge brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BAHIA TOBAGO Reclining Chaise Lounge supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J124" s="50" t="inlineStr">
@@ -18140,12 +18140,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>BOYLE Dust Cover for Chair Small in Light Brown | GOODDEGG</t>
+          <t>BOYLE Dust Cover for Chair - Small | GOODDEGG</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>The BOYLE Dust Cover for Chair brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BOYLE Dust Cover for Chair - Small Accessory supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -18287,12 +18287,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>BOYLE Dust Cover for Sofa Small in Light Brown | GOODDEGG</t>
+          <t>BOYLE Dust Cover for Sofa - Small | GOODDEGG</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>The BOYLE Dust Cover for Sofa brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BOYLE Dust Cover for Sofa - Small Accessory supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18428,12 +18428,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>BRINDSMADE 6 Pc. Patio Set w/ Coffee Table &amp; 2 End Tables | GOODD</t>
+          <t>BRINDSMADE 6 Pc. Patio Set w/ Coffee Table + 2 End Tables | GOODDEGG</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>BRINDSMADE Patio w/ Coffee Table and End Tables offers relaxed seating for everyday. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Sofa Set BRINDSMADE 6 Pc. Patio Set w/ Coffee supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ILONA Armless Chair in Brown Beige | GOODDEGG</t>
+          <t>ILONA Armless Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>The ILONA Armless Chair offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA Armless Chair Sofa Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ILONA Coffee Table in Brown Beige | GOODDEGG</t>
+          <t>ILONA Coffee Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>The ILONA Coffee Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA Coffee Table Sofa Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -18847,12 +18847,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ILONA Corner in Brown Beige | GOODDEGG</t>
+          <t>ILONA Corner | GOODDEGG</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>The ILONA Corner offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA Corner Sofa Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -18988,12 +18988,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ILONA End Table in Brown Beige | GOODDEGG</t>
+          <t>ILONA End Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>The ILONA End Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA End Table Sofa Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ILONA Left Arm Chair in Brown Beige | GOODDEGG</t>
+          <t>ILONA Left Arm Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The ILONA Left Arm Chair offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA Left Arm Chair Sofa Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -19270,12 +19270,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ILONA Ottoman in Brown Beige | GOODDEGG</t>
+          <t>ILONA Ottoman | GOODDEGG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>The ILONA Ottoman offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ILONA Ottoman Sofa Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -19411,12 +19411,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CYPRUS Round Bar Table in Gray | GOODDEGG</t>
+          <t>CYPRUS Round Bar Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The CYPRUS Round Bar Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYPRUS Round Bar Table Bar Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19548,12 +19548,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>DAVINA 3 Pc. Patio Set Storage in Brown Beige | GOODDEGG</t>
+          <t>DAVINA 3 Pc. Patio Set Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>The DAVINA Patio Storage offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DAVINA 3 Pc. Patio Set Storage Sectional supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19685,12 +19685,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>DAVINA Patio 3 Pc. Set Storage in Brown Beige | GOODDEGG</t>
+          <t>DAVINA Patio 3 Pc. Set Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>The DAVINA Patio. Storage offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DAVINA Patio 3 Pc. Set Storage Sectional supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -19822,12 +19822,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>SAMARA Modular Sectional in Gun Metal Natural Gray | GOODDEG</t>
+          <t>SAMARA Modular Sectional | GOODDEGG</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>The SAMARA Modular Sectional offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SAMARA Modular Sectional supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -19963,12 +19963,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>SAN JOSE Modular Sectional in Gun Metal Natural Gray | GOODD</t>
+          <t>SAN JOSE Modular Sectional | GOODDEGG</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>The SAN JOSE Modular Sectional offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SAN JOSE Modular Sectional supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>WINONA Patio Sectional w/ Table in White Oak Blue | GOODD</t>
+          <t>WINONA Patio Sectional w/ Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The WINONA Patio Sectional w/ Table offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WINONA Patio Sectional w/ Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -20246,12 +20246,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>DURO Round Umbrella Base in Black | GOODDEGG</t>
+          <t>DURO Round Umbrella Base | GOODDEGG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>DURO Round Umbrella Base improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DURO Round Umbrella Base supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -20388,12 +20388,12 @@
       </c>
       <c r="H141" s="65" t="inlineStr">
         <is>
-          <t>FAB Round Umbrella Base in Black | GOODDEGG</t>
+          <t>FAB Round Umbrella Base | GOODDEGG</t>
         </is>
       </c>
       <c r="I141" s="65" t="inlineStr">
         <is>
-          <t>FAB Round Umbrella Base improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAB Round Umbrella Base supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J141" s="65" t="inlineStr">
@@ -20532,12 +20532,12 @@
       </c>
       <c r="H142" s="65" t="inlineStr">
         <is>
-          <t>FAB Round Umbrella Base in Black | GOODDEGG</t>
+          <t>FAB Round Umbrella Base | GOODDEGG</t>
         </is>
       </c>
       <c r="I142" s="65" t="inlineStr">
         <is>
-          <t>FAB Round Umbrella Base improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAB Round Umbrella Base supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J142" s="65" t="inlineStr">
@@ -20675,12 +20675,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SAYA Base For 360 Degree Rotating Umbrella in Black | GOODDEGG</t>
+          <t>SAYA Base For 360 Degree Rotating Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SAYA Base For Degree Rotating Umbrella improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Umbrella Base SAYA Base For 360 Degree supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -20816,12 +20816,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>TANGRAM Umbrella Base w/ Handle in Black | GOODDEGG</t>
+          <t>TANGRAM Umbrella Base w/ Handle | GOODDEGG</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>TANGRAM Umbrella Base w/ Handle improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANGRAM Umbrella Base w/ Handle supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -20963,12 +20963,12 @@
       </c>
       <c r="H145" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Beige | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I145" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J145" s="38" t="inlineStr">
@@ -21116,12 +21116,12 @@
       </c>
       <c r="H146" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Beige | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I146" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J146" s="38" t="inlineStr">
@@ -21267,12 +21267,12 @@
       </c>
       <c r="H147" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Blue | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I147" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J147" s="38" t="inlineStr">
@@ -21420,12 +21420,12 @@
       </c>
       <c r="H148" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Blue | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I148" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J148" s="38" t="inlineStr">
@@ -21571,12 +21571,12 @@
       </c>
       <c r="H149" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Gray | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I149" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J149" s="38" t="inlineStr">
@@ -21720,12 +21720,12 @@
       </c>
       <c r="H150" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Gray | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I150" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J150" s="38" t="inlineStr">
@@ -21871,12 +21871,12 @@
       </c>
       <c r="H151" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Red | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I151" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J151" s="38" t="inlineStr">
@@ -22020,12 +22020,12 @@
       </c>
       <c r="H152" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Red | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I152" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J152" s="38" t="inlineStr">
@@ -22171,12 +22171,12 @@
       </c>
       <c r="H153" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Teal | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I153" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J153" s="38" t="inlineStr">
@@ -22320,12 +22320,12 @@
       </c>
       <c r="H154" s="38" t="inlineStr">
         <is>
-          <t>FERA 10' Round Umbrella LED Bulb in Teal | GOODDEGG</t>
+          <t>FERA 10' Round Umbrella, LED Bulb | GOODDEGG</t>
         </is>
       </c>
       <c r="I154" s="38" t="inlineStr">
         <is>
-          <t>FERA Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERA 10' Round Umbrella, LED Bulb supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J154" s="38" t="inlineStr">
@@ -22471,12 +22471,12 @@
       </c>
       <c r="H155" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Beige | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I155" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J155" s="67" t="inlineStr">
@@ -22624,12 +22624,12 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Beige | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I156" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J156" s="67" t="inlineStr">
@@ -22775,12 +22775,12 @@
       </c>
       <c r="H157" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Blue | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I157" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J157" s="67" t="inlineStr">
@@ -22928,12 +22928,12 @@
       </c>
       <c r="H158" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Blue | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I158" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J158" s="67" t="inlineStr">
@@ -23079,12 +23079,12 @@
       </c>
       <c r="H159" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Gray | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I159" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J159" s="67" t="inlineStr">
@@ -23228,12 +23228,12 @@
       </c>
       <c r="H160" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Gray | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I160" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J160" s="67" t="inlineStr">
@@ -23379,12 +23379,12 @@
       </c>
       <c r="H161" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Red | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I161" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J161" s="67" t="inlineStr">
@@ -23528,12 +23528,12 @@
       </c>
       <c r="H162" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Red | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I162" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J162" s="67" t="inlineStr">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="H163" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Teal | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I163" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J163" s="67" t="inlineStr">
@@ -23828,12 +23828,12 @@
       </c>
       <c r="H164" s="67" t="inlineStr">
         <is>
-          <t>FIDA 8' Square Umbrella Double Top in Teal | GOODDEGG</t>
+          <t>FIDA 8' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I164" s="67" t="inlineStr">
         <is>
-          <t>FIDA Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIDA 8' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J164" s="67" t="inlineStr">
@@ -23973,12 +23973,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella in Blue White Black | GOODDEGG</t>
+          <t>GLAM Cantilever Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLAM Cantilever Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -24120,12 +24120,12 @@
       </c>
       <c r="H166" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED in Black White | GOODDEGG</t>
+          <t>GLAM Cantilever Umbrella w/ LED | GOODDEGG</t>
         </is>
       </c>
       <c r="I166" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLAM Cantilever Umbrella w/ LED supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J166" s="46" t="inlineStr">
@@ -24264,12 +24264,12 @@
       </c>
       <c r="H167" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED in Canvas Stone | GOODDEGG</t>
+          <t>GLAM Cantilever Umbrella w/ LED | GOODDEGG</t>
         </is>
       </c>
       <c r="I167" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLAM Cantilever Umbrella w/ LED supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J167" s="46" t="inlineStr">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="H168" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED in Dark Sapphire | GOODDEGG</t>
+          <t>GLAM Cantilever Umbrella w/ LED | GOODDEGG</t>
         </is>
       </c>
       <c r="I168" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLAM Cantilever Umbrella w/ LED supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J168" s="46" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="H169" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED in Graphite | GOODDEGG</t>
+          <t>GLAM Cantilever Umbrella w/ LED | GOODDEGG</t>
         </is>
       </c>
       <c r="I169" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLAM Cantilever Umbrella w/ LED supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J169" s="46" t="inlineStr">
@@ -24696,12 +24696,12 @@
       </c>
       <c r="H170" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED in Light Sapphire | GOODDEGG</t>
+          <t>GLAM Cantilever Umbrella w/ LED | GOODDEGG</t>
         </is>
       </c>
       <c r="I170" s="46" t="inlineStr">
         <is>
-          <t>GLAM Cantilever Umbrella w/ LED improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GLAM Cantilever Umbrella w/ LED supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J170" s="46" t="inlineStr">
@@ -24839,12 +24839,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>HALO Market Umbrella in Blue White Black | GOODDEGG</t>
+          <t>HALO Market Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>HALO Market Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALO Market Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -24986,12 +24986,12 @@
       </c>
       <c r="H172" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella in Black White | GOODDEGG</t>
+          <t>HALO Round Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I172" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALO Round Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J172" s="52" t="inlineStr">
@@ -25130,12 +25130,12 @@
       </c>
       <c r="H173" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella in Canvas Stone | GOODDEGG</t>
+          <t>HALO Round Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I173" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALO Round Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J173" s="52" t="inlineStr">
@@ -25274,12 +25274,12 @@
       </c>
       <c r="H174" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella in Dark Sapphire | GOODDEGG</t>
+          <t>HALO Round Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I174" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALO Round Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J174" s="52" t="inlineStr">
@@ -25418,12 +25418,12 @@
       </c>
       <c r="H175" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella in Graphite | GOODDEGG</t>
+          <t>HALO Round Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I175" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALO Round Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J175" s="52" t="inlineStr">
@@ -25562,12 +25562,12 @@
       </c>
       <c r="H176" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella in Light Sapphire | GOODDEGG</t>
+          <t>HALO Round Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I176" s="52" t="inlineStr">
         <is>
-          <t>HALO Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALO Round Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J176" s="52" t="inlineStr">
@@ -25711,12 +25711,12 @@
       </c>
       <c r="H177" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Beige | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I177" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J177" s="54" t="inlineStr">
@@ -25864,12 +25864,12 @@
       </c>
       <c r="H178" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Beige | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I178" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J178" s="54" t="inlineStr">
@@ -26015,12 +26015,12 @@
       </c>
       <c r="H179" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Blue | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I179" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J179" s="54" t="inlineStr">
@@ -26168,12 +26168,12 @@
       </c>
       <c r="H180" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Blue | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I180" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J180" s="54" t="inlineStr">
@@ -26319,12 +26319,12 @@
       </c>
       <c r="H181" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Gray | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I181" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J181" s="54" t="inlineStr">
@@ -26468,12 +26468,12 @@
       </c>
       <c r="H182" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Gray | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I182" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J182" s="54" t="inlineStr">
@@ -26619,12 +26619,12 @@
       </c>
       <c r="H183" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Red | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I183" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J183" s="54" t="inlineStr">
@@ -26768,12 +26768,12 @@
       </c>
       <c r="H184" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Red | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I184" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J184" s="54" t="inlineStr">
@@ -26919,12 +26919,12 @@
       </c>
       <c r="H185" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Teal | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I185" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J185" s="54" t="inlineStr">
@@ -27068,12 +27068,12 @@
       </c>
       <c r="H186" s="54" t="inlineStr">
         <is>
-          <t>HERO 10' Square Umbrella Double Top in Teal | GOODDEGG</t>
+          <t>HERO 10' Square Umbrella, Double Top | GOODDEGG</t>
         </is>
       </c>
       <c r="I186" s="54" t="inlineStr">
         <is>
-          <t>HERO Square Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HERO 10' Square Umbrella, Double Top supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J186" s="54" t="inlineStr">
@@ -27214,12 +27214,12 @@
       </c>
       <c r="H187" s="48" t="inlineStr">
         <is>
-          <t>LALI 11' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>LALI 11' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I187" s="48" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 11' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J187" s="48" t="inlineStr">
@@ -27360,12 +27360,12 @@
       </c>
       <c r="H188" s="48" t="inlineStr">
         <is>
-          <t>LALI 11' Outdoor Umbrella in Red | GOODDEGG</t>
+          <t>LALI 11' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I188" s="48" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 11' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J188" s="48" t="inlineStr">
@@ -27506,12 +27506,12 @@
       </c>
       <c r="H189" s="48" t="inlineStr">
         <is>
-          <t>LALI 11' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>LALI 11' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I189" s="48" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 11' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J189" s="48" t="inlineStr">
@@ -27652,12 +27652,12 @@
       </c>
       <c r="H190" s="24" t="inlineStr">
         <is>
-          <t>LALI 9' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>LALI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I190" s="24" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J190" s="24" t="inlineStr">
@@ -27800,12 +27800,12 @@
       </c>
       <c r="H191" s="24" t="inlineStr">
         <is>
-          <t>LALI 9' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>LALI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I191" s="24" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J191" s="24" t="inlineStr">
@@ -27946,12 +27946,12 @@
       </c>
       <c r="H192" s="24" t="inlineStr">
         <is>
-          <t>LALI 9' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>LALI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I192" s="24" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J192" s="24" t="inlineStr">
@@ -28094,12 +28094,12 @@
       </c>
       <c r="H193" s="24" t="inlineStr">
         <is>
-          <t>LALI 9' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>LALI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I193" s="24" t="inlineStr">
         <is>
-          <t>LALI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J193" s="24" t="inlineStr">
@@ -28240,12 +28240,12 @@
       </c>
       <c r="H194" s="38" t="inlineStr">
         <is>
-          <t>MORA 11' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>MORA 11' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I194" s="38" t="inlineStr">
         <is>
-          <t>MORA Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORA 11' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J194" s="38" t="inlineStr">
@@ -28384,12 +28384,12 @@
       </c>
       <c r="H195" s="38" t="inlineStr">
         <is>
-          <t>MORA 11' Outdoor Umbrella in Red | GOODDEGG</t>
+          <t>MORA 11' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I195" s="38" t="inlineStr">
         <is>
-          <t>MORA Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORA 11' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J195" s="38" t="inlineStr">
@@ -28528,12 +28528,12 @@
       </c>
       <c r="H196" s="38" t="inlineStr">
         <is>
-          <t>MORA 11' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>MORA 11' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I196" s="38" t="inlineStr">
         <is>
-          <t>MORA Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MORA 11' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J196" s="38" t="inlineStr">
@@ -28672,12 +28672,12 @@
       </c>
       <c r="H197" s="67" t="inlineStr">
         <is>
-          <t>MUSA Rectangular Market Umbrella in Canvas Stone | GOODDEGG</t>
+          <t>MUSA Rectangular Market Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I197" s="67" t="inlineStr">
         <is>
-          <t>MUSA Rectangular Market Umbrella improves outdoor comfort and extends usable seating hours. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MUSA Rectangular Market Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J197" s="67" t="inlineStr">
@@ -28816,12 +28816,12 @@
       </c>
       <c r="H198" s="67" t="inlineStr">
         <is>
-          <t>MUSA Rectangular Market Umbrella in Gray | GOODDEGG</t>
+          <t>MUSA Rectangular Market Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I198" s="67" t="inlineStr">
         <is>
-          <t>MUSA Rectangular Market Umbrella improves outdoor comfort and extends usable seating hours. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MUSA Rectangular Market Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J198" s="67" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="H199" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Beige | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I199" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J199" s="59" t="inlineStr">
@@ -29118,12 +29118,12 @@
       </c>
       <c r="H200" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Beige | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I200" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J200" s="59" t="inlineStr">
@@ -29269,12 +29269,12 @@
       </c>
       <c r="H201" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Blue | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I201" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J201" s="59" t="inlineStr">
@@ -29422,12 +29422,12 @@
       </c>
       <c r="H202" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Blue | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I202" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J202" s="59" t="inlineStr">
@@ -29573,12 +29573,12 @@
       </c>
       <c r="H203" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Gray | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I203" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J203" s="59" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="H204" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Gray | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I204" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J204" s="59" t="inlineStr">
@@ -29873,12 +29873,12 @@
       </c>
       <c r="H205" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Red | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I205" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J205" s="59" t="inlineStr">
@@ -30022,12 +30022,12 @@
       </c>
       <c r="H206" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Red | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I206" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J206" s="59" t="inlineStr">
@@ -30173,12 +30173,12 @@
       </c>
       <c r="H207" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Teal | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I207" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J207" s="59" t="inlineStr">
@@ -30322,12 +30322,12 @@
       </c>
       <c r="H208" s="59" t="inlineStr">
         <is>
-          <t>NUTI 10' Round Umbrella LED Light in Teal | GOODDEGG</t>
+          <t>NUTI 10' Round Umbrella, LED Light | GOODDEGG</t>
         </is>
       </c>
       <c r="I208" s="59" t="inlineStr">
         <is>
-          <t>NUTI Round Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NUTI 10' Round Umbrella, LED Light supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J208" s="59" t="inlineStr">
@@ -30473,12 +30473,12 @@
       </c>
       <c r="H209" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb and Control | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I209" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J209" s="35" t="inlineStr">
@@ -30626,12 +30626,12 @@
       </c>
       <c r="H210" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb and Control | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I210" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J210" s="35" t="inlineStr">
@@ -30777,12 +30777,12 @@
       </c>
       <c r="H211" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Blue | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I211" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J211" s="35" t="inlineStr">
@@ -30930,12 +30930,12 @@
       </c>
       <c r="H212" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Blue | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I212" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J212" s="35" t="inlineStr">
@@ -31081,12 +31081,12 @@
       </c>
       <c r="H213" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Gray | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I213" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J213" s="35" t="inlineStr">
@@ -31230,12 +31230,12 @@
       </c>
       <c r="H214" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Gray | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I214" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J214" s="35" t="inlineStr">
@@ -31381,12 +31381,12 @@
       </c>
       <c r="H215" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Red | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I215" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J215" s="35" t="inlineStr">
@@ -31530,12 +31530,12 @@
       </c>
       <c r="H216" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Red | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I216" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J216" s="35" t="inlineStr">
@@ -31681,12 +31681,12 @@
       </c>
       <c r="H217" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Teal | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I217" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J217" s="35" t="inlineStr">
@@ -31830,12 +31830,12 @@
       </c>
       <c r="H218" s="35" t="inlineStr">
         <is>
-          <t>SANO 10' SQ Umbrella Double Top, LED Bulb &amp; Control in Teal | GOODDEGG</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I218" s="35" t="inlineStr">
         <is>
-          <t>SANO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SANO 10' SQ Umbrella, Double Top, LED Bulb + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J218" s="35" t="inlineStr">
@@ -31976,12 +31976,12 @@
       </c>
       <c r="H219" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella in Black White | GOODDEGG</t>
+          <t>SLEEK Rectangular Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I219" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLEEK Rectangular Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J219" s="24" t="inlineStr">
@@ -32120,12 +32120,12 @@
       </c>
       <c r="H220" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella in Canvas Stone | GOODDEGG</t>
+          <t>SLEEK Rectangular Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I220" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLEEK Rectangular Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J220" s="24" t="inlineStr">
@@ -32264,12 +32264,12 @@
       </c>
       <c r="H221" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella in Dark Sapphire | GOODDEGG</t>
+          <t>SLEEK Rectangular Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I221" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLEEK Rectangular Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J221" s="24" t="inlineStr">
@@ -32408,12 +32408,12 @@
       </c>
       <c r="H222" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella in Graphite | GOODDEGG</t>
+          <t>SLEEK Rectangular Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I222" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLEEK Rectangular Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J222" s="24" t="inlineStr">
@@ -32552,12 +32552,12 @@
       </c>
       <c r="H223" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella in Light Sapphire | GOODDEGG</t>
+          <t>SLEEK Rectangular Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I223" s="24" t="inlineStr">
         <is>
-          <t>SLEEK Rectangular Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SLEEK Rectangular Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J223" s="24" t="inlineStr">
@@ -32696,12 +32696,12 @@
       </c>
       <c r="H224" s="31" t="inlineStr">
         <is>
-          <t>SOLI 9' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>SOLI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I224" s="31" t="inlineStr">
         <is>
-          <t>SOLI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOLI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J224" s="31" t="inlineStr">
@@ -32842,12 +32842,12 @@
       </c>
       <c r="H225" s="31" t="inlineStr">
         <is>
-          <t>SOLI 9' Outdoor Umbrella in Red | GOODDEGG</t>
+          <t>SOLI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I225" s="31" t="inlineStr">
         <is>
-          <t>SOLI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOLI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J225" s="31" t="inlineStr">
@@ -32988,12 +32988,12 @@
       </c>
       <c r="H226" s="31" t="inlineStr">
         <is>
-          <t>SOLI 9' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>SOLI 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I226" s="31" t="inlineStr">
         <is>
-          <t>SOLI Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOLI 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J226" s="31" t="inlineStr">
@@ -33134,12 +33134,12 @@
       </c>
       <c r="H227" s="65" t="inlineStr">
         <is>
-          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt in Blue | GOODDEGG</t>
+          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt | GOODDEGG</t>
         </is>
       </c>
       <c r="I227" s="65" t="inlineStr">
         <is>
-          <t>SOLI Outdoor Umbrella w/ Auto Tilt improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J227" s="65" t="inlineStr">
@@ -33278,12 +33278,12 @@
       </c>
       <c r="H228" s="65" t="inlineStr">
         <is>
-          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt in Red | GOODDEGG</t>
+          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt | GOODDEGG</t>
         </is>
       </c>
       <c r="I228" s="65" t="inlineStr">
         <is>
-          <t>SOLI Outdoor Umbrella w/ Auto Tilt improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J228" s="65" t="inlineStr">
@@ -33422,12 +33422,12 @@
       </c>
       <c r="H229" s="65" t="inlineStr">
         <is>
-          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt in Beige | GOODDEGG</t>
+          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt | GOODDEGG</t>
         </is>
       </c>
       <c r="I229" s="65" t="inlineStr">
         <is>
-          <t>SOLI Outdoor Umbrella w/ Auto Tilt improves outdoor comfort and extends usable seating. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOLI 9' Outdoor Umbrella w/ Auto Tilt supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J229" s="65" t="inlineStr">
@@ -33566,12 +33566,12 @@
       </c>
       <c r="H230" s="38" t="inlineStr">
         <is>
-          <t>TANO 9' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>TANO 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I230" s="38" t="inlineStr">
         <is>
-          <t>TANO Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANO 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J230" s="38" t="inlineStr">
@@ -33710,12 +33710,12 @@
       </c>
       <c r="H231" s="38" t="inlineStr">
         <is>
-          <t>TANO 9' Outdoor Umbrella in Blue | GOODDEGG</t>
+          <t>TANO 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I231" s="38" t="inlineStr">
         <is>
-          <t>TANO Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANO 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J231" s="38" t="inlineStr">
@@ -33856,12 +33856,12 @@
       </c>
       <c r="H232" s="38" t="inlineStr">
         <is>
-          <t>TANO 9' Outdoor Umbrella in Red | GOODDEGG</t>
+          <t>TANO 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I232" s="38" t="inlineStr">
         <is>
-          <t>TANO Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANO 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J232" s="38" t="inlineStr">
@@ -34000,12 +34000,12 @@
       </c>
       <c r="H233" s="38" t="inlineStr">
         <is>
-          <t>TANO 9' Outdoor Umbrella in Red | GOODDEGG</t>
+          <t>TANO 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I233" s="38" t="inlineStr">
         <is>
-          <t>TANO Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANO 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J233" s="38" t="inlineStr">
@@ -34146,12 +34146,12 @@
       </c>
       <c r="H234" s="38" t="inlineStr">
         <is>
-          <t>TANO 9' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>TANO 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I234" s="38" t="inlineStr">
         <is>
-          <t>TANO Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANO 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J234" s="38" t="inlineStr">
@@ -34290,12 +34290,12 @@
       </c>
       <c r="H235" s="38" t="inlineStr">
         <is>
-          <t>TANO 9' Outdoor Umbrella in Beige | GOODDEGG</t>
+          <t>TANO 9' Outdoor Umbrella | GOODDEGG</t>
         </is>
       </c>
       <c r="I235" s="38" t="inlineStr">
         <is>
-          <t>TANO Outdoor Umbrella improves outdoor comfort and extends usable seating hours with. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANO 9' Outdoor Umbrella supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J235" s="38" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="H236" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light and Control | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I236" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J236" s="67" t="inlineStr">
@@ -34594,12 +34594,12 @@
       </c>
       <c r="H237" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light and Control | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I237" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J237" s="67" t="inlineStr">
@@ -34745,12 +34745,12 @@
       </c>
       <c r="H238" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Blue | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I238" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J238" s="67" t="inlineStr">
@@ -34898,12 +34898,12 @@
       </c>
       <c r="H239" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Blue | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I239" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J239" s="67" t="inlineStr">
@@ -35049,12 +35049,12 @@
       </c>
       <c r="H240" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Gray | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I240" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J240" s="67" t="inlineStr">
@@ -35198,12 +35198,12 @@
       </c>
       <c r="H241" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Gray | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I241" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J241" s="67" t="inlineStr">
@@ -35349,12 +35349,12 @@
       </c>
       <c r="H242" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Red | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I242" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J242" s="67" t="inlineStr">
@@ -35498,12 +35498,12 @@
       </c>
       <c r="H243" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Red | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I243" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J243" s="67" t="inlineStr">
@@ -35649,12 +35649,12 @@
       </c>
       <c r="H244" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Teal | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I244" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J244" s="67" t="inlineStr">
@@ -35798,12 +35798,12 @@
       </c>
       <c r="H245" s="67" t="inlineStr">
         <is>
-          <t>XICO 8' SQ Umbrella Double Top, LED Light &amp; Control in Teal | GOODDEGG</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + Control | GOODDEGG</t>
         </is>
       </c>
       <c r="I245" s="67" t="inlineStr">
         <is>
-          <t>XICO Umbrella improves outdoor comfort and extends usable seating hours with shade. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XICO 8' SQ Umbrella, Double Top, LED Light + supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J245" s="67" t="inlineStr">
@@ -35944,12 +35944,12 @@
       </c>
       <c r="H246" s="59" t="inlineStr">
         <is>
-          <t>HALEY Hammock w/ Stand in Green Blue | GOODDEGG</t>
+          <t>HALEY Hammock w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I246" s="59" t="inlineStr">
         <is>
-          <t>The HALEY Hammock w/ Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEY Hammock w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J246" s="59" t="inlineStr">
@@ -36086,12 +36086,12 @@
       </c>
       <c r="H247" s="59" t="inlineStr">
         <is>
-          <t>HALEY Hammock w/ Stand in Brown Black | GOODDEGG</t>
+          <t>HALEY Hammock w/ Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I247" s="59" t="inlineStr">
         <is>
-          <t>The HALEY Hammock w/ Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALEY Hammock w/ Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J247" s="59" t="inlineStr">
@@ -36231,12 +36231,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>IMBLER Shelf in Natural | GOODDEGG</t>
+          <t>IMBLER Shelf | GOODDEGG</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>The IMBLER Shelf organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IMBLER Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -36372,12 +36372,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>POTTER Trolley in Natural | GOODDEGG</t>
+          <t>POTTER Trolley | GOODDEGG</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>The POTTER Trolley organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>POTTER Trolley Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -36513,12 +36513,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>TIMBER Shelf in Natural | GOODDEGG</t>
+          <t>TIMBER Shelf | GOODDEGG</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>The TIMBER Shelf organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TIMBER Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -36654,12 +36654,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>WATTER Trolley in Natural | GOODDEGG</t>
+          <t>WATTER Trolley | GOODDEGG</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>The WATTER Trolley organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WATTER Trolley Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -36793,7 +36793,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>The JOHARI Patio Coffee Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOHARI Patio Coffee Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -36914,12 +36914,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>KESI Patio Folding Bed in Natural | GOODDEGG</t>
+          <t>KESI Patio Folding Bed | GOODDEGG</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>The KESI Patio Folding Bed creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KESI Patio Folding Bed supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -37056,12 +37056,12 @@
       </c>
       <c r="H254" s="35" t="inlineStr">
         <is>
-          <t>KYUSHU Table and Loveseat in Beige Natural | GOODDEGG</t>
+          <t>KYUSHU Table + Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I254" s="35" t="inlineStr">
         <is>
-          <t>The KYUSHU Table and Loveseat creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU Table + Loveseat Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J254" s="35" t="inlineStr">
@@ -37200,12 +37200,12 @@
       </c>
       <c r="H255" s="35" t="inlineStr">
         <is>
-          <t>KYUSHU Table and Loveseat in Black Natural | GOODDEGG</t>
+          <t>KYUSHU Table + Loveseat | GOODDEGG</t>
         </is>
       </c>
       <c r="I255" s="35" t="inlineStr">
         <is>
-          <t>The KYUSHU Table and Loveseat creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYUSHU Table + Loveseat Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J255" s="35" t="inlineStr">
@@ -37344,12 +37344,12 @@
       </c>
       <c r="H256" s="31" t="inlineStr">
         <is>
-          <t>LOTUS 3 Pc. Patio Set in Black Light Brown | GOODDEGG</t>
+          <t>LOTUS 3 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I256" s="31" t="inlineStr">
         <is>
-          <t>The LOTUS Patio creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOTUS 3 Pc. Patio Set Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J256" s="31" t="inlineStr">
@@ -37488,12 +37488,12 @@
       </c>
       <c r="H257" s="31" t="inlineStr">
         <is>
-          <t>LOTUS 3 Pc. Patio Set in Natural Beige | GOODDEGG</t>
+          <t>LOTUS 3 Pc. Patio Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I257" s="31" t="inlineStr">
         <is>
-          <t>The LOTUS Patio creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOTUS 3 Pc. Patio Set Table Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J257" s="31" t="inlineStr">
@@ -37632,12 +37632,12 @@
       </c>
       <c r="H258" s="65" t="inlineStr">
         <is>
-          <t>MACKAY Patio Dining Table in Gun Metal Natural Teak | GOODDEGG</t>
+          <t>MACKAY Patio Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I258" s="65" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY Patio Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J258" s="65" t="inlineStr">
@@ -37776,12 +37776,12 @@
       </c>
       <c r="H259" s="65" t="inlineStr">
         <is>
-          <t>MACKAY Patio Dining Table in Gun Metal Natural Teak | GOODDEGG</t>
+          <t>MACKAY Patio Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I259" s="65" t="inlineStr">
         <is>
-          <t>The MACKAY Patio Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACKAY Patio Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J259" s="65" t="inlineStr">
@@ -37919,12 +37919,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>MALIA Patio Dining Table in Gray | GOODDEGG</t>
+          <t>MALIA Patio Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>The MALIA Patio Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA Patio Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -38061,12 +38061,12 @@
       </c>
       <c r="H261" s="48" t="inlineStr">
         <is>
-          <t>SINTRA Patio Dining Table in Black Gray | GOODDEGG</t>
+          <t>SINTRA Patio Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I261" s="48" t="inlineStr">
         <is>
-          <t>The SINTRA Patio Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA Patio Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J261" s="48" t="inlineStr">
@@ -38205,12 +38205,12 @@
       </c>
       <c r="H262" s="48" t="inlineStr">
         <is>
-          <t>SINTRA Patio Dining Table in Black Gray | GOODDEGG</t>
+          <t>SINTRA Patio Dining Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I262" s="48" t="inlineStr">
         <is>
-          <t>The SINTRA Patio Dining Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SINTRA Patio Dining Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J262" s="48" t="inlineStr">
@@ -38348,12 +38348,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>MALIA 5 Pc. Sectional Set w/ Bench in Gray | GOODDEGG</t>
+          <t>MALIA 5 Pc. Sectional Set w/ Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>The MALIA Sectional w/ Bench offers relaxed seating for everyday lounging. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 5 Pc. Sectional Set w/ Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -38489,12 +38489,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>MAUI Convertible Sofa Daybed in Gray Turquoise | GOODDEGG</t>
+          <t>MAUI Convertible Sofa Daybed | GOODDEGG</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>The MAUI Convertible Sofa Daybed creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAUI Convertible Sofa Daybed Day Bed supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -38630,12 +38630,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>VELDEN Convertible Sofa Daybed in Natural Gray | GOODDEGG</t>
+          <t>VELDEN Convertible Sofa Daybed | GOODDEGG</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>The VELDEN Convertible Sofa Daybed creates a restful centerpiece for the bedroom. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VELDEN Convertible Sofa Daybed Day Bed supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -38771,12 +38771,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>MOSIER Hall Tree w/ Bench &amp; Shoe Storage in Natural Gray | GOO</t>
+          <t>MOSIER Hall Tree w/ Bench &amp; Shoe Storage | GOODDEGG</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>MOSIER Hall Tree w/ Bench &amp; Shoe Storage brings everyday comfort and function to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MOSIER Hall Tree w/ Bench &amp; Shoe Storage supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -38913,12 +38913,12 @@
       </c>
       <c r="H267" s="46" t="inlineStr">
         <is>
-          <t>NIAMBI Square Table in Gray | GOODDEGG</t>
+          <t>NIAMBI Square Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I267" s="46" t="inlineStr">
         <is>
-          <t>The NIAMBI Square Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI Square Table Patio Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J267" s="46" t="inlineStr">
@@ -39055,12 +39055,12 @@
       </c>
       <c r="H268" s="46" t="inlineStr">
         <is>
-          <t>NIAMBI Square Table in Natural | GOODDEGG</t>
+          <t>NIAMBI Square Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I268" s="46" t="inlineStr">
         <is>
-          <t>The NIAMBI Square Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIAMBI Square Table Patio Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J268" s="46" t="inlineStr">
@@ -39196,12 +39196,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>ZUBERI Round Table in Natural | GOODDEGG</t>
+          <t>ZUBERI Round Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>The ZUBERI Round Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZUBERI Round Table Patio Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -39337,12 +39337,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>OLIVERI 4 Pc. Wicker Conversation Set in Brown Dark Teal | GOODDE</t>
+          <t>OLIVERI 4 Pc. Wicker Conversation Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>The OLIVERI Wicker Conversation brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVERI 4 Pc. Wicker Conversation Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -39478,7 +39478,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>OLIVERI Wicker Conversation ( Pack) brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVERI 4 Pc. Wicker Conversation Set (9 Pack) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -39607,12 +39607,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>SEGOVIA Fire Pit Table in Black Gray | GOODDEGG</t>
+          <t>SEGOVIA Fire Pit Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>The SEGOVIA Fire Pit Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGOVIA Fire Pit Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -39748,12 +39748,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>WAVE Stand in Black | GOODDEGG</t>
+          <t>WAVE Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>The WAVE Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WAVE Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">

--- a/FOA Singles/Outdoor-Single.xlsx
+++ b/FOA Singles/Outdoor-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Outdoor-Single.xlsx
+++ b/FOA Singles/Outdoor-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
